--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SOLAR-GLOW DRH v3.0 BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SOLAR-GLOW DRH v4.0 BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="8" min="1" max="1"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Indoor solar cells (charge the supercap stack); parallel via per-panel Schottky</t>
+          <t>Indoor solar cells - both merge to node SRC and feed the AEM10300 (U8), which runs MPPT and blocks reverse feed (v4: the per-panel blocking diodes are removed)</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="4" ht="23.25" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>D1, D9, D10, D11</t>
+          <t>SC1–SC4</t>
         </is>
       </c>
       <c r="B4" s="12" t="n">
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Blocking Schottky (D1/D9, VIN·VINB→VS); comparator-supply diode-OR (D10/D11, VIN·VINB→VCMP)</t>
+          <t>Supercap energy tank — 2P2S → 1 F @ 5.5 V ≈ 15 J</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Schottky, Vf≈0.3–0.6 V</t>
+          <t>1 F, 2.75 V (WS17)</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>SOD-123</t>
+          <t>WS17 (under-body P/N pads)</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>onsemi</t>
+          <t>SCHURTER</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>MMSD301T1G</t>
+          <t>3-153-438</t>
         </is>
       </c>
       <c r="H4" s="14" t="n">
-        <v>0.37</v>
+        <v>15.48</v>
       </c>
       <c r="I4" s="14" t="n">
-        <v>1.48</v>
+        <v>61.92</v>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
@@ -660,24 +660,24 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>Low-Vf for the ~4 V solar; one per panel so a half-shadow can't back-feed. DK P/N re-verified verbatim 2026-07-02 ($0.37 @ 1). Non-G MMSD301T1 is obsolete (Rochester stock only) - keep the G. D10/D11 added 2026-07-04: OR of VIN+VINB → VCMP powers clamp comparator U4 only while a panel produces (0 dark drain); same qualified MPN, qty 2→4.</t>
+          <t>⚠ DOMINANT COST. Solder to the under-body flat pads (asymmetric P/N widths = polarity key), NOT the end tabs. Confirm live price. DK product page verified 2026-07-02 (1 F, 2.75 V, SCPC). DK part number string not captured - order by MPN.</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>D1,D9,D10,D11  MMSD301T1G  $0.37.pdf</t>
+          <t>SC1-SC4  SCHURTER 3-153-438  $15.48.pdf</t>
         </is>
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>MMSD301T1GOSCT-ND</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23.25" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>SC1–SC4</t>
+          <t>D2–D5</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
@@ -685,34 +685,34 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Supercap energy tank — 2P2S → 1 F @ 5.5 V ≈ 15 J</t>
+          <t>Glow LEDs — reverse-mount; emit through the bare-FR4 'DRH' window</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>1 F, 2.75 V (WS17)</t>
+          <t>Amber 617 nm, Vf≈2.25 V</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>WS17 (under-body P/N pads)</t>
+          <t>SMD, 3.4x1.9 mm</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>SCHURTER</t>
+          <t>ams OSRAM</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>3-153-438</t>
+          <t>LA P47F-V2BB-24-3B5A-30-R18-Z</t>
         </is>
       </c>
       <c r="H5" s="14" t="n">
-        <v>15.48</v>
+        <v>0.43</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>61.92</v>
+        <v>1.72</v>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
@@ -721,121 +721,117 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>⚠ DOMINANT COST. Solder to the under-body flat pads (asymmetric P/N widths = polarity key), NOT the end tabs. Confirm live price. DK product page verified 2026-07-02 (1 F, 2.75 V, SCPC). DK part number string not captured - order by MPN.</t>
+          <t>Reverse-mount; light path runs through the all-layer keepout window. Fully verified 2026-07-02: DK lists the full code; ams-OSRAM packing doc maps it to Q65110A9267 = the REVERSE-mount bin per the LA P47F datasheet; DK CT number confirmed verbatim; 11.3k in stock; $0.43 @ 1 / $0.294 @ 10.</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>SC1-SC4  SCHURTER 3-153-438  $15.48.pdf</t>
+          <t>D2-D5  LA P47F-V2BB-24-3B5A-30-R18-Z  $0.43.pdf</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>475-LAP47F-V2BB-24-3B5A-30-R18-ZCT-ND</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34.5" customHeight="1" s="9">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>R1–R4</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Supercap balancer — dual SAB MOSFET across the MID node (auto leakage balance; keeps each cell &lt;2.75 V)</t>
+          <t>LED ballast — one per LED; sets per-LED current (low-side PWM)</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Dual SAB, ~0.3 nA–1 mA</t>
+          <t>150 Ω, ±1%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>SOIC-8</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Advanced Linear Devices</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>ALD910025SALI</t>
+          <t>RC0402FR-07150RL</t>
         </is>
       </c>
       <c r="H6" s="14" t="n">
-        <v>7.68</v>
+        <v>0.1</v>
       </c>
       <c r="I6" s="14" t="n">
-        <v>7.68</v>
+        <v>0.4</v>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>SIZED</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>DK page fetched 2026-07-02 (Devin-supplied URL): Active, tube, $7.68 @ 1 — but only 43 in stock and 8-wk mfr lead once depleted, so buy a spare. Page: "MOSFET DUAL SAB 2.5V", 8-SOIC 3.90 mm, dual N-ch = one package balances the 2-series stack. DK datasheet link = aldinc.com ALD810025.pdf (the combined ALD8100xx/9100xx doc = repo file). I-suffix = industrial temp; sch value fixed to SALI and committed.</t>
+          <t>Package corrected to 0402 to match the placed land (BOM previously listed 1206; a 1206 part will not fit). 1/16 W is ample (~12 mW peak/LED). Value still SIZED for the clamped ~3.47 V rail (~9 mA/LED peak); re-tune after the energy-budget bench test. Any 0402 150 Ω 1% equivalent works (esp. for PCBA sourcing).</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>U2  ALD910025SALI  $7.68.pdf (combined ALD8100xx/ALD9100xx doc)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>ALD910025SALI-ND</t>
+          <t>RC0402FR-07150RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="9">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>D2–D5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Glow LEDs — reverse-mount; emit through the bare-FR4 'DRH' window</t>
+          <t>TINY-mode ballast — dims all LEDs via SW2 'TINY' for long-runtime glow</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Amber 617 nm, Vf≈2.25 V</t>
+          <t>220 Ω, ±1%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>SMD, 3.4x1.9 mm</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>ams OSRAM</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>LA P47F-V2BB-24-3B5A-30-R18-Z</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>1.72</v>
-      </c>
+          <t>RC0402FR-07220RL</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="n"/>
+      <c r="I7" s="14" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -843,37 +839,37 @@
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>Reverse-mount; light path runs through the all-layer keepout window. Fully verified 2026-07-02: DK lists the full code; ams-OSRAM packing doc maps it to Q65110A9267 = the REVERSE-mount bin per the LA P47F datasheet; DK CT number confirmed verbatim; 11.3k in stock; $0.43 @ 1 / $0.294 @ 10.</t>
+          <t>Sets the SW2 TINY dim level; tunable. [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>D2-D5  LA P47F-V2BB-24-3B5A-30-R18-Z  $0.43.pdf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>475-LAP47F-V2BB-24-3B5A-30-R18-ZCT-ND</t>
+          <t>RC0402FR-07220RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="23.25" customHeight="1" s="9">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>R1–R4</t>
+          <t>R5, R6</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>LED ballast — one per LED; sets per-LED current (low-side PWM)</t>
+          <t>VSENSE divider — taps the solar input (VIN÷2) into PD2</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>150 Ω, ±1%</t>
+          <t>1 MΩ, ±1%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -888,23 +884,19 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07150RL</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>0.4</v>
-      </c>
+          <t>RC0402FR-071ML</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>SIZED</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>Package corrected to 0402 to match the placed land (BOM previously listed 1206; a 1206 part will not fit). 1/16 W is ample (~12 mW peak/LED). Value still SIZED for the clamped ~3.47 V rail (~9 mA/LED peak); re-tune after the energy-budget bench test. Any 0402 150 Ω 1% equivalent works (esp. for PCBA sourcing).</t>
+          <t>R5=R6 → VSENSE = VIN/2 (tracks light, ~0 V dark). Feeds ADC + the AC0 wake-on-light comparator. [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
@@ -914,14 +906,14 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07150RL-ND (format-derived — confirm at cart)</t>
+          <t>RC0402FR-071ML-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="23.25" customHeight="1" s="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
@@ -929,12 +921,12 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>TINY-mode ballast — dims all LEDs via SW2 'TINY' for long-runtime glow</t>
+          <t>VSENSE filter cap</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>220 Ω, ±1%</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -944,12 +936,12 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07220RL</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H9" s="14" t="n"/>
@@ -961,56 +953,60 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>Sets the SW2 TINY dim level; tunable. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC] [consolidation: 10nF -&gt; 100nF, joins the 100 nF group]</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07220RL-ND (format-derived — confirm at cart)</t>
+          <t>GRM155R71C103KA01D-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="23.25" customHeight="1" s="9">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>R5, R6</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>VSENSE divider — taps the solar input (VIN÷2) into PD2</t>
+          <t>3-axis accelerometer — tap/double-tap wake; INT1/INT2 → PF1/PF0</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>1 MΩ, ±1%</t>
+          <t>I²C 0x1D, ±2–8 g</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>LGA-12 CC-12-4 (2.2×2.3×0.87 mm)</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="n"/>
-      <c r="I10" s="14" t="n"/>
+          <t>ADXL367BCCZ-RL7</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1018,37 +1014,37 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>R5=R6 → VSENSE = VIN/2 (tracks light, ~0 V dark). Feeds ADC + the AC0 wake-on-light comparator. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>SCLK→GND (I²C); ASEL (pin 3)→GND ⇒ addr 0x1D. FOOTPRINT = placeholder ST land re-netted by pin #; swap ADI CC-12-4 land before fab.</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>datasheets/U3  ADXL367BCCZ-RL7  $7.50.pdf</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML-ND (format-derived — confirm at cart)</t>
+          <t>(by MPN)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="9">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>R10, R11</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>VSENSE filter cap</t>
+          <t>I²C pull-ups (TWI0 host on PC2/PC3) → VS</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>4.7 kΩ, ±1%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -1058,12 +1054,12 @@
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>RC0402FR-074K7L</t>
         </is>
       </c>
       <c r="H11" s="14" t="n"/>
@@ -1075,24 +1071,24 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC] [consolidation: 10nF -&gt; 100nF, joins the 100 nF group]</t>
+          <t>Required — open-drain TWI bus. Firmware must set TWIROUTEA = ALT2. [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C103KA01D-ND (format-derived — confirm at cart)</t>
+          <t>RC0402FR-074K7L-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" s="9">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
@@ -1100,34 +1096,34 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>3-axis accelerometer — tap/double-tap wake; INT1/INT2 → PF1/PF0</t>
+          <t>MCU decoupling (VDD)</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I²C 0x1D, ±2–8 g</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>LGA-12 CC-12-4 (2.2×2.3×0.87 mm)</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>ADXL367BCCZ-RL7</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H12" s="14" t="n">
-        <v>7.5</v>
+        <v>0.1</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>7.5</v>
+        <v>0.1</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
@@ -1136,37 +1132,37 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>SCLK→GND (I²C); ASEL (pin 3)→GND ⇒ addr 0x1D. FOOTPRINT = placeholder ST land re-netted by pin #; swap ADI CC-12-4 land before fab.</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C2/C3/C6/C7/C8 are the same line item.</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>datasheets/U3  ADXL367BCCZ-RL7  $7.50.pdf</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" s="9">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>R10, R11</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>I²C pull-ups (TWI0 host on PC2/PC3) → VS</t>
+          <t>MCU / VDDIO2 decoupling</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>4.7 kΩ, ±1%</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -1176,16 +1172,20 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-074K7L</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="n"/>
-      <c r="I13" s="14" t="n"/>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1193,24 +1193,24 @@
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>Required — open-drain TWI bus. Firmware must set TWIROUTEA = ALT2. [v3.0: 0402 to match board land; price TBC]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-074K7L-ND (format-derived — confirm at cart)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" s="9">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
@@ -1218,35 +1218,31 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Comparator + 1.242 V ref, open-drain</t>
+          <t>VS-rail bulk decoupling</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>TLV3011BIDBVR</t>
+          <t>4.7 µF, X5R, 10 V</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>TLV3011BIDBVR</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>2.78</v>
-      </c>
+          <t>GRM155R61A475MEAAD</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1254,24 +1250,24 @@
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>Rail-clamp comparator. B-grade TLV3011B chosen 2026-07-04 over the A: HALF the input offset (6 mV vs 12 mV max) tightens the clamp trip, LOWER Iq (3.1 uA vs 5 uA max) cuts standby drain off the supercaps, and it adds integrated hysteresis + fail-safe inputs + POR (all B-only) so a slow rail crossing wont chatter. Uncommitted on-chip 1.242 V ref (init +-1%, 100 ppm/degC max drift) + 10 pA input bias let the sense divider stay high-Z AND accurate. REPLACES the TLV431B whose 0.5 uA Iref across the 1.8 M top R pushed the real clamp to ~3.74 V typ / ~4.5 V worst (over the 3.6 V accel &amp; NFC ceilings). Open-drain OUT (reuses the R9 pullup), supply 1.65-5.5 V. Verified on CSV: SOT-23-6, 2,123 in stock, $2.78, ACTIVE. Datasheet in repo (U4  TLV3011BIDBVR  $2.78.pdf). Pinout (SOT-23-6): 1=V+ 2=REF 3=IN- 4=GND 5=OUT 6=IN+.</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] [consolidation: 1 µF -&gt; 4.7 µF, same part as C13]</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>U4  TLV3011BIDBVR  $2.78.pdf (repo; TI SBOS300C)</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>296-TLV3011BIDBVRCT-ND (cut tape; verified on CSV)</t>
+          <t>GRM155R61A105KE15D-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" s="9">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
@@ -1279,34 +1275,34 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Rail-clamp pass PNP — shunts VS→GND when U4 trips</t>
+          <t>Accelerometer decoupling</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>PNP (BCP53 family)</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>WDFN 2×2 (case 515AA)</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>onsemi</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>BCP5316MTWG</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>0.79</v>
+        <v>0.1</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>0.79</v>
+        <v>0.1</v>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
@@ -1315,24 +1311,24 @@
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>DK page fetched 2026-07-02 (Devin-supplied URL): Active, 2,961 in stock, bulk, $0.79 @ 1 / $0.489 @ 10. Page confirms 3-WDFNW (2×2) WETTABLE FLANK = board land (onsemi case 515AA) and hFE bin 100 @ 150 mA; DK datasheet link = repo Q1  BCP5316MTWG  $0.79.pdf. Mfr restock lead 32 wk — buy spares. Fallback alternates if ever dry: NSVBCP5316MTWG (auto twin), BCP5310MTWG (lower-bin, same case).</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>Q1  BCP5316MTWG  $0.79.pdf</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>488-BCP5316MTWG-ND</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="9">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
@@ -1340,12 +1336,12 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Clamp divider top — sets VS trip with R8</t>
+          <t>Accelerometer VREG_OUT decoupling (mandatory)</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>6.81 MΩ, ±1%</t>
+          <t>0.2 µF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -1355,16 +1351,20 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-076M81L</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
+          <t>GRM155R71C224KA12D</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1372,24 +1372,24 @@
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>Clamp divider top. Raised 2026-07-04 from 1.82 M to 6.81 M (with R8 3.74 M) to cut standby drain. Ratio 1.821 is unchanged, so the worst-case clamp stays 3.60 V (ref +-1% + 100 ppm/degC + resistor +-1%); trip is ratio-dependent, not value-dependent. WHY now possible: the TLV3011 comparator input bias is +-10 pA, so the IB*R7 offset is ~68 uV (negligible) even at 6.81 M -- the old TLV431 could not do this (its 0.5 uA Iref across 1.8 M was ~0.9 V of error, forcing low impedance). Benefit: the divider is the ONLY continuous passive drain off the supercaps; at ~3.5 V it drops from 1.24 uA to 0.33 uA (-73%). Stayed at 6.81 M (not 9.76 M) to keep margin below where PCB surface leakage perturbs a high-Z node. Hot-car note (unchanged, ratio-set): 85-105 degC worst-case ~3.61-3.65 V, still ~1 V under the 4.6/4.8 V absolute-max. Format-derived DK -- confirm at cart.</t>
+          <t>ADXL367 pin 9 VREG_OUT1 → GND. Datasheet-mandated 0.2 µF; 0.22 µF nearest std.</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-076M81L-ND (format-derived — confirm at cart)</t>
+          <t>(by MPN)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="9">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Clamp divider bottom</t>
+          <t>Accelerometer VDDIO decoupling</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>3.74 MΩ, ±1%</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -1412,16 +1412,20 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-073M74L</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1429,24 +1433,24 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>Clamp divider bottom. Raised 2026-07-04 from 1.00 M to 3.74 M in step with R7 (6.81 M) to lower standby drain while holding the 1.821 ratio (worst-case clamp 3.60 V unchanged). Fixed leg of VS = 1.242*(1+R7/R8). Format-derived DK -- confirm at cart.</t>
+          <t>ADXL367 pin 12 VDDIO → GND.</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-073M74L-ND (format-derived — confirm at cart)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="9">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
@@ -1454,12 +1458,12 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>Clamp base pull-up / cathode path</t>
+          <t>Local MCU-side decoupling</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>1 kΩ, ±1%</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1469,16 +1473,20 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-071KL</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="14" t="n"/>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1486,24 +1494,24 @@
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>VS→CLBASE; holds Q1 off until U4 conducts. [v3.0: 0402 to match board land; price TBC]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] C10 added 2026-07-04: 100 nF VCMP decoupling for the comparator (U4 now panel-powered via D10/D11). [C10 -&gt; DNP in consolidation: VCMP decoupling not strictly required]</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-071KL-ND (format-derived — confirm at cart)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="9">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>SJ1</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
@@ -1511,95 +1519,91 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>MCU decoupling (VDD)</t>
+          <t>VDDIO2 tie — bonds VDDIO2 to VS (MVIO unused)</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>0 Ω jumper</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>RC0805JR-070RL</t>
         </is>
       </c>
       <c r="H19" s="14" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C2/C3/C6/C7/C8 are the same line item.</t>
-        </is>
-      </c>
+      <c r="K19" s="13" t="n"/>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>RC0805JR-070RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="9">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>C2, C3</t>
+          <t>SW2</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>Decoupling — VDDIO2 / MCU</t>
+          <t>LED master switch — OFF / ON / TINY (solder-bridge)</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>3-pad bridge</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>solder-bridge</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>(none — PCB bridge)</t>
         </is>
       </c>
       <c r="H20" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
@@ -1608,56 +1612,60 @@
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t>ANODE common; bridge to VS (ON) or via R12 (TINY); open = OFF (hardware off).</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="9">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>SB1–SB4</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>VS-rail bulk decoupling</t>
+          <t>Per-LED force-on jumpers (bridge to force a channel on)</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>4.7 µF, X5R, 10 V</t>
+          <t>solder-bridge</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>solder-bridge</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>GRM155R61A475MEAAD</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="n"/>
-      <c r="I21" s="14" t="n"/>
+          <t>(none — PCB bridge)</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1665,24 +1673,24 @@
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] [consolidation: 1 µF -&gt; 4.7 µF, same part as C13]</t>
+          <t>Open = normal MCU control. Bridge to force that LED hard-on, bypassing the MCU.</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>GRM155R61A105KE15D-ND (format-derived — confirm at cart)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="9">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>TC1</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
@@ -1690,34 +1698,34 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Accelerometer decoupling</t>
+          <t>Tag-Connect TC2030 programming footprint (UPDI)</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>TC2030-MCP-FP</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>TC2030 legged land</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>(no part — pogo interface)</t>
         </is>
       </c>
       <c r="H22" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
@@ -1726,24 +1734,24 @@
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Hands-free UPDI; pairs with a TC2030-MCP cable.</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="9">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
@@ -1751,224 +1759,228 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Accelerometer VREG_OUT decoupling (mandatory)</t>
+          <t>UPDI header (backup to TC1)</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>0.2 µF, X7R, 16 V</t>
+          <t>1×3, 0.1″</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0.1″ THT pads</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C224KA12D</t>
+          <t>(unpopulated / 0.1″ header)</t>
         </is>
       </c>
       <c r="H23" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>OPTIONAL</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>ADXL367 pin 9 VREG_OUT1 → GND. Datasheet-mandated 0.2 µF; 0.22 µF nearest std.</t>
+          <t>Populate a 3-pin header if not using the Tag-Connect.</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="24" ht="23.25" customHeight="1" s="9">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Accelerometer VDDIO decoupling</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>100 nF, X7R, 16 V</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>GRM155R71C104KA88D</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>ADXL367 pin 12 VDDIO → GND.</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>(Murata GRM155 family)</t>
-        </is>
-      </c>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>490-3261-1-ND</t>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>JP1</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Bench pad strip — GND / VS / SCL / SDA probe pads (bench power injection + I²C tap)</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>4× bare SMD pads</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>1.7 mm sq, 2.54 mm pitch, B side</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>(bare pads — no component)</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>NO PART</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>v3.0 addition at (48.4, 14.54–22.16). Nothing to buy or place — mark DNP in the CPL. Pinout + bench ritual in solar-glow-drh-v2-hardware.md.</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="25" ht="23.25" customHeight="1" s="9">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Clamp local decoupling (C7 on VS; C10 on VCMP at U4 V+)</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>100 nF, X7R, 16 V</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>GRM155R71C104KA88D</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] C10 added 2026-07-04: 100 nF VCMP decoupling for the comparator (U4 now panel-powered via D10/D11). [C10 -&gt; DNP in consolidation: VCMP decoupling not strictly required]</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>(Murata GRM155 family)</t>
-        </is>
-      </c>
-      <c r="M25" s="11" t="inlineStr">
-        <is>
-          <t>490-3261-1-ND</t>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>VIN test pad (pre-D1 solar node) — charge test / panel emulation</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>1× bare SMD pad</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>1.7 mm sq, B side</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>(bare pad — no component)</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>NO PART</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>v3.0 addition at (48.4, 12.0). Mark DNP in the CPL.</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="9">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>SJ1</t>
+          <t>MH1–MH4</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>VDDIO2 tie — bonds VDDIO2 to VS (MVIO unused)</t>
+          <t>M2 mounting holes (grounded), board corners</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>0 Ω jumper</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>2.2 mm plated</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>RC0805JR-070RL</t>
+          <t>(no part — drill)</t>
         </is>
       </c>
       <c r="H26" s="14" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K26" s="13" t="n"/>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Ties a metal back-plate to GND if enclosed; user-supplied M2 hardware.</t>
+        </is>
+      </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -1976,14 +1988,14 @@
       </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>RC0805JR-070RL-ND (format-derived — confirm at cart)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="27" ht="23.25" customHeight="1" s="9">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
@@ -1991,34 +2003,34 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>LED master switch — OFF / ON / TINY (solder-bridge)</t>
+          <t>NFC tag — NTAG I²C plus 2K; phone reads/writes EEPROM, FD signals field to MCU</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>3-pad bridge</t>
+          <t>NTAG I²C plus, 2 KB, I²C 0x55</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>solder-bridge</t>
+          <t>XQFN8 (SOT902-3, 1.6×1.6×0.5 mm)</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NXP</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>(none — PCB bridge)</t>
+          <t>NT3H2211W0FHKH</t>
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -2027,59 +2039,59 @@
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>ANODE common; bridge to VS (ON) or via R12 (TINY); open = OFF (hardware off).</t>
+          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x1D). VCC→VS; VOUT pin 7 unconnected. Confirm live price. DK page verified 2026-07-02 (XFQFN8 exposed pad, $1.38 @ 1); Mouser cross: 771-NT3H2211W0FHKH, 9k stock.</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>U5  NT3H2211W0FHKH  $1.38.pdf</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="9">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>SB1–SB4</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Per-LED force-on jumpers (bridge to force a channel on)</t>
+          <t>NFC tag (U5) VCC decoupling</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>solder-bridge</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>solder-bridge</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>(none — PCB bridge)</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H28" s="14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
@@ -2088,24 +2100,24 @@
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>Open = normal MCU control. Bridge to force that LED hard-on, bypassing the MCU.</t>
+          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="9">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>TC1</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
@@ -2113,17 +2125,17 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Tag-Connect TC2030 programming footprint (UPDI)</t>
+          <t>NFC antenna trim — DNP (U5's internal 50 pF tunes the coil)</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>TC2030-MCP-FP</t>
+          <t>DNP (NP0/C0G land)</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>TC2030 legged land</t>
+          <t>0402 (NP0/C0G land)</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2133,7 +2145,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>(no part — pogo interface)</t>
+          <t>(DNP — not ordered)</t>
         </is>
       </c>
       <c r="H29" s="14" t="n">
@@ -2144,17 +2156,17 @@
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>Hands-free UPDI; pairs with a TC2030-MCP cable.</t>
+          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): the 364006 sheet (0.38 mm stack, µ′~100-150 class ferrite) against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
@@ -2166,7 +2178,7 @@
     <row r="30" ht="23.25" customHeight="1" s="9">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
@@ -2174,60 +2186,52 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>UPDI header (backup to TC1)</t>
+          <t>LED-anode bulk — supplies the glow-PWM transient locally, keeps it off the shared VS rail (MCU/accel)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>1×3, 0.1″</t>
+          <t>4.7 µF, X5R, 10 V</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>0.1″ THT pads</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>(unpopulated / 0.1″ header)</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>0</v>
-      </c>
+          <t>GRM155R61A475MEAAD</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>OPTIONAL</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Populate a 3-pin header if not using the Tag-Connect.</t>
-        </is>
-      </c>
-      <c r="L30" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>NEW bulk at the LED anode (LED side of SW2). ~3 uF effective at ~3.4 V after DC-bias derate = ~3x the C4 bulk. Place ~(20, 47.9) B.Cu, south of the window. Bench-gate: only load-bearing if the glow visibly modulates VS. 4.7 uF X5R 0402 10V is a real, stocked part; GRM155R61A475MEAAD is format-derived from the Murata convention — confirm exact suffix/availability at cart (Samsung CL05A475M* / Yageo CC0402 equiv all fine).</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="n"/>
       <c r="M30" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>GRM155R61A475MEAAD-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="23.25" customHeight="1" s="9">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>JP1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -2235,17 +2239,17 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Bench pad strip — GND / VS / SCL / SDA probe pads (bench power injection + I²C tap)</t>
+          <t>NFC antenna — PCB coil (LA/LB routed copper, F+B)</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>4× bare SMD pads</t>
+          <t>2.76 µH design value</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>1.7 mm sq, 2.54 mm pitch, B side</t>
+          <t>PCB copper — no package</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -2255,7 +2259,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>(bare pads — no component)</t>
+          <t>(no part — PCB feature)</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
@@ -2271,7 +2275,7 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition at (48.4, 14.54–22.16). Nothing to buy or place — mark DNP in the CPL. Pinout + bench ritual in solar-glow-drh-v2-hardware.md.</t>
+          <t>Sch-only symbol, no footprint. Inductance set by copper geometry; C9 land reserved for bench trim against it. Nothing to order or place.</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
@@ -2288,7 +2292,7 @@
     <row r="32" ht="15" customHeight="1" s="9">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>TP1</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
@@ -2296,840 +2300,694 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>VIN test pad (pre-D1 solar node) — charge test / panel emulation</t>
+          <t>NFC VNFC load switch — power-gates U5 VCC from PA7 (NFC_EN)</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>1× bare SMD pad</t>
+          <t>High-side load switch</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>1.7 mm sq, B side</t>
+          <t>SOT-23-6 (DBV)</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>(bare pad — no component)</t>
+          <t>TPS22918DBVR</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>NO PART</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition at (48.4, 12.0). Mark DNP in the CPL.</t>
+          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/U6  TPS22918DBVR  $0.55.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off.</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>U6  TPS22918DBVR  $0.55.pdf</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="9">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>MH1–MH4</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>M2 mounting holes (grounded), board corners</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>2.2 mm plated</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>(no part — drill)</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>NFC_EN pulldown — holds U6 OFF while PA7 tristates (UPDI / reset / brown-out)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>1 MΩ, ±1%</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>RC0402FR-071ML</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>Ties a metal back-plate to GND if enclosed; user-supplied M2 hardware.</t>
-        </is>
-      </c>
-      <c r="L33" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M33" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). DK verified 2026-07-02: RC0402FR-07100KL-ND (CT, Active, $0.10 @ 1); legacy 311-100KLRCT-ND also live. [consolidation: 100 kΩ -&gt; 1 MΩ, joins the R5/R6 reel]</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>RC0402FR-07100KL-ND</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="9">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>U5</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>NFC tag — NTAG I²C plus 2K; phone reads/writes EEPROM, FD signals field to MCU</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>NTAG I²C plus, 2 KB, I²C 0x55</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>XQFN8 (SOT902-3, 1.6×1.6×0.5 mm)</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>NXP</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>NT3H2211W0FHKH</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J34" s="11" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x1D). VCC→VS; VOUT pin 7 unconnected. Confirm live price. DK page verified 2026-07-02 (XFQFN8 exposed pad, $1.38 @ 1); Mouser cross: 771-NT3H2211W0FHKH, 9k stock.</t>
-        </is>
-      </c>
-      <c r="L34" s="11" t="inlineStr">
-        <is>
-          <t>U5  NT3H2211W0FHKH  $1.38.pdf</t>
-        </is>
-      </c>
-      <c r="M34" s="11" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN)</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ambient energy harvester PMIC - MPPT buck-boost; charges the supercap tank from the two panels</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AEM10300</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>QFN-28 (4x4 mm, EP land 2.30)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>e-peas</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>10AEM10300C0000</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Datasheet-confirmed orderable P/N (aem10300.pdf p1). Specialty long-lead part - order early.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>aem10300.pdf</t>
         </is>
       </c>
     </row>
     <row r="35" ht="23.25" customHeight="1" s="9">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>NFC tag (U5) VCC decoupling</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>100 nF, X7R, 16 V</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LDO - regulates STO down to the 3.3 V VS rail for the MCU/accel</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TPS7A0233, 3.3 V, ~25 nA Iq</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SOT-23-5</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>TPS7A0233PDBVR</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>v4 NEW - VERIFY</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>MPN suffix format-derived from TI TPS7A02 DBV convention; confirm exact orderable at cart. No repo datasheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="9">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FRAM - 512 kbit I2C archival log (0x50), power-gated on VNFC with the NFC tag</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MB85RC512TY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SOIC-8 (150 mil)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fujitsu/RAMXEED</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>MB85RC512TYPNF-GS-BCERE1</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Price from repo datasheet filename. AEC-Q100.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>U7  MB85RC512TYPNF-GS-BCERE1  $10.19.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="79.84999999999999" customHeight="1" s="9">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Power inductor - AEM10300 buck-boost DCDC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>10 uH</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0603 land (SEE NOTE)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Coilcraft (rec.)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>XFL2020-103MEB</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>v4 NEW - RECONCILE LAND</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>LAND TENSION: placed land is 0603, but a 10 uH / &gt;=1 A low-DCR part (XFL2020-103MEB) is 2.0x2.0 mm. Either grow the land to a 2016/2020 or pick a 0603 10 uH part sized to the (low) AEM peak current. Confirm before order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="9">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FB1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ferrite bead - STO island feed filter</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0603 bead</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Murata (rec.)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>BLM18PG221SN1D</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>v4 NEW - VERIFY</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No project part named; generic 0603 bead recommended (220 ohm @100 MHz). A low-DCR bead is preferable on a power feed - confirm at design review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="23.85" customHeight="1" s="9">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C22, C23</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LDO input (C22, STO side) + output (C23, VS side) caps</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1 uF, 0402, X5R</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Murata</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>GRM155R61A105KE15D</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Reuses the project 1 uF 0402 part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="9">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>STO-sense filter cap (on STO_SNS)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>100 nF, 0402, X7R</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>GRM155R71C104KA88D</t>
         </is>
       </c>
-      <c r="H35" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
-        </is>
-      </c>
-      <c r="L35" s="11" t="inlineStr">
-        <is>
-          <t>(Murata GRM155 family)</t>
-        </is>
-      </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>490-3261-1-ND</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="9">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>NFC antenna trim — DNP (U5's internal 50 pF tunes the coil)</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>DNP (NP0/C0G land)</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>0402 (NP0/C0G land)</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>(DNP — not ordered)</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): the 364006 sheet (0.38 mm stack, µ′~100-150 class ferrite) against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
-        </is>
-      </c>
-      <c r="L36" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M36" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="79.84999999999999" customHeight="1" s="9">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>LED-anode bulk — supplies the glow-PWM transient locally, keeps it off the shared VS rail (MCU/accel)</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>4.7 µF, X5R, 10 V</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Reuses the project 100 nF 0402 part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="9">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AEM BUFSRC input buffer cap</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22 uF, 0603, X5R</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Murata (rec.)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>GRM188R60J226MEA0D</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>v4 NEW - VERIFY</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>22 uF 6.3 V 0603; confirm DC-bias derate at the BUFSRC/SRC node.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="9">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C26, C27</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AEM VINT buffer (C26) + STO local bulk (C27)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10 uF, 0402, X5R</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Murata (rec.)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>GRM155R60J106ME44D</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>v4 NEW - VERIFY</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>10 uF 6.3 V 0402. C27 was 100 uF bulk; dropped to 10 uF since the 1 F supercaps already meet the AEM STO&gt;=100 uF minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="9">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FRAM VNFC decoupling</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>100 nF, 0402, X7R</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Murata</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>GRM155R61A475MEAAD</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="n"/>
-      <c r="I37" s="14" t="n"/>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>NEW bulk at the LED anode (LED side of SW2). ~3 uF effective at ~3.4 V after DC-bias derate = ~3x the C4 bulk. Place ~(20, 47.9) B.Cu, south of the window. Bench-gate: only load-bearing if the glow visibly modulates VS. 4.7 uF X5R 0402 10V is a real, stocked part; GRM155R61A475MEAAD is format-derived from the Murata convention — confirm exact suffix/availability at cart (Samsung CL05A475M* / Yageo CC0402 equiv all fine).</t>
-        </is>
-      </c>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="inlineStr">
-        <is>
-          <t>GRM155R61A475MEAAD-ND (format-derived — confirm at cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="9">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>NFC antenna — PCB coil (LA/LB routed copper, F+B)</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>2.76 µH design value</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>PCB copper — no package</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>(no part — PCB feature)</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>NO PART</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>Sch-only symbol, no footprint. Inductance set by copper geometry; C9 land reserved for bench trim against it. Nothing to order or place.</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="23.85" customHeight="1" s="9">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>NFC FD pull-up — open-drain FD (U5 pin 4) → PA6</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>10 kΩ, ±1%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Reuses the project 100 nF 0402 part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="9">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 M, 0402, 1%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Yageo</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>RC0402FR-0710KL</t>
-        </is>
-      </c>
-      <c r="H39" s="14" t="n"/>
-      <c r="I39" s="14" t="n"/>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>v2.2 NFC addition. Pulls open-drain FD up to VS. [v3.0: 0402 to match board land; price TBC] [consolidation: DNP, internal PA6 pull-up covers FD]</t>
-        </is>
-      </c>
-      <c r="L39" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M39" s="11" t="inlineStr">
-        <is>
-          <t>RC0402FR-0710KL-ND (format-derived — confirm at cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="9">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>U6</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>NFC VNFC load switch — power-gates U5 VCC from PA7 (NFC_EN)</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>High-side load switch</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>SOT-23-6 (DBV)</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>TPS22918DBVR</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/U6  TPS22918DBVR  $0.55.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off.</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t>U6  TPS22918DBVR  $0.55.pdf</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="9">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>NFC_EN pulldown — holds U6 OFF while PA7 tristates (UPDI / reset / brown-out)</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>1 MΩ, ±1%</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>RC0402FR-072ML</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>v4 NEW - VERIFY</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="9">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>R16, R17</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>STO sense divider bottom (R16) + EN_STO_CH pull-up to VINT (R17)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1 M, 0402, 1%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Yageo</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>RC0402FR-071ML</t>
         </is>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I41" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). DK verified 2026-07-02: RC0402FR-07100KL-ND (CT, Active, $0.10 @ 1); legacy 311-100KLRCT-ND also live. [consolidation: 100 kΩ -&gt; 1 MΩ, joins the R5/R6 reel]</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t>RC0402FR-07100KL-ND</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="9">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="9">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>PRG1</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Adafruit UPDI Friend</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>26.4×17.8 mm board + JST-SH lead</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
-      </c>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t>(guide linked in firmware/README)</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="9">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>CBL1</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>TC2030-MCP (legged, RJ12 end)</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>6-ft cable, 6P6C modular plug</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>Tag-Connect</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>TC2030-MCP</t>
-        </is>
-      </c>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
-      </c>
-      <c r="K44" s="8" t="inlineStr">
-        <is>
-          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
-        <is>
-          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
-        </is>
-      </c>
-      <c r="M44" s="8" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="9">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>HW1</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>head ⌀3.8 × 1.4 mm</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>(generic)</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
-        <is>
-          <t>DIN 84 M2×3 brass</t>
-        </is>
-      </c>
-      <c r="J45" s="8" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
-      </c>
-      <c r="K45" s="8" t="inlineStr">
-        <is>
-          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
-        </is>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
-        <is>
-          <t>docs/screw-m2x3-cheese.png</t>
-        </is>
-      </c>
-      <c r="M45" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Reuses the project 1 M part (shared with R5/R6/R14).</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="9">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>ENC1</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n">
-        <v>1</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Ti-6Al-4V, 3.55 mm stack</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>CNC from enclosure/ STEP</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>(PCBWay CNC or equiv.)</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>(order from enclosure/*.step)</t>
+          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
-        </is>
-      </c>
-      <c r="K46" s="8" t="inlineStr">
-        <is>
-          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t>enclosure/README.md</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="9">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>INS1</t>
+          <t>PRG1</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -3137,128 +2995,355 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>~0.05 mm polyimide, die-cut to board outline</t>
+          <t>Adafruit UPDI Friend</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>sheet / die-cut</t>
+          <t>26.4×17.8 mm board + JST-SH lead</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>(polyimide film, 0.05 mm)</t>
-        </is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>6.95</v>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>AUX-OPTIONAL</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(guide linked in firmware/README)</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="9">
       <c r="A48" s="8" t="inlineStr">
         <is>
+          <t>CBL1</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>TC2030-MCP (legged, RJ12 end)</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>6-ft cable, 6P6C modular plug</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Tag-Connect</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>TC2030-MCP</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>(DK page verified — order by MPN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="9">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>HW1</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>head ⌀3.8 × 1.4 mm</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>(generic)</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>DIN 84 M2×3 brass</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>docs/screw-m2x3-cheese.png</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>ENC1</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Ti-6Al-4V, 3.55 mm stack</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>CNC from enclosure/ STEP</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>(PCBWay CNC or equiv.)</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>(order from enclosure/*.step)</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>enclosure/README.md</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="360.4" customHeight="1" s="9">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>INS1</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>~0.05 mm polyimide, die-cut to board outline</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>sheet / die-cut</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>(generic)</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>(polyimide film, 0.05 mm)</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>AUX-OPTIONAL</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
           <t>FER1</t>
         </is>
       </c>
-      <c r="B48" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="B52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>Würth Elektronik</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>364006</t>
         </is>
       </c>
-      <c r="H48" s="8" t="n">
+      <c r="H52" s="8" t="n">
         <v>17.43</v>
       </c>
-      <c r="I48" s="8" t="n">
+      <c r="I52" s="8" t="n">
         <v>17.43</v>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
         </is>
       </c>
-      <c r="K48" s="8" t="inlineStr">
+      <c r="K52" s="8" t="inlineStr">
         <is>
           <t>FINAL, verified 2026-07-03: DK 732-5049-ND, Active, tray, $17.43 @ 1 (51 in stock at verification; 24-wk mfr lead — buy with the order). 60×60 mm sheet, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA); one sheet = 4 patches. Cut 12.2 × 25.8 mm on the 2 mm score grid; brace channel depth = measured stack − 0.05 (sits ~0.05 proud, seats flush; PET face to the board, PSA into the brace). Stock-dry fallback: 3× stacked 3641014 (732-13935-ND, $4.19 ea, µ′150/µ″3 @ 13.56 MHz, 0.14 mm ea) ≈ same ferrite thickness; last resort Laird MHLL6060-300 (240-2791-ND, 0.09 mm, weakest). All three datasheets in repo.</t>
         </is>
       </c>
-      <c r="L48" s="8" t="inlineStr">
+      <c r="L52" s="8" t="inlineStr">
         <is>
           <t>FER1  Wurth WE-FSFS 364006  $17.43.pdf + FER1-alt  Wurth WE-FSFS 3641014  $4.19.pdf + FER1-alt  Laird MHLL6060-300  $6.40.pdf (repo)</t>
         </is>
       </c>
-      <c r="M48" s="8" t="inlineStr">
+      <c r="M52" s="8" t="inlineStr">
         <is>
           <t>732-5049-ND</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="9">
-      <c r="G49" s="8" t="inlineStr">
+    <row r="53">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
         </is>
       </c>
-      <c r="I49" s="8" t="n">
+      <c r="I53" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="K49" s="8" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>Sum of the 30 priced Ext$ cells only — several converted lines remain unpriced pending quotes; see footnote.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="360.4" customHeight="1" s="9">
-      <c r="A51" s="15" t="inlineStr">
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).</t>
         </is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>DigiKey P/N</t>
+          <t>Distributor P/N (DigiKey unless noted)</t>
         </is>
       </c>
     </row>
@@ -2412,558 +2412,618 @@
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="9">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>U8</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Ambient energy harvester PMIC - MPPT buck-boost; charges the supercap tank from the two panels</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>AEM10300</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>QFN-28 (4x4 mm, EP land 2.30)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>e-peas</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>10AEM10300C0000</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Datasheet-confirmed orderable P/N (aem10300.pdf p1). Specialty long-lead part - order early.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>Datasheet-confirmed orderable P/N (aem10300.pdf p1). Specialty long-lead part - order early. SOURCING: MOUSER only - this is the one non-DigiKey line (e-peas is not a DigiKey vendor); Mouser carries the AEM10300 line (verified 2026-07). Order by MPN 10AEM10300C0000.</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t>aem10300.pdf</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>MOUSER 10AEM10300C0000 (e-peas; not a DigiKey vendor)</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="23.25" customHeight="1" s="9">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>U9</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
+      <c r="B35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>LDO - regulates STO down to the 3.3 V VS rail for the MCU/accel</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>TPS7A0233, 3.3 V, ~25 nA Iq</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>SOT-23-5</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>TPS7A0233PDBVR</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>Verified active on DigiKey (product 12165099): TPS7A0233PDBVR, SOT-23-5, 200 mA nanopower LDO (TI TPS7A02 family, ~25 nA Iq). No repo datasheet.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>296-TPS7A0233PDBVRCT-ND (DK 12165099, active; confirm CT/reel at cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="9">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>FRAM - 512 kbit I2C archival log (0x50), power-gated on VNFC with the NFC tag</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>MB85RC512TY</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>SOIC-8 (150 mil)</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Fujitsu/RAMXEED</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>MB85RC512TYPNF-GS-BCERE1</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>Price from repo datasheet filename. AEC-Q100.</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>U7  MB85RC512TYPNF-GS-BCERE1  $10.19.pdf</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>865-MB85RC512TYPNF-GS-BCERE1TR-ND</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="79.84999999999999" customHeight="1" s="9">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Power inductor - AEM10300 buck-boost DCDC</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>10 uH</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>2.5x2.0x1.0 mm (DFE252010); land grows past 0603</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>DFE252010F-100M</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>v4 NEW - LAND REWORK</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>AEM10300 datasheet Table 11 + section 9.8.2: LDCDC = 10 uH, must sustain &gt;=1 A peak at &gt;=10 MHz, low ESR. Murata DFE252010F-100M (10 uH, 1.76 A, 2.5x2.0x1.0 mm) is the datasheet-recommended part (supersedes the old XFL2020-103MEB, ~0.55 A / wrong land). The placed land is 0603 and must grow to the DFE252010 footprint - PCB geometry rework pending (user).</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>DFE252010F-100M (Murata; order by MPN, confirm DK P/N at cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="9">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>FB1</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Ferrite bead - STO island feed filter</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>0603 bead</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Murata (rec.)</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>BLM18PG221SN1D</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>v4 NEW - VERIFY</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>MPN suffix format-derived from TI TPS7A02 DBV convention; confirm exact orderable at cart. No repo datasheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="9">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>FRAM - 512 kbit I2C archival log (0x50), power-gated on VNFC with the NFC tag</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>MB85RC512TY</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>SOIC-8 (150 mil)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Fujitsu/RAMXEED</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>MB85RC512TYPNF-GS-BCERE1</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="I36" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>No project part named; generic 0603 bead recommended (220 ohm @100 MHz). A low-DCR bead is preferable on a power feed - confirm at design review.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>BLM18PG221SN1D-ND (format-derived - confirm at cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="23.85" customHeight="1" s="9">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>C22, C23</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>LDO input (C22, STO side) + output (C23, VS side) caps</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>1 uF, 0402, X5R</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>GRM155R61A105KE15D</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Price from repo datasheet filename. AEC-Q100.</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>U7  MB85RC512TYPNF-GS-BCERE1  $10.19.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="79.84999999999999" customHeight="1" s="9">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Power inductor - AEM10300 buck-boost DCDC</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>10 uH</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0603 land (SEE NOTE)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Coilcraft (rec.)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>XFL2020-103MEB</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>v4 NEW - RECONCILE LAND</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>LAND TENSION: placed land is 0603, but a 10 uH / &gt;=1 A low-DCR part (XFL2020-103MEB) is 2.0x2.0 mm. Either grow the land to a 2016/2020 or pick a 0603 10 uH part sized to the (low) AEM peak current. Confirm before order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="9">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>FB1</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ferrite bead - STO island feed filter</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0603 bead</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>Reuses the project 1 uF 0402 part.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>GRM155R61A105KE15D-ND (format-derived - confirm at cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="9">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>STO-sense filter cap (on STO_SNS)</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>100 nF, 0402, X7R</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Reuses the project 100 nF 0402 part.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>490-3261-1-ND</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="9">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>AEM BUFSRC input buffer cap</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>22 uF, 10 V, 0603, X5R</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>GRM188R61A226ME15D</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>GRM188R61A226ME15D-ND (format-derived - confirm at cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="9">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>C26, C27</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>AEM VINT buffer (C26) + STO local bulk (C27)</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>10 uF, 0402, X5R</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>Murata (rec.)</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>BLM18PG221SN1D</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>v4 NEW - VERIFY</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>No project part named; generic 0603 bead recommended (220 ohm @100 MHz). A low-DCR bead is preferable on a power feed - confirm at design review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="23.85" customHeight="1" s="9">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C22, C23</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>GRM155R60J106ME44D</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>AEM CINT per datasheet Table 11 (recommends GRM155R60J106ME15; ME44D is the current-production equivalent, 10 uF 6.3 V 0402 X5R). C27 was 100 uF bulk; dropped to 10 uF since the 1 F supercaps already meet the AEM STO&gt;=100 uF minimum.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>GRM155R60J106ME44D-ND (format-derived - confirm at cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="9">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>FRAM VNFC decoupling</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>100 nF, 0402, X7R</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>Reuses the project 100 nF 0402 part.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>490-3261-1-ND</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="9">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>2 M, 0402, 1%</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>RC0402FR-072ML</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>RC0402FR-072ML-ND (format-derived - confirm at cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="9">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>R16, R17</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>LDO input (C22, STO side) + output (C23, VS side) caps</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1 uF, 0402, X5R</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>STO sense divider bottom (R16) + EN_STO_CH pull-up to VINT (R17)</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>1 M, 0402, 1%</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>GRM155R61A105KE15D</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>RC0402FR-071ML</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Reuses the project 1 uF 0402 part.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="9">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C24</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>STO-sense filter cap (on STO_SNS)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>100 nF, 0402, X7R</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>GRM155R71C104KA88D</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>v4 NEW</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Reuses the project 100 nF 0402 part.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="9">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>C25</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AEM BUFSRC input buffer cap</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>22 uF, 0603, X5R</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Murata (rec.)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>GRM188R60J226MEA0D</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>v4 NEW - VERIFY</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>22 uF 6.3 V 0603; confirm DC-bias derate at the BUFSRC/SRC node.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="9">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>C26, C27</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AEM VINT buffer (C26) + STO local bulk (C27)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>10 uF, 0402, X5R</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Murata (rec.)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>GRM155R60J106ME44D</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>v4 NEW - VERIFY</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>10 uF 6.3 V 0402. C27 was 100 uF bulk; dropped to 10 uF since the 1 F supercaps already meet the AEM STO&gt;=100 uF minimum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="9">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>C28</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>FRAM VNFC decoupling</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>100 nF, 0402, X7R</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Murata</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>GRM155R71C104KA88D</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>v4 NEW</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Reuses the project 100 nF 0402 part.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="9">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>R15</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2 M, 0402, 1%</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Yageo</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>RC0402FR-072ML</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>v4 NEW - VERIFY</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="9">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>R16, R17</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STO sense divider bottom (R16) + EN_STO_CH pull-up to VINT (R17)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1 M, 0402, 1%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Yageo</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>RC0402FR-071ML</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>v4 NEW</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="8" t="inlineStr">
         <is>
           <t>Reuses the project 1 M part (shared with R5/R6/R14).</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="8" min="1" max="1"/>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>4.7 µF, X5R, 10 V</t>
+          <t>10 µF, X5R, 10 V</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -1238,19 +1238,19 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>GRM155R61A475MEAAD</t>
+          <t>GRM188R61A106KE69D</t>
         </is>
       </c>
       <c r="H14" s="14" t="n"/>
       <c r="I14" s="14" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>LAND REWORK</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] [consolidation: 1 µF -&gt; 4.7 µF, same part as C13]</t>
+          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603 for more effective VS bulk (stiffer rail under glow / NFC-inrush / accel transients). 0603 land - PCB rework.</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>GRM155R61A105KE15D-ND (format-derived — confirm at cart)</t>
+          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>4.7 µF, X5R, 10 V</t>
+          <t>10 µF, X5R, 10 V</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -2206,25 +2206,25 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>GRM155R61A475MEAAD</t>
+          <t>GRM188R61A106KE69D</t>
         </is>
       </c>
       <c r="H30" s="14" t="n"/>
       <c r="I30" s="14" t="n"/>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>LAND REWORK</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>NEW bulk at the LED anode (LED side of SW2). ~3 uF effective at ~3.4 V after DC-bias derate = ~3x the C4 bulk. Place ~(20, 47.9) B.Cu, south of the window. Bench-gate: only load-bearing if the glow visibly modulates VS. 4.7 uF X5R 0402 10V is a real, stocked part; GRM155R61A475MEAAD is format-derived from the Murata convention — confirm exact suffix/availability at cart (Samsung CL05A475M* / Yageo CC0402 equiv all fine).</t>
+          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603; keeps the glow-PWM transient off the shared VS rail. 0603 land - PCB rework.</t>
         </is>
       </c>
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="11" t="inlineStr">
         <is>
-          <t>GRM155R61A475MEAAD-ND (format-derived — confirm at cart)</t>
+          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
           <t>aem10300.pdf</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="8" t="inlineStr">
         <is>
           <t>MOUSER 10AEM10300C0000 (e-peas; not a DigiKey vendor)</t>
         </is>
@@ -2510,7 +2510,7 @@
           <t>Verified active on DigiKey (product 12165099): TPS7A0233PDBVR, SOT-23-5, 200 mA nanopower LDO (TI TPS7A02 family, ~25 nA Iq). No repo datasheet.</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="8" t="inlineStr">
         <is>
           <t>296-TPS7A0233PDBVRCT-ND (DK 12165099, active; confirm CT/reel at cart)</t>
         </is>
@@ -2571,7 +2571,7 @@
           <t>U7  MB85RC512TYPNF-GS-BCERE1  $10.19.pdf</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" s="8" t="inlineStr">
         <is>
           <t>865-MB85RC512TYPNF-GS-BCERE1TR-ND</t>
         </is>
@@ -2621,7 +2621,7 @@
           <t>AEM10300 datasheet Table 11 + section 9.8.2: LDCDC = 10 uH, must sustain &gt;=1 A peak at &gt;=10 MHz, low ESR. Murata DFE252010F-100M (10 uH, 1.76 A, 2.5x2.0x1.0 mm) is the datasheet-recommended part (supersedes the old XFL2020-103MEB, ~0.55 A / wrong land). The placed land is 0603 and must grow to the DFE252010 footprint - PCB geometry rework pending (user).</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="8" t="inlineStr">
         <is>
           <t>DFE252010F-100M (Murata; order by MPN, confirm DK P/N at cart)</t>
         </is>
@@ -2671,7 +2671,7 @@
           <t>No project part named; generic 0603 bead recommended (220 ohm @100 MHz). A low-DCR bead is preferable on a power feed - confirm at design review.</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t>BLM18PG221SN1D-ND (format-derived - confirm at cart)</t>
         </is>
@@ -2680,15 +2680,15 @@
     <row r="39" ht="23.85" customHeight="1" s="9">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>C22, C23</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>LDO input (C22, STO side) + output (C23, VS side) caps</t>
+          <t>LDO input cap (STO side)</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2718,10 +2718,10 @@
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 1 uF 0402 part.</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
+          <t>Reuses the project 1uF 0402 part.</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
         <is>
           <t>GRM155R61A105KE15D-ND (format-derived - confirm at cart)</t>
         </is>
@@ -2730,7 +2730,7 @@
     <row r="40" ht="15" customHeight="1" s="9">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>STO-sense filter cap (on STO_SNS)</t>
+          <t>LDO output cap (VS rail) - stability</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>100 nF, 0402, X7R</t>
+          <t>2.2 µF, 10 V, 0402, X5R</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRM155R61A225KE11D</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2768,19 +2768,19 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part.</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>490-3261-1-ND</t>
+          <t>Bumped 1uF -&gt; 2.2uF: TPS7A02 needs &gt;=0.5uF EFFECTIVE for stability; a 1uF 0402 worst-cases at that floor over bias/tol/temp/age. 2.2uF 0402 restores ~2x margin, no rework.</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>GRM155R61A225KE11D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="9">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
@@ -2788,17 +2788,17 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>AEM BUFSRC input buffer cap</t>
+          <t>STO-sense filter cap (on STO_SNS)</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>22 uF, 10 V, 0603, X5R</t>
+          <t>100 nF, 0402, X7R</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A226ME15D</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -2818,47 +2818,47 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard.</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>GRM188R61A226ME15D-ND (format-derived - confirm at cart)</t>
+          <t>Reuses the project 100 nF 0402 part.</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="9">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>C26, C27</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>AEM VINT buffer (C26) + STO local bulk (C27)</t>
+          <t>AEM BUFSRC input buffer cap</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>10 uF, 0402, X5R</t>
+          <t>22 uF, 10 V, 0603, X5R</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Murata (rec.)</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>GRM155R60J106ME44D</t>
+          <t>GRM188R61A226ME15D</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -2868,19 +2868,19 @@
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>AEM CINT per datasheet Table 11 (recommends GRM155R60J106ME15; ME44D is the current-production equivalent, 10 uF 6.3 V 0402 X5R). C27 was 100 uF bulk; dropped to 10 uF since the 1 F supercaps already meet the AEM STO&gt;=100 uF minimum.</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>GRM155R60J106ME44D-ND (format-derived - confirm at cart)</t>
+          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard.</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>GRM188R61A226ME15D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="9">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>FRAM VNFC decoupling</t>
+          <t>AEM VINT buffer cap</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>100 nF, 0402, X7R</t>
+          <t>10 uF, 0402, X5R</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Murata (rec.)</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRM155R60J106ME44D</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -2918,19 +2918,19 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>490-3261-1-ND</t>
+          <t>AEM CINT (datasheet Table 11: 10uF 6.3V 0402; ME44D is the current-production equivalent). VINT ~2.2V, so 6.3V rating is fine.</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>GRM155R60J106ME44D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="9">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
+          <t>STO local HF decoupling</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>2 M, 0402, 1%</t>
+          <t>4.7 µF, 10 V, 0402, X5R</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-072ML</t>
+          <t>GRM155R61A475MEAAD</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -2968,32 +2968,32 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>RC0402FR-072ML-ND (format-derived - confirm at cart)</t>
+          <t>Bumped 6.3V 10uF -&gt; 10V 4.7uF: STO rides to 4.65V where a 6.3V 0402 is thin (74% of rating) and heavily derated. 10V is the point; HF role (the 1F tank is the bulk). Reuses the 4.7uF 10V 0402 part.</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>GRM155R61A475MEAAD-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="9">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>R16, R17</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>STO sense divider bottom (R16) + EN_STO_CH pull-up to VINT (R17)</t>
+          <t>FRAM VNFC decoupling</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>1 M, 0402, 1%</t>
+          <t>100 nF, 0402, X7R</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -3018,181 +3018,171 @@
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 1 M part (shared with R5/R6/R14).</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
+          <t>Reuses the project 100 nF 0402 part.</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="9">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
+          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>2 M, 0402, 1%</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>RC0402FR-072ML</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart.</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>RC0402FR-072ML-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="9">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>PRG1</t>
+          <t>R16, R17</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
+          <t>STO sense divider bottom (R16) + EN_STO_CH pull-up to VINT (R17)</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Adafruit UPDI Friend</t>
+          <t>1 M, 0402, 1%</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>26.4×17.8 mm board + JST-SH lead</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Adafruit</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="I47" s="8" t="n">
-        <v>6.95</v>
+          <t>RC0402FR-071ML</t>
+        </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>v4 NEW</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>(guide linked in firmware/README)</t>
+          <t>Reuses the project 1 M part (shared with R5/R6/R14).</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
+          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="9">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>CBL1</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="n">
-        <v>1</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>TC2030-MCP (legged, RJ12 end)</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>6-ft cable, 6P6C modular plug</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>Tag-Connect</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>TC2030-MCP</t>
+          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
-        </is>
-      </c>
-      <c r="K48" s="8" t="inlineStr">
-        <is>
-          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
-        <is>
-          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
-        </is>
-      </c>
-      <c r="M48" s="8" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="9">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>HW1</t>
+          <t>PRG1</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
+          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
+          <t>Adafruit UPDI Friend</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>head ⌀3.8 × 1.4 mm</t>
+          <t>26.4×17.8 mm board + JST-SH lead</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>DIN 84 M2×3 brass</t>
-        </is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>6.95</v>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
@@ -3201,24 +3191,24 @@
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
+          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>docs/screw-m2x3-cheese.png</t>
+          <t>(guide linked in firmware/README)</t>
         </is>
       </c>
       <c r="M49" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>ENC1</t>
+          <t>CBL1</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
@@ -3226,27 +3216,27 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V, 3.55 mm stack</t>
+          <t>TC2030-MCP (legged, RJ12 end)</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>CNC from enclosure/ STEP</t>
+          <t>6-ft cable, 6P6C modular plug</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>(PCBWay CNC or equiv.)</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>(order from enclosure/*.step)</t>
+          <t>TC2030-MCP</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -3256,42 +3246,42 @@
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>enclosure/README.md</t>
+          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="360.4" customHeight="1" s="9">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>INS1</t>
+          <t>HW1</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>~0.05 mm polyimide, die-cut to board outline</t>
+          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>sheet / die-cut</t>
+          <t>head ⌀3.8 × 1.4 mm</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -3301,22 +3291,22 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>(polyimide film, 0.05 mm)</t>
+          <t>DIN 84 M2×3 brass</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>AUX-OPTIONAL</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>docs/screw-m2x3-cheese.png</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
@@ -3328,82 +3318,192 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
+          <t>ENC1</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Ti-6Al-4V, 3.55 mm stack</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>CNC from enclosure/ STEP</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>(PCBWay CNC or equiv.)</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>(order from enclosure/*.step)</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+        </is>
+      </c>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>enclosure/README.md</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>INS1</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>~0.05 mm polyimide, die-cut to board outline</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>sheet / die-cut</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>(generic)</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>(polyimide film, 0.05 mm)</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>AUX-OPTIONAL</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
           <t>FER1</t>
         </is>
       </c>
-      <c r="B52" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="B54" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>Würth Elektronik</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>364006</t>
         </is>
       </c>
-      <c r="H52" s="8" t="n">
+      <c r="H54" s="8" t="n">
         <v>17.43</v>
       </c>
-      <c r="I52" s="8" t="n">
+      <c r="I54" s="8" t="n">
         <v>17.43</v>
       </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
         </is>
       </c>
-      <c r="K52" s="8" t="inlineStr">
+      <c r="K54" s="8" t="inlineStr">
         <is>
           <t>FINAL, verified 2026-07-03: DK 732-5049-ND, Active, tray, $17.43 @ 1 (51 in stock at verification; 24-wk mfr lead — buy with the order). 60×60 mm sheet, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA); one sheet = 4 patches. Cut 12.2 × 25.8 mm on the 2 mm score grid; brace channel depth = measured stack − 0.05 (sits ~0.05 proud, seats flush; PET face to the board, PSA into the brace). Stock-dry fallback: 3× stacked 3641014 (732-13935-ND, $4.19 ea, µ′150/µ″3 @ 13.56 MHz, 0.14 mm ea) ≈ same ferrite thickness; last resort Laird MHLL6060-300 (240-2791-ND, 0.09 mm, weakest). All three datasheets in repo.</t>
         </is>
       </c>
-      <c r="L52" s="8" t="inlineStr">
+      <c r="L54" s="8" t="inlineStr">
         <is>
           <t>FER1  Wurth WE-FSFS 364006  $17.43.pdf + FER1-alt  Wurth WE-FSFS 3641014  $4.19.pdf + FER1-alt  Laird MHLL6060-300  $6.40.pdf (repo)</t>
         </is>
       </c>
-      <c r="M52" s="8" t="inlineStr">
+      <c r="M54" s="8" t="inlineStr">
         <is>
           <t>732-5049-ND</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="G53" s="8" t="inlineStr">
+    <row r="55">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
         </is>
       </c>
-      <c r="I53" s="8" t="n">
+      <c r="I55" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="K53" s="8" t="inlineStr">
+      <c r="K55" s="8" t="inlineStr">
         <is>
           <t>Sum of the 30 priced Ext$ cells only — several converted lines remain unpriced pending quotes; see footnote.</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).</t>
         </is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2943,12 +2943,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>4.7 µF, 10 V, 0402, X5R</t>
+          <t>10 µF, 10 V, 0603, X5R</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -2958,22 +2958,22 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A475MEAAD</t>
+          <t>GRM188R61A106KE69D</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>LAND REWORK</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>Bumped 6.3V 10uF -&gt; 10V 4.7uF: STO rides to 4.65V where a 6.3V 0402 is thin (74% of rating) and heavily derated. 10V is the point; HF role (the 1F tank is the bulk). Reuses the 4.7uF 10V 0402 part.</t>
+          <t>Moved to 0603 to keep 10uF at 10V (per request; matches C25's approach). STO rides to 4.65V where a 6.3V 0402 was thin + heavily derated; 10V 0603 gives full margin and effective bulk. Shares the C4/C13 10uF 10V 0603 reel. Land grows from 0402 - PCB rework.</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A475MEAAD-ND (format-derived - confirm at cart)</t>
+          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="15" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2598,7 +2598,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>2.5x2.0x1.0 mm (DFE252010); land grows past 0603</t>
+          <t>1008/2520 (L_1008_2520Metric), 2.5x2.0 mm</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW - LAND REWORK</t>
+          <t>v4 - ROUTE L2</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>AEM10300 datasheet Table 11 + section 9.8.2: LDCDC = 10 uH, must sustain &gt;=1 A peak at &gt;=10 MHz, low ESR. Murata DFE252010F-100M (10 uH, 1.76 A, 2.5x2.0x1.0 mm) is the datasheet-recommended part (supersedes the old XFL2020-103MEB, ~0.55 A / wrong land). The placed land is 0603 and must grow to the DFE252010 footprint - PCB geometry rework pending (user).</t>
+          <t>Murata DFE252010F-100M (10uH, 1.76A) per aem10300.pdf Table 11 / 9.8.2 (&gt;=1A, &gt;=10MHz, low ESR). Schematic footprint set to the KiCad stock 1008/2520 land (Inductor_SMD:L_1008_2520Metric, pads 1.25x2.2mm), the generic land for the 2.5x2.0mm package. Re-run Update-PCB to place it, then route (the earlier upload still had L2 on a 0603 land). Swap to Murata's exact DFE252010F land later if preferred.</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>SCLK→GND (I²C); ASEL (pin 3)→GND ⇒ addr 0x1D. FOOTPRINT = placeholder ST land re-netted by pin #; swap ADI CC-12-4 land before fab.</t>
+          <t>SCLK→GND (I²C); ASEL (pin 3)→GND ⇒ addr 0x1D. FOOTPRINT = ADI CC-12-4 land fitted (KiCad ADXL367 CC-12-4_ADI); verified vs datasheet Fig 64 (2.11×2.21 mm envelope, 0.5 mm pitch).</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
@@ -3501,6 +3501,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="15" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -1132,7 +1132,7 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C2/C3/C6/C7/C8 are the same line item.</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C3/C6/C7/C8 are the same line item.</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>0.2 µF, X7R, 16 V</t>
+          <t>0.22 µF (220 nF), X7R, 16 V</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] C10 added 2026-07-04: 100 nF VCMP decoupling for the comparator (U4 now panel-powered via D10/D11). [C10 -&gt; DNP in consolidation: VCMP decoupling not strictly required]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>ANODE common; bridge to VS (ON) or via R12 (TINY); open = OFF (hardware off).</t>
+          <t>ANODE common; bridge to STO (ON) or via R12 (TINY); open = OFF (hardware off).</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Bench pad strip — GND / VS / SCL / SDA probe pads (bench power injection + I²C tap)</t>
+          <t>Bench pad strip — GND / STO / SCL / SDA probe pads (bench power injection + I²C tap)</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>VIN test pad (pre-D1 solar node) — charge test / panel emulation</t>
+          <t>VIN test pad (solar node SRC) — charge test / panel emulation</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). DK verified 2026-07-02: RC0402FR-07100KL-ND (CT, Active, $0.10 @ 1); legacy 311-100KLRCT-ND also live. [consolidation: 100 kΩ -&gt; 1 MΩ, joins the R5/R6 reel]</t>
+          <t>v3.0 addition, placed with the R14 board patch. Consolidated 100 kΩ -&gt; 1 MΩ (joins the R5/R6/R16/R17 reel, RC0402FR-071ML).</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-07100KL-ND</t>
+          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="15" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2638,7 +2638,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Ferrite bead - STO island feed filter</t>
+          <t>Ferrite bead - STO_LDO island filter (isolates U9 LDO input from AEM DCDC ripple)</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -3501,6 +3501,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="15" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="8" min="1" max="1"/>
@@ -616,25 +616,25 @@
     <row r="4" ht="23.25" customHeight="1" s="9">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>SC1–SC4</t>
+          <t>SC1, SC3</t>
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Supercap energy tank — 2P2S → 1 F @ 5.5 V ≈ 15 J</t>
+          <t>Supercap energy tank (hybrid): larger SS17 cans, the 2S2P top pair, in series with the WS17 pair. Bank ~1.3 F @ 5.5 V, ~21 J total; AEM balances MID.</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>1 F, 2.75 V (WS17)</t>
+          <t>1.8 F, 2.75 V (SS17)</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>WS17 (under-body P/N pads)</t>
+          <t>SS17 (under-body P/N pads, 39 mm)</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -644,15 +644,11 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>3-153-438</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>15.48</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>61.92</v>
-      </c>
+          <t>3-153-440</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
       <c r="J4" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -660,7 +656,7 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>⚠ DOMINANT COST. Solder to the under-body flat pads (asymmetric P/N widths = polarity key), NOT the end tabs. Confirm live price. DK product page verified 2026-07-02 (1 F, 2.75 V, SCPC). DK part number string not captured - order by MPN.</t>
+          <t>DOMINANT COST (with the WS17 pair). Larger 1.8 F SS17 can; CONFIRM LIVE PRICE (pricier than the WS17). Solder to under-body flat pads (asymmetric P/N widths = polarity key), NOT end tabs. Hybrid: bigger cans placed where the board has room. Same SCPC family sheet as the WS17.</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
@@ -670,49 +666,49 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>(SCPC family sheet; order 3-153-440 by MPN, confirm price)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23.25" customHeight="1" s="9">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>D2–D5</t>
+          <t>SC2, SC4</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Glow LEDs — reverse-mount; emit through the bare-FR4 'DRH' window</t>
+          <t>Supercap energy tank (hybrid): smaller WS17 cans, the 2S2P bottom pair; see SC1/SC3 for the SS17 pair.</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Amber 617 nm, Vf≈2.25 V</t>
+          <t>1.0 F, 2.75 V (WS17)</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>SMD, 3.4x1.9 mm</t>
+          <t>WS17 (under-body P/N pads, 28.5 mm)</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>ams OSRAM</t>
+          <t>SCHURTER</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>LA P47F-V2BB-24-3B5A-30-R18-Z</t>
+          <t>3-153-438</t>
         </is>
       </c>
       <c r="H5" s="14" t="n">
-        <v>0.43</v>
+        <v>15.48</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>1.72</v>
+        <v>30.96</v>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
@@ -721,24 +717,24 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>Reverse-mount; light path runs through the all-layer keepout window. Fully verified 2026-07-02: DK lists the full code; ams-OSRAM packing doc maps it to Q65110A9267 = the REVERSE-mount bin per the LA P47F datasheet; DK CT number confirmed verbatim; 11.3k in stock; $0.43 @ 1 / $0.294 @ 10.</t>
+          <t>DOMINANT COST. Solder to under-body flat pads (asymmetric P/N widths = polarity key), NOT end tabs. DK product page verified 2026-07-02 (1 F, 2.75 V, SCPC). Order by MPN.</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>D2-D5  LA P47F-V2BB-24-3B5A-30-R18-Z  $0.43.pdf</t>
+          <t>SC1-SC4  SCHURTER 3-153-438  $15.48.pdf</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>475-LAP47F-V2BB-24-3B5A-30-R18-ZCT-ND</t>
+          <t>(DK page verified; order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34.5" customHeight="1" s="9">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>R1–R4</t>
+          <t>D2–D5</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -746,73 +742,73 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>LED ballast — one per LED; sets per-LED current (low-side PWM)</t>
+          <t>Glow LEDs — reverse-mount; emit through the bare-FR4 'DRH' window</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>150 Ω, ±1%</t>
+          <t>Amber 617 nm, Vf≈2.25 V</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SMD, 3.4x1.9 mm</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>ams OSRAM</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07150RL</t>
+          <t>LA P47F-V2BB-24-3B5A-30-R18-Z</t>
         </is>
       </c>
       <c r="H6" s="14" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="I6" s="14" t="n">
-        <v>0.4</v>
+        <v>1.72</v>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>SIZED</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Package corrected to 0402 to match the placed land (BOM previously listed 1206; a 1206 part will not fit). 1/16 W is ample (~12 mW peak/LED). Value still SIZED for the clamped ~3.47 V rail (~9 mA/LED peak); re-tune after the energy-budget bench test. Any 0402 150 Ω 1% equivalent works (esp. for PCBA sourcing).</t>
+          <t>Reverse-mount; light path runs through the all-layer keepout window. Fully verified 2026-07-02: DK lists the full code; ams-OSRAM packing doc maps it to Q65110A9267 = the REVERSE-mount bin per the LA P47F datasheet; DK CT number confirmed verbatim; 11.3k in stock; $0.43 @ 1 / $0.294 @ 10.</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>D2-D5  LA P47F-V2BB-24-3B5A-30-R18-Z  $0.43.pdf</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07150RL-ND (format-derived — confirm at cart)</t>
+          <t>475-LAP47F-V2BB-24-3B5A-30-R18-ZCT-ND</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="9">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R1–R4</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>TINY-mode ballast — dims all LEDs via SW2 'TINY' for long-runtime glow</t>
+          <t>LED ballast — one per LED; sets per-LED current (low-side PWM)</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>220 Ω, ±1%</t>
+          <t>150 Ω, ±1%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -827,19 +823,23 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07220RL</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="n"/>
-      <c r="I7" s="14" t="n"/>
+          <t>RC0402FR-07150RL</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.4</v>
+      </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>SIZED</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>Sets the SW2 TINY dim level; tunable. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Package corrected to 0402 to match the placed land (BOM previously listed 1206; a 1206 part will not fit). 1/16 W is ample (~12 mW peak/LED). Value still SIZED for the clamped ~3.47 V rail (~9 mA/LED peak); re-tune after the energy-budget bench test. Any 0402 150 Ω 1% equivalent works (esp. for PCBA sourcing).</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07220RL-ND (format-derived — confirm at cart)</t>
+          <t>RC0402FR-07150RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="23.25" customHeight="1" s="9">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>R5, R6</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>VSENSE divider — taps the solar input (VIN÷2) into PD2</t>
+          <t>TINY-mode ballast — dims all LEDs via SW2 'TINY' for long-runtime glow</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>1 MΩ, ±1%</t>
+          <t>220 Ω, ±1%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML</t>
+          <t>RC0402FR-07220RL</t>
         </is>
       </c>
       <c r="H8" s="14" t="n"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>R5=R6 → VSENSE = VIN/2 (tracks light, ~0 V dark). Feeds ADC + the AC0 wake-on-light comparator. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Sets the SW2 TINY dim level; tunable. [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
@@ -906,27 +906,27 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML-ND (format-derived — confirm at cart)</t>
+          <t>RC0402FR-07220RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="23.25" customHeight="1" s="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>R5, R6</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>VSENSE filter cap</t>
+          <t>VSENSE divider — taps the solar input (VIN÷2) into PD2</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>1 MΩ, ±1%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>RC0402FR-071ML</t>
         </is>
       </c>
       <c r="H9" s="14" t="n"/>
@@ -953,24 +953,24 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC] [consolidation: 10nF -&gt; 100nF, joins the 100 nF group]</t>
+          <t>R5=R6 → VSENSE = VIN/2 (tracks light, ~0 V dark). Feeds ADC + the AC0 wake-on-light comparator. [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C103KA01D-ND (format-derived — confirm at cart)</t>
+          <t>RC0402FR-071ML-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="23.25" customHeight="1" s="9">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -978,35 +978,31 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>3-axis accelerometer — tap/double-tap wake; INT1/INT2 → PF1/PF0</t>
+          <t>VSENSE filter cap</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>I²C 0x1D, ±2–8 g</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>LGA-12 CC-12-4 (2.2×2.3×0.87 mm)</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>ADXL367BCCZ-RL7</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>7.5</v>
-      </c>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="14" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1014,56 +1010,60 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>SCLK→GND (I²C); ASEL (pin 3)→GND ⇒ addr 0x1D. FOOTPRINT = ADI CC-12-4 land fitted (KiCad ADXL367 CC-12-4_ADI); verified vs datasheet Fig 64 (2.11×2.21 mm envelope, 0.5 mm pitch).</t>
+          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC] [consolidation: 10nF -&gt; 100nF, joins the 100 nF group]</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>datasheets/U3  ADXL367BCCZ-RL7  $7.50.pdf</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>GRM155R71C103KA01D-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="9">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>R10, R11</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>I²C pull-ups (TWI0 host on PC2/PC3) → VS</t>
+          <t>3-axis accelerometer — tap/double-tap wake; INT1/INT2 → PF1/PF0</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>4.7 kΩ, ±1%</t>
+          <t>I²C 0x1D, ±2–8 g</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>LGA-12 CC-12-4 (2.2×2.3×0.87 mm)</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-074K7L</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="n"/>
-      <c r="I11" s="14" t="n"/>
+          <t>ADXL367BCCZ-RL7</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1071,37 +1071,37 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>Required — open-drain TWI bus. Firmware must set TWIROUTEA = ALT2. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>SCLK→GND (I²C); ASEL (pin 3)→GND ⇒ addr 0x1D. FOOTPRINT = ADI CC-12-4 land fitted (KiCad ADXL367 CC-12-4_ADI); verified vs datasheet Fig 64 (2.11×2.21 mm envelope, 0.5 mm pitch).</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>datasheets/U3  ADXL367BCCZ-RL7  $7.50.pdf</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-074K7L-ND (format-derived — confirm at cart)</t>
+          <t>(by MPN)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" s="9">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>R10, R11</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>MCU decoupling (VDD)</t>
+          <t>I²C pull-ups (TWI0 host on PC2/PC3) → VS</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>4.7 kΩ, ±1%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -1111,20 +1111,16 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>0.1</v>
-      </c>
+          <t>RC0402FR-074K7L</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="14" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1132,24 +1128,24 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C3/C6/C7/C8 are the same line item.</t>
+          <t>Required — open-drain TWI bus. Firmware must set TWIROUTEA = ALT2. [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>RC0402FR-074K7L-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" s="9">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
@@ -1157,7 +1153,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>MCU / VDDIO2 decoupling</t>
+          <t>MCU decoupling (VDD)</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1184,7 +1180,7 @@
         <v>0.1</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
@@ -1193,7 +1189,7 @@
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C3/C6/C7/C8 are the same line item.</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
@@ -1210,7 +1206,7 @@
     <row r="14" ht="23.25" customHeight="1" s="9">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
@@ -1218,17 +1214,17 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>VS-rail bulk decoupling</t>
+          <t>MCU / VDDIO2 decoupling</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>10 µF, X5R, 10 V</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -1238,19 +1234,23 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>LAND REWORK</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603 for more effective VS bulk (stiffer rail under glow / NFC-inrush / accel transients). 0603 land - PCB rework.</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
@@ -1260,14 +1260,14 @@
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" s="9">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Accelerometer decoupling</t>
+          <t>VS-rail bulk decoupling</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>10 µF, X5R, 10 V</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1295,23 +1295,19 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>0.1</v>
-      </c>
+          <t>GRM188R61A106KE69D</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>LAND REWORK</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603 for more effective VS bulk (stiffer rail under glow / NFC-inrush / accel transients). 0603 land - PCB rework.</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
@@ -1321,14 +1317,14 @@
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="9">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
@@ -1336,12 +1332,12 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Accelerometer VREG_OUT decoupling (mandatory)</t>
+          <t>Accelerometer decoupling</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>0.22 µF (220 nF), X7R, 16 V</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C224KA12D</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H16" s="14" t="n">
@@ -1372,7 +1368,7 @@
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>ADXL367 pin 9 VREG_OUT1 → GND. Datasheet-mandated 0.2 µF; 0.22 µF nearest std.</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
@@ -1382,14 +1378,14 @@
       </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="9">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
@@ -1397,12 +1393,12 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Accelerometer VDDIO decoupling</t>
+          <t>Accelerometer VREG_OUT decoupling (mandatory)</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>0.22 µF (220 nF), X7R, 16 V</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -1417,7 +1413,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRM155R71C224KA12D</t>
         </is>
       </c>
       <c r="H17" s="14" t="n">
@@ -1433,7 +1429,7 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>ADXL367 pin 12 VDDIO → GND.</t>
+          <t>ADXL367 pin 9 VREG_OUT1 → GND. Datasheet-mandated 0.2 µF; 0.22 µF nearest std.</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
@@ -1443,14 +1439,14 @@
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>(by MPN)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="9">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
@@ -1458,7 +1454,7 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>Local MCU-side decoupling</t>
+          <t>Accelerometer VDDIO decoupling</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1485,7 +1481,7 @@
         <v>0.1</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
@@ -1494,7 +1490,7 @@
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t>ADXL367 pin 12 VDDIO → GND.</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
@@ -1511,7 +1507,7 @@
     <row r="19" ht="15" customHeight="1" s="9">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>SJ1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
@@ -1519,56 +1515,60 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>VDDIO2 tie — bonds VDDIO2 to VS (MVIO unused)</t>
+          <t>Local MCU-side decoupling</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>0 Ω jumper</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>RC0805JR-070RL</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H19" s="14" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K19" s="13" t="n"/>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+        </is>
+      </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>RC0805JR-070RL-ND (format-derived — confirm at cart)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="9">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>SJ1</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
@@ -1576,45 +1576,41 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>LED master switch — OFF / ON / TINY (solder-bridge)</t>
+          <t>VDDIO2 tie — bonds VDDIO2 to VS (MVIO unused)</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>3-pad bridge</t>
+          <t>0 Ω jumper</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>solder-bridge</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>(none — PCB bridge)</t>
+          <t>RC0805JR-070RL</t>
         </is>
       </c>
       <c r="H20" s="14" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>ANODE common; bridge to STO (ON) or via R12 (TINY); open = OFF (hardware off).</t>
-        </is>
-      </c>
+      <c r="K20" s="13" t="n"/>
       <c r="L20" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -1622,27 +1618,27 @@
       </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>RC0805JR-070RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="9">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>SB1–SB4</t>
+          <t>SW2</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Per-LED force-on jumpers (bridge to force a channel on)</t>
+          <t>LED master switch — OFF / ON / TINY (solder-bridge)</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>solder-bridge</t>
+          <t>3-pad bridge</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1673,7 +1669,7 @@
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>Open = normal MCU control. Bridge to force that LED hard-on, bypassing the MCU.</t>
+          <t>ANODE common; bridge to STO (ON) or via R12 (TINY); open = OFF (hardware off).</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
@@ -1690,25 +1686,25 @@
     <row r="22" ht="15" customHeight="1" s="9">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>TC1</t>
+          <t>SB1–SB4</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Tag-Connect TC2030 programming footprint (UPDI)</t>
+          <t>Per-LED force-on jumpers (bridge to force a channel on)</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>TC2030-MCP-FP</t>
+          <t>solder-bridge</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>TC2030 legged land</t>
+          <t>solder-bridge</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -1718,7 +1714,7 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>(no part — pogo interface)</t>
+          <t>(none — PCB bridge)</t>
         </is>
       </c>
       <c r="H22" s="14" t="n">
@@ -1734,12 +1730,12 @@
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>Hands-free UPDI; pairs with a TC2030-MCP cable.</t>
+          <t>Open = normal MCU control. Bridge to force that LED hard-on, bypassing the MCU.</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
@@ -1751,7 +1747,7 @@
     <row r="23" ht="15" customHeight="1" s="9">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>TC1</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
@@ -1759,17 +1755,17 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>UPDI header (backup to TC1)</t>
+          <t>Tag-Connect TC2030 programming footprint (UPDI)</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>1×3, 0.1″</t>
+          <t>TC2030-MCP-FP</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>0.1″ THT pads</t>
+          <t>TC2030 legged land</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -1779,7 +1775,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>(unpopulated / 0.1″ header)</t>
+          <t>(no part — pogo interface)</t>
         </is>
       </c>
       <c r="H23" s="14" t="n">
@@ -1790,81 +1786,81 @@
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Hands-free UPDI; pairs with a TC2030-MCP cable.</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
+        </is>
+      </c>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="23.25" customHeight="1" s="9">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>UPDI header (backup to TC1)</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>1×3, 0.1″</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>0.1″ THT pads</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>(unpopulated / 0.1″ header)</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
           <t>OPTIONAL</t>
         </is>
       </c>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="K24" s="13" t="inlineStr">
         <is>
           <t>Populate a 3-pin header if not using the Tag-Connect.</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="23.25" customHeight="1" s="9">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>JP1</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Bench pad strip — GND / STO / SCL / SDA probe pads (bench power injection + I²C tap)</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>4× bare SMD pads</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>1.7 mm sq, 2.54 mm pitch, B side</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>(bare pads — no component)</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>NO PART</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>v3.0 addition at (48.4, 14.54–22.16). Nothing to buy or place — mark DNP in the CPL. Pinout + bench ritual in solar-glow-drh-v2-hardware.md.</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1873,7 +1869,7 @@
     <row r="25" ht="23.25" customHeight="1" s="9">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>TP1</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -1881,17 +1877,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>VIN test pad (solar node SRC) — charge test / panel emulation</t>
+          <t>Bench pad strip — GND / STO / SCL / SDA probe pads (bench power injection + I²C tap)</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>1× bare SMD pad</t>
+          <t>4× bare SMD pads</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>1.7 mm sq, B side</t>
+          <t>1.7 mm sq, 2.54 mm pitch, B side</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -1901,7 +1897,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>(bare pad — no component)</t>
+          <t>(bare pads — no component)</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
@@ -1917,76 +1913,76 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
+          <t>v3.0 addition at (48.4, 14.54–22.16). Nothing to buy or place — mark DNP in the CPL. Pinout + bench ritual in solar-glow-drh-v2-hardware.md.</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="9">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>VIN test pad (solar node SRC) — charge test / panel emulation</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>1× bare SMD pad</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>1.7 mm sq, B side</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>(bare pad — no component)</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>NO PART</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
           <t>v3.0 addition at (48.4, 12.0). Mark DNP in the CPL.</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="9">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>MH1–MH4</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>M2 mounting holes (grounded), board corners</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>2.2 mm plated</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>(no part — drill)</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>Ties a metal back-plate to GND if enclosed; user-supplied M2 hardware.</t>
-        </is>
-      </c>
-      <c r="L26" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="11" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1995,42 +1991,42 @@
     <row r="27" ht="23.25" customHeight="1" s="9">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>MH1–MH4</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>NFC tag — NTAG I²C plus 2K; phone reads/writes EEPROM, FD signals field to MCU</t>
+          <t>M2 mounting holes (grounded), board corners</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>NTAG I²C plus, 2 KB, I²C 0x55</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>XQFN8 (SOT902-3, 1.6×1.6×0.5 mm)</t>
+          <t>2.2 mm plated</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>NXP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>NT3H2211W0FHKH</t>
+          <t>(no part — drill)</t>
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
@@ -2039,24 +2035,24 @@
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x1D). VCC→VS; VOUT pin 7 unconnected. Confirm live price. DK page verified 2026-07-02 (XFQFN8 exposed pad, $1.38 @ 1); Mouser cross: 771-NT3H2211W0FHKH, 9k stock.</t>
+          <t>Ties a metal back-plate to GND if enclosed; user-supplied M2 hardware.</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>U5  NT3H2211W0FHKH  $1.38.pdf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="9">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
@@ -2064,34 +2060,34 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>NFC tag (U5) VCC decoupling</t>
+          <t>NFC tag — NTAG I²C plus 2K; phone reads/writes EEPROM, FD signals field to MCU</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>NTAG I²C plus, 2 KB, I²C 0x55</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>XQFN8 (SOT902-3, 1.6×1.6×0.5 mm)</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>NXP</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>NT3H2211W0FHKH</t>
         </is>
       </c>
       <c r="H28" s="14" t="n">
-        <v>0.1</v>
+        <v>1.38</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0.1</v>
+        <v>1.38</v>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
@@ -2100,24 +2096,24 @@
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x1D). VCC→VS; VOUT pin 7 unconnected. Confirm live price. DK page verified 2026-07-02 (XFQFN8 exposed pad, $1.38 @ 1); Mouser cross: 771-NT3H2211W0FHKH, 9k stock.</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>U5  NT3H2211W0FHKH  $1.38.pdf</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="9">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
@@ -2125,174 +2121,174 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>NFC antenna trim — DNP (U5's internal 50 pF tunes the coil)</t>
+          <t>NFC tag (U5) VCC decoupling</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>DNP (NP0/C0G land)</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>0402 (NP0/C0G land)</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>(DNP — not ordered)</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="H29" s="14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>DNP</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): the 364006 sheet (0.38 mm stack, µ′~100-150 class ferrite) against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
+          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="30" ht="23.25" customHeight="1" s="9">
       <c r="A30" s="11" t="inlineStr">
         <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>NFC antenna trim — DNP (U5's internal 50 pF tunes the coil)</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>DNP (NP0/C0G land)</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>0402 (NP0/C0G land)</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>(DNP — not ordered)</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): the 364006 sheet (0.38 mm stack, µ′~100-150 class ferrite) against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="23.25" customHeight="1" s="9">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="B31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>LED-anode bulk — supplies the glow-PWM transient locally, keeps it off the shared VS rail (MCU/accel)</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>10 µF, X5R, 10 V</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Murata</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>GRM188R61A106KE69D</t>
         </is>
       </c>
-      <c r="H30" s="14" t="n"/>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>LAND REWORK</t>
         </is>
       </c>
-      <c r="K30" s="13" t="inlineStr">
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603; keeps the glow-PWM transient off the shared VS rail. 0603 land - PCB rework.</t>
         </is>
       </c>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="11" t="inlineStr">
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="inlineStr">
         <is>
           <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="23.25" customHeight="1" s="9">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>NFC antenna — PCB coil (LA/LB routed copper, F+B)</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>2.76 µH design value</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>PCB copper — no package</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>(no part — PCB feature)</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>NO PART</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>Sch-only symbol, no footprint. Inductance set by copper geometry; C9 land reserved for bench trim against it. Nothing to order or place.</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="9">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
@@ -2300,60 +2296,60 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>NFC VNFC load switch — power-gates U5 VCC from PA7 (NFC_EN)</t>
+          <t>NFC antenna — PCB coil (LA/LB routed copper, F+B)</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>High-side load switch</t>
+          <t>2.76 µH design value</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>SOT-23-6 (DBV)</t>
+          <t>PCB copper — no package</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>TPS22918DBVR</t>
+          <t>(no part — PCB feature)</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>NO PART</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/U6  TPS22918DBVR  $0.55.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off.</t>
+          <t>Sch-only symbol, no footprint. Inductance set by copper geometry; C9 land reserved for bench trim against it. Nothing to order or place.</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>U6  TPS22918DBVR  $0.55.pdf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="9">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
@@ -2361,34 +2357,34 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>NFC_EN pulldown — holds U6 OFF while PA7 tristates (UPDI / reset / brown-out)</t>
+          <t>NFC VNFC load switch — power-gates U5 VCC from PA7 (NFC_EN)</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>1 MΩ, ±1%</t>
+          <t>High-side load switch</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>SOT-23-6 (DBV)</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML</t>
+          <t>TPS22918DBVR</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
@@ -2397,24 +2393,24 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition, placed with the R14 board patch. Consolidated 100 kΩ -&gt; 1 MΩ (joins the R5/R6/R16/R17 reel, RC0402FR-071ML).</t>
+          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/U6  TPS22918DBVR  $0.55.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off.</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>U6  TPS22918DBVR  $0.55.pdf</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="9">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
@@ -2422,54 +2418,60 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Ambient energy harvester PMIC - MPPT buck-boost; charges the supercap tank from the two panels</t>
+          <t>NFC_EN pulldown — holds U6 OFF while PA7 tristates (UPDI / reset / brown-out)</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>AEM10300</t>
+          <t>1 MΩ, ±1%</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>QFN-28 (4x4 mm, EP land 2.30)</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>e-peas</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>10AEM10300C0000</t>
-        </is>
+          <t>RC0402FR-071ML</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>0.1</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>Datasheet-confirmed orderable P/N (aem10300.pdf p1). Specialty long-lead part - order early. SOURCING: MOUSER only - this is the one non-DigiKey line (e-peas is not a DigiKey vendor); Mouser carries the AEM10300 line (verified 2026-07). Order by MPN 10AEM10300C0000.</t>
+          <t>v3.0 addition, placed with the R14 board patch. Consolidated 100 kΩ -&gt; 1 MΩ (joins the R5/R6/R16/R17 reel, RC0402FR-071ML).</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>aem10300.pdf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>MOUSER 10AEM10300C0000 (e-peas; not a DigiKey vendor)</t>
+          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="23.25" customHeight="1" s="9">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
@@ -2477,27 +2479,27 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>LDO - regulates STO down to the 3.3 V VS rail for the MCU/accel</t>
+          <t>Ambient energy harvester PMIC - MPPT buck-boost; charges the supercap tank from the two panels</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>TPS7A0233, 3.3 V, ~25 nA Iq</t>
+          <t>AEM10300</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>QFN-28 (4x4 mm, EP land 2.30)</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>e-peas</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>TPS7A0233PDBVR</t>
+          <t>10AEM10300C0000</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -2507,19 +2509,24 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>Verified active on DigiKey (product 12165099): TPS7A0233PDBVR, SOT-23-5, 200 mA nanopower LDO (TI TPS7A02 family, ~25 nA Iq). No repo datasheet.</t>
+          <t>Datasheet-confirmed orderable P/N (aem10300.pdf p1). Specialty long-lead part - order early. SOURCING: MOUSER only - this is the one non-DigiKey line (e-peas is not a DigiKey vendor); Mouser carries the AEM10300 line (verified 2026-07). Order by MPN 10AEM10300C0000.</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>aem10300.pdf</t>
         </is>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>296-TPS7A0233PDBVRCT-ND (DK 12165099, active; confirm CT/reel at cart)</t>
+          <t>MOUSER 10AEM10300C0000 (e-peas; not a DigiKey vendor)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="9">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
@@ -2527,34 +2534,28 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>FRAM - 512 kbit I2C archival log (0x50), power-gated on VNFC with the NFC tag</t>
+          <t>LDO - regulates STO down to the 3.3 V VS rail for the MCU/accel</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>MB85RC512TY</t>
+          <t>TPS7A0233, 3.3 V, ~25 nA Iq</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>SOIC-8 (150 mil)</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Fujitsu/RAMXEED</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>MB85RC512TYPNF-GS-BCERE1</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>10.19</v>
+          <t>TPS7A0233PDBVR</t>
+        </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
@@ -2563,24 +2564,19 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>Price from repo datasheet filename. AEC-Q100.</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>U7  MB85RC512TYPNF-GS-BCERE1  $10.19.pdf</t>
+          <t>Verified active on DigiKey (product 12165099): TPS7A0233PDBVR, SOT-23-5, 200 mA nanopower LDO (TI TPS7A02 family, ~25 nA Iq). No repo datasheet.</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>865-MB85RC512TYPNF-GS-BCERE1TR-ND</t>
+          <t>296-TPS7A0233PDBVRCT-ND (DK 12165099, active; confirm CT/reel at cart)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="79.84999999999999" customHeight="1" s="9">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -2588,49 +2584,60 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Power inductor - AEM10300 buck-boost DCDC</t>
+          <t>FRAM - 512 kbit I2C archival log (0x50), power-gated on VNFC with the NFC tag</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>10 uH</t>
+          <t>MB85RC512TY</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>1008/2520 (L_1008_2520Metric), 2.5x2.0 mm</t>
+          <t>SOIC-8 (150 mil)</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Fujitsu/RAMXEED</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>DFE252010F-100M</t>
-        </is>
+          <t>MB85RC512TYPNF-GS-BCERE1</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>10.19</v>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>v4 - ROUTE L2</t>
+          <t>v4 NEW</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>Murata DFE252010F-100M (10uH, 1.76A) per aem10300.pdf Table 11 / 9.8.2 (&gt;=1A, &gt;=10MHz, low ESR). Schematic footprint set to the KiCad stock 1008/2520 land (Inductor_SMD:L_1008_2520Metric, pads 1.25x2.2mm), the generic land for the 2.5x2.0mm package. Re-run Update-PCB to place it, then route (the earlier upload still had L2 on a 0603 land). Swap to Murata's exact DFE252010F land later if preferred.</t>
+          <t>Price from repo datasheet filename. AEC-Q100.</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>U7  MB85RC512TYPNF-GS-BCERE1  $10.19.pdf</t>
         </is>
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>DFE252010F-100M (Murata; order by MPN, confirm DK P/N at cart)</t>
+          <t>865-MB85RC512TYPNF-GS-BCERE1TR-ND</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="9">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
@@ -2638,49 +2645,49 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Ferrite bead - STO_LDO island filter (isolates U9 LDO input from AEM DCDC ripple)</t>
+          <t>Power inductor - AEM10300 buck-boost DCDC</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>0603 bead</t>
+          <t>10 uH</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>1008/2520 (L_1008_2520Metric), 2.5x2.0 mm</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Murata (rec.)</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>BLM18PG221SN1D</t>
+          <t>DFE252010F-100M</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW - VERIFY</t>
+          <t>v4 - ROUTE L2</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>No project part named; generic 0603 bead recommended (220 ohm @100 MHz). A low-DCR bead is preferable on a power feed - confirm at design review.</t>
+          <t>Murata DFE252010F-100M (10uH, 1.76A) per aem10300.pdf Table 11 / 9.8.2 (&gt;=1A, &gt;=10MHz, low ESR). Schematic footprint set to the KiCad stock 1008/2520 land (Inductor_SMD:L_1008_2520Metric, pads 1.25x2.2mm), the generic land for the 2.5x2.0mm package. Re-run Update-PCB to place it, then route (the earlier upload still had L2 on a 0603 land). Swap to Murata's exact DFE252010F land later if preferred.</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>BLM18PG221SN1D-ND (format-derived - confirm at cart)</t>
+          <t>DFE252010F-100M (Murata; order by MPN, confirm DK P/N at cart)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="23.85" customHeight="1" s="9">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
@@ -2688,49 +2695,49 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>LDO input cap (STO side)</t>
+          <t>Ferrite bead - STO_LDO island filter (isolates U9 LDO input from AEM DCDC ripple)</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>1 uF, 0402, X5R</t>
+          <t>0603 bead</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Murata (rec.)</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A105KE15D</t>
+          <t>BLM18PG221SN1D</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>v4 NEW - VERIFY</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 1uF 0402 part.</t>
+          <t>No project part named; generic 0603 bead recommended (220 ohm @100 MHz). A low-DCR bead is preferable on a power feed - confirm at design review.</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A105KE15D-ND (format-derived - confirm at cart)</t>
+          <t>BLM18PG221SN1D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="9">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
@@ -2738,12 +2745,12 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>LDO output cap (VS rail) - stability</t>
+          <t>LDO input cap (STO side)</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>2.2 µF, 10 V, 0402, X5R</t>
+          <t>1 uF, 0402, X5R</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -2758,7 +2765,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A225KE11D</t>
+          <t>GRM155R61A105KE15D</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2768,19 +2775,19 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>Bumped 1uF -&gt; 2.2uF: TPS7A02 needs &gt;=0.5uF EFFECTIVE for stability; a 1uF 0402 worst-cases at that floor over bias/tol/temp/age. 2.2uF 0402 restores ~2x margin, no rework.</t>
+          <t>Reuses the project 1uF 0402 part.</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A225KE11D-ND (format-derived - confirm at cart)</t>
+          <t>GRM155R61A105KE15D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="9">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
@@ -2788,12 +2795,12 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>STO-sense filter cap (on STO_SNS)</t>
+          <t>LDO output cap (VS rail) - stability</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>100 nF, 0402, X7R</t>
+          <t>2.2 µF, 10 V, 0402, X5R</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -2808,7 +2815,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRM155R61A225KE11D</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -2818,19 +2825,19 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part.</t>
+          <t>Bumped 1uF -&gt; 2.2uF: TPS7A02 needs &gt;=0.5uF EFFECTIVE for stability; a 1uF 0402 worst-cases at that floor over bias/tol/temp/age. 2.2uF 0402 restores ~2x margin, no rework.</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>GRM155R61A225KE11D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="9">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
@@ -2838,17 +2845,17 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>AEM BUFSRC input buffer cap</t>
+          <t>STO-sense filter cap (on STO_SNS)</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>22 uF, 10 V, 0603, X5R</t>
+          <t>100 nF, 0402, X7R</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -2858,7 +2865,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A226ME15D</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -2868,19 +2875,19 @@
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard.</t>
+          <t>Reuses the project 100 nF 0402 part.</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A226ME15D-ND (format-derived - confirm at cart)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="9">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
@@ -2888,27 +2895,27 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>AEM VINT buffer cap</t>
+          <t>AEM BUFSRC input buffer cap</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>10 uF, 0402, X5R</t>
+          <t>22 uF, 10 V, 0603, X5R</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Murata (rec.)</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>GRM155R60J106ME44D</t>
+          <t>GRM188R61A226ME15D</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -2918,19 +2925,19 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>AEM CINT (datasheet Table 11: 10uF 6.3V 0402; ME44D is the current-production equivalent). VINT ~2.2V, so 6.3V rating is fine.</t>
+          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard.</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>GRM155R60J106ME44D-ND (format-derived - confirm at cart)</t>
+          <t>GRM188R61A226ME15D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="9">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
@@ -2938,49 +2945,49 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>STO local HF decoupling</t>
+          <t>AEM VINT buffer cap</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>10 µF, 10 V, 0603, X5R</t>
+          <t>10 uF, 0402, X5R</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Murata (rec.)</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D</t>
+          <t>GRM155R60J106ME44D</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>LAND REWORK</t>
+          <t>v4 NEW</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>Moved to 0603 to keep 10uF at 10V (per request; matches C25's approach). STO rides to 4.65V where a 6.3V 0402 was thin + heavily derated; 10V 0603 gives full margin and effective bulk. Shares the C4/C13 10uF 10V 0603 reel. Land grows from 0402 - PCB rework.</t>
+          <t>AEM CINT (datasheet Table 11: 10uF 6.3V 0402; ME44D is the current-production equivalent). VINT ~2.2V, so 6.3V rating is fine.</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
+          <t>GRM155R60J106ME44D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="9">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
@@ -2988,17 +2995,17 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>FRAM VNFC decoupling</t>
+          <t>STO local HF decoupling</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>100 nF, 0402, X7R</t>
+          <t>10 µF, 10 V, 0603, X5R</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -3008,29 +3015,29 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRM188R61A106KE69D</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>LAND REWORK</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part.</t>
+          <t>Moved to 0603 to keep 10uF at 10V (per request; matches C25's approach). STO rides to 4.65V where a 6.3V 0402 was thin + heavily derated; 10V 0603 gives full margin and effective bulk. Shares the C4/C13 10uF 10V 0603 reel. Land grows from 0402 - PCB rework.</t>
         </is>
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="9">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
@@ -3038,12 +3045,12 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
+          <t>FRAM VNFC decoupling</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>2 M, 0402, 1%</t>
+          <t>100 nF, 0402, X7R</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -3053,12 +3060,12 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-072ML</t>
+          <t>GRM155R71C104KA88D</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
@@ -3068,32 +3075,32 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart.</t>
+          <t>Reuses the project 100 nF 0402 part.</t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-072ML-ND (format-derived - confirm at cart)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="9">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>R16, R17</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>STO sense divider bottom (R16) + EN_STO_CH pull-up to VINT (R17)</t>
+          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>1 M, 0402, 1%</t>
+          <t>2 M, 0402, 1%</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -3108,7 +3115,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML</t>
+          <t>RC0402FR-072ML</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -3118,97 +3125,86 @@
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 1 M part (shared with R5/R6/R14).</t>
+          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart.</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
+          <t>RC0402FR-072ML-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="9">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>R16, R17</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
+          <t>STO sense divider bottom (R16) + EN_STO_CH pull-up to VINT (R17)</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>1 M, 0402, 1%</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>RC0402FR-071ML</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>v4 NEW</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>Reuses the project 1 M part (shared with R5/R6/R14).</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="9">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>PRG1</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="n">
-        <v>1</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Adafruit UPDI Friend</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>26.4×17.8 mm board + JST-SH lead</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="I49" s="8" t="n">
-        <v>6.95</v>
+          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
+        </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
-        </is>
-      </c>
-      <c r="K49" s="8" t="inlineStr">
-        <is>
-          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
-        </is>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
-        <is>
-          <t>(guide linked in firmware/README)</t>
-        </is>
-      </c>
-      <c r="M49" s="8" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>CBL1</t>
+          <t>PRG1</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
@@ -3216,28 +3212,34 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
+          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>TC2030-MCP (legged, RJ12 end)</t>
+          <t>Adafruit UPDI Friend</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>6-ft cable, 6P6C modular plug</t>
+          <t>26.4×17.8 mm board + JST-SH lead</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>TC2030-MCP</t>
-        </is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>6.95</v>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
@@ -3246,52 +3248,52 @@
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
+          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
+          <t>(guide linked in firmware/README)</t>
         </is>
       </c>
       <c r="M50" s="8" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="360.4" customHeight="1" s="9">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>HW1</t>
+          <t>CBL1</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
+          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
+          <t>TC2030-MCP (legged, RJ12 end)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>head ⌀3.8 × 1.4 mm</t>
+          <t>6-ft cable, 6P6C modular plug</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>DIN 84 M2×3 brass</t>
+          <t>TC2030-MCP</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -3301,52 +3303,52 @@
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
+          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>docs/screw-m2x3-cheese.png</t>
+          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>ENC1</t>
+          <t>HW1</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V, 3.55 mm stack</t>
+          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>CNC from enclosure/ STEP</t>
+          <t>head ⌀3.8 × 1.4 mm</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>(PCBWay CNC or equiv.)</t>
+          <t>(generic)</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>(order from enclosure/*.step)</t>
+          <t>DIN 84 M2×3 brass</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -3356,12 +3358,12 @@
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>enclosure/README.md</t>
+          <t>docs/screw-m2x3-cheese.png</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
@@ -3373,7 +3375,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>INS1</t>
+          <t>ENC1</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
@@ -3381,42 +3383,42 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>~0.05 mm polyimide, die-cut to board outline</t>
+          <t>Ti-6Al-4V, 3.55 mm stack</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>sheet / die-cut</t>
+          <t>CNC from enclosure/ STEP</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>(PCBWay CNC or equiv.)</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>(polyimide film, 0.05 mm)</t>
+          <t>(order from enclosure/*.step)</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>AUX-OPTIONAL</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>enclosure/README.md</t>
         </is>
       </c>
       <c r="M53" s="8" t="inlineStr">
@@ -3428,82 +3430,137 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
+          <t>INS1</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>~0.05 mm polyimide, die-cut to board outline</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>sheet / die-cut</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>(generic)</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>(polyimide film, 0.05 mm)</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>AUX-OPTIONAL</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
           <t>FER1</t>
         </is>
       </c>
-      <c r="B54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="B55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>Würth Elektronik</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>364006</t>
         </is>
       </c>
-      <c r="H54" s="8" t="n">
+      <c r="H55" s="8" t="n">
         <v>17.43</v>
       </c>
-      <c r="I54" s="8" t="n">
+      <c r="I55" s="8" t="n">
         <v>17.43</v>
       </c>
-      <c r="J54" s="8" t="inlineStr">
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
         </is>
       </c>
-      <c r="K54" s="8" t="inlineStr">
+      <c r="K55" s="8" t="inlineStr">
         <is>
           <t>FINAL, verified 2026-07-03: DK 732-5049-ND, Active, tray, $17.43 @ 1 (51 in stock at verification; 24-wk mfr lead — buy with the order). 60×60 mm sheet, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA); one sheet = 4 patches. Cut 12.2 × 25.8 mm on the 2 mm score grid; brace channel depth = measured stack − 0.05 (sits ~0.05 proud, seats flush; PET face to the board, PSA into the brace). Stock-dry fallback: 3× stacked 3641014 (732-13935-ND, $4.19 ea, µ′150/µ″3 @ 13.56 MHz, 0.14 mm ea) ≈ same ferrite thickness; last resort Laird MHLL6060-300 (240-2791-ND, 0.09 mm, weakest). All three datasheets in repo.</t>
         </is>
       </c>
-      <c r="L54" s="8" t="inlineStr">
+      <c r="L55" s="8" t="inlineStr">
         <is>
           <t>FER1  Wurth WE-FSFS 364006  $17.43.pdf + FER1-alt  Wurth WE-FSFS 3641014  $4.19.pdf + FER1-alt  Laird MHLL6060-300  $6.40.pdf (repo)</t>
         </is>
       </c>
-      <c r="M54" s="8" t="inlineStr">
+      <c r="M55" s="8" t="inlineStr">
         <is>
           <t>732-5049-ND</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="G55" s="8" t="inlineStr">
+    <row r="56">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
         </is>
       </c>
-      <c r="I55" s="8" t="n">
+      <c r="I56" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="K55" s="8" t="inlineStr">
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>Sum of the 30 priced Ext$ cells only — several converted lines remain unpriced pending quotes; see footnote.</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).</t>
         </is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -647,8 +647,12 @@
           <t>3-153-440</t>
         </is>
       </c>
-      <c r="H4" s="14" t="n"/>
-      <c r="I4" s="14" t="n"/>
+      <c r="H4" s="14" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>34.32</v>
+      </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -656,7 +660,7 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>DOMINANT COST (with the WS17 pair). Larger 1.8 F SS17 can; CONFIRM LIVE PRICE (pricier than the WS17). Solder to under-body flat pads (asymmetric P/N widths = polarity key), NOT end tabs. Hybrid: bigger cans placed where the board has room. Same SCPC family sheet as the WS17.</t>
+          <t>DOMINANT COST (with the WS17 pair). Larger 1.8 F SS17 can. DK live-verified 2026-07-22: 486-3-153-440-ND, Active, $17.16 @ 1 (200 in stock; breaks 10@$13.48, 50@$12.01, 100@$11.55) - pricier than the WS17, as expected. Solder to under-body flat pads (asymmetric P/N widths = polarity key), NOT end tabs. Hybrid: bigger cans placed where the board has room. Same SCPC family sheet as the WS17.</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
@@ -666,7 +670,7 @@
       </c>
       <c r="M4" s="11" t="inlineStr">
         <is>
-          <t>(SCPC family sheet; order 3-153-440 by MPN, confirm price)</t>
+          <t>486-3-153-440-ND</t>
         </is>
       </c>
     </row>
@@ -705,10 +709,10 @@
         </is>
       </c>
       <c r="H5" s="14" t="n">
-        <v>15.48</v>
+        <v>16.69</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>30.96</v>
+        <v>33.38</v>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
@@ -717,7 +721,7 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>DOMINANT COST. Solder to under-body flat pads (asymmetric P/N widths = polarity key), NOT end tabs. DK product page verified 2026-07-02 (1 F, 2.75 V, SCPC). Order by MPN.</t>
+          <t>DOMINANT COST. Solder to under-body flat pads (asymmetric P/N widths = polarity key), NOT end tabs. DK live-verified 2026-07-22: 486-3-153-438-ND, $16.69 @ 1 (195 in stock; breaks 10@$13.08, 100@$11.20) - up from $15.48 @ 2026-07-02. Order by MPN.</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
@@ -727,7 +731,7 @@
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>(DK page verified; order by MPN)</t>
+          <t>486-3-153-438-ND</t>
         </is>
       </c>
     </row>
@@ -3550,19 +3554,18 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>Sum of the 30 priced Ext$ cells only — several converted lines remain unpriced pending quotes; see footnote.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
+          <t>Sum of the 30 priced Ext$ cells only - several converted lines remain unpriced pending quotes (and U8/AEM10300 pending a Mouser quote); see footnote.</t>
+        </is>
+      </c>
+    </row>
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).</t>
+          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22.</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="H3" s="14" t="n">
-        <v>6.98</v>
+        <v>7.61</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>13.96</v>
+        <v>15.22</v>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>TF = the 1.2 mm 'thin' variant; electrically identical to the 1.8 mm SM141K06L. Same 42×23 land. DK verified 2026-07-02. TF = Gen3 Thin: ANYSOLAR PCN ASL2022-001 maps SM141K06L (Standard) -&gt; SM141K06TF (Thin) - the citation for the pending sch value fix.</t>
+          <t>TF = the 1.2 mm 'thin' variant; electrically identical to the 1.8 mm SM141K06L. Same 42×23 land. DK verified 2026-07-02. TF = Gen3 Thin: ANYSOLAR PCN ASL2022-001 maps SM141K06L (Standard) -&gt; SM141K06TF (Thin) - the citation for the pending sch value fix. DK live-verified 2026-07-22: 2994-SM141K06TF-ND, Active, $7.61 @1 (was $6.98 @2026-07-02).</t>
         </is>
       </c>
       <c r="L3" s="11" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>Package corrected to 0402 to match the placed land (BOM previously listed 1206; a 1206 part will not fit). 1/16 W is ample (~12 mW peak/LED). Value still SIZED for the clamped ~3.47 V rail (~9 mA/LED peak); re-tune after the energy-budget bench test. Any 0402 150 Ω 1% equivalent works (esp. for PCBA sourcing).</t>
+          <t>Package corrected to 0402 to match the placed land (BOM previously listed 1206; a 1206 part will not fit). 1/16 W is ample (~12 mW peak/LED). Value still SIZED for the clamped ~3.47 V rail (~9 mA/LED peak); re-tune after the energy-budget bench test. Any 0402 150 Ω 1% equivalent works (esp. for PCBA sourcing). DK live-verified 2026-07-22: 311-150LRCT-ND, Active, $0.10 @1 (DKPN corrected from format-derived guess).</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07150RL-ND (format-derived — confirm at cart)</t>
+          <t>311-150LRCT-ND</t>
         </is>
       </c>
     </row>
@@ -891,8 +891,12 @@
           <t>RC0402FR-07220RL</t>
         </is>
       </c>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
+      <c r="H8" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -900,7 +904,7 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>Sets the SW2 TINY dim level; tunable. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Sets the SW2 TINY dim level; tunable. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-220LRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
@@ -910,7 +914,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07220RL-ND (format-derived — confirm at cart)</t>
+          <t>311-220LRCT-ND</t>
         </is>
       </c>
     </row>
@@ -948,8 +952,12 @@
           <t>RC0402FR-071ML</t>
         </is>
       </c>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="H9" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -957,7 +965,7 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>R5=R6 → VSENSE = VIN/2 (tracks light, ~0 V dark). Feeds ADC + the AC0 wake-on-light comparator. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>R5=R6 → VSENSE = VIN/2 (tracks light, ~0 V dark). Feeds ADC + the AC0 wake-on-light comparator. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -967,7 +975,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML-ND (format-derived — confirm at cart)</t>
+          <t>311-1.00MLRCT-ND</t>
         </is>
       </c>
     </row>
@@ -1005,8 +1013,12 @@
           <t>GRM155R71C104KA88D</t>
         </is>
       </c>
-      <c r="H10" s="14" t="n"/>
-      <c r="I10" s="14" t="n"/>
+      <c r="H10" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1014,7 +1026,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC] [consolidation: 10nF -&gt; 100nF, joins the 100 nF group]</t>
+          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC] [consolidation: 10nF -&gt; 100nF, joins the 100 nF group] DK live-verified 2026-07-22: DKPN corrected from GRM155R71C103KA01D-ND (a 10nF part, stale from the 10nF-&gt;100nF consolidation) to 490-3261-1-ND (100nF, matches the KA88D MPN). Active, $0.10 @1.</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
@@ -1024,7 +1036,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C103KA01D-ND (format-derived — confirm at cart)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
@@ -1063,10 +1075,10 @@
         </is>
       </c>
       <c r="H11" s="14" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
@@ -1075,7 +1087,7 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>SCLK→GND (I²C); ASEL (pin 3)→GND ⇒ addr 0x1D. FOOTPRINT = ADI CC-12-4 land fitted (KiCad ADXL367 CC-12-4_ADI); verified vs datasheet Fig 64 (2.11×2.21 mm envelope, 0.5 mm pitch).</t>
+          <t>SCLK→GND (I²C); ASEL (pin 3)→GND ⇒ addr 0x1D. FOOTPRINT = ADI CC-12-4 land fitted (KiCad ADXL367 CC-12-4_ADI); verified vs datasheet Fig 64 (2.11×2.21 mm envelope, 0.5 mm pitch). DK live-verified 2026-07-22: 505-ADXL367BCCZ-RL7CT-ND, Active, $7.80 @1 (was $7.50).</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -1085,7 +1097,7 @@
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>505-ADXL367BCCZ-RL7CT-ND</t>
         </is>
       </c>
     </row>
@@ -1123,8 +1135,12 @@
           <t>RC0402FR-074K7L</t>
         </is>
       </c>
-      <c r="H12" s="14" t="n"/>
-      <c r="I12" s="14" t="n"/>
+      <c r="H12" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1132,7 +1148,7 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>Required — open-drain TWI bus. Firmware must set TWIROUTEA = ALT2. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Required — open-drain TWI bus. Firmware must set TWIROUTEA = ALT2. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-4.7KLRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
@@ -1142,7 +1158,7 @@
       </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-074K7L-ND (format-derived — confirm at cart)</t>
+          <t>311-4.7KLRCT-ND</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1327,7 @@
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603 for more effective VS bulk (stiffer rail under glow / NFC-inrush / accel transients). 0603 land - PCB rework.</t>
+          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603 for more effective VS bulk (stiffer rail under glow / NFC-inrush / accel transients). 0603 land - PCB rework. DK live-verified 2026-07-22: 490-10474-1-ND, Active, but DK API returned no qty-1 standard price (non-stock/order item); ~$0.15 class - confirm at cart.</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
@@ -1321,7 +1337,7 @@
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
+          <t>490-10474-1-ND</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1449,7 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>ADXL367 pin 9 VREG_OUT1 → GND. Datasheet-mandated 0.2 µF; 0.22 µF nearest std.</t>
+          <t>ADXL367 pin 9 VREG_OUT1 → GND. Datasheet-mandated 0.2 µF; 0.22 µF nearest std. DK live-verified 2026-07-22: 490-5418-1-ND, Active, $0.10 @1 (DKPN filled).</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
@@ -1443,7 +1459,7 @@
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>490-5418-1-ND</t>
         </is>
       </c>
     </row>
@@ -1604,17 +1620,21 @@
         </is>
       </c>
       <c r="H20" s="14" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K20" s="13" t="n"/>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>DK live-verified 2026-07-22: 311-0.0ARCT-ND, Active, $0.10 @1 (was $0.05; DKPN corrected).</t>
+        </is>
+      </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
           <t>—</t>
@@ -1622,7 +1642,7 @@
       </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
-          <t>RC0805JR-070RL-ND (format-derived — confirm at cart)</t>
+          <t>311-0.0ARCT-ND</t>
         </is>
       </c>
     </row>
@@ -2088,10 +2108,10 @@
         </is>
       </c>
       <c r="H28" s="14" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
@@ -2100,7 +2120,7 @@
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x1D). VCC→VS; VOUT pin 7 unconnected. Confirm live price. DK page verified 2026-07-02 (XFQFN8 exposed pad, $1.38 @ 1); Mouser cross: 771-NT3H2211W0FHKH, 9k stock.</t>
+          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x1D). VCC→VS; VOUT pin 7 unconnected. Confirm live price. DK page verified 2026-07-02 (XFQFN8 exposed pad, $1.38 @ 1); Mouser cross: 771-NT3H2211W0FHKH, 9k stock. DK live-verified 2026-07-22: 568-12901-1-ND, Active, $1.56 @1 (was $1.38).</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
@@ -2110,7 +2130,7 @@
       </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>568-12901-1-ND</t>
         </is>
       </c>
     </row>
@@ -2279,13 +2299,13 @@
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603; keeps the glow-PWM transient off the shared VS rail. 0603 land - PCB rework.</t>
+          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603; keeps the glow-PWM transient off the shared VS rail. 0603 land - PCB rework. DK live-verified 2026-07-22: 490-10474-1-ND, Active, but DK API returned no qty-1 standard price (non-stock/order item); ~$0.15 class - confirm at cart.</t>
         </is>
       </c>
       <c r="L31" s="11" t="n"/>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
+          <t>490-10474-1-ND</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2417,7 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/U6  TPS22918DBVR  $0.55.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off.</t>
+          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/U6  TPS22918DBVR  $0.55.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off. DK live-verified 2026-07-22: 296-46278-1-ND, Active, $0.55 @1 (DKPN filled).</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -2407,7 +2427,7 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>296-46278-1-ND</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2478,7 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition, placed with the R14 board patch. Consolidated 100 kΩ -&gt; 1 MΩ (joins the R5/R6/R16/R17 reel, RC0402FR-071ML).</t>
+          <t>v3.0 addition, placed with the R14 board patch. Consolidated 100 kΩ -&gt; 1 MΩ (joins the R5/R6/R16/R17 reel, RC0402FR-071ML). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
@@ -2468,7 +2488,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
+          <t>311-1.00MLRCT-ND</t>
         </is>
       </c>
     </row>
@@ -2561,6 +2581,12 @@
           <t>TPS7A0233PDBVR</t>
         </is>
       </c>
+      <c r="H36" s="8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>0.84</v>
+      </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
@@ -2568,12 +2594,12 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>Verified active on DigiKey (product 12165099): TPS7A0233PDBVR, SOT-23-5, 200 mA nanopower LDO (TI TPS7A02 family, ~25 nA Iq). No repo datasheet.</t>
+          <t>Verified active on DigiKey (product 12165099): TPS7A0233PDBVR, SOT-23-5, 200 mA nanopower LDO (TI TPS7A02 family, ~25 nA Iq). No repo datasheet. DK live-verified 2026-07-22: 296-TPS7A0233PDBVRCT-ND (DK 12165099), Active, $0.84 @1.</t>
         </is>
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>296-TPS7A0233PDBVRCT-ND (DK 12165099, active; confirm CT/reel at cart)</t>
+          <t>296-TPS7A0233PDBVRCT-ND</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2650,7 @@
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>Price from repo datasheet filename. AEC-Q100.</t>
+          <t>Price from repo datasheet filename. AEC-Q100. DK live-verified 2026-07-22: 865-MB85RC512TYPNF-GS-BCERE1CT-ND, Active, $10.19 @1 (CT variation of the TR P/N).</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
@@ -2634,7 +2660,7 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>865-MB85RC512TYPNF-GS-BCERE1TR-ND</t>
+          <t>865-MB85RC512TYPNF-GS-BCERE1CT-ND</t>
         </is>
       </c>
     </row>
@@ -2672,6 +2698,12 @@
           <t>DFE252010F-100M</t>
         </is>
       </c>
+      <c r="H38" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
           <t>v4 - ROUTE L2</t>
@@ -2679,12 +2711,12 @@
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>Murata DFE252010F-100M (10uH, 1.76A) per aem10300.pdf Table 11 / 9.8.2 (&gt;=1A, &gt;=10MHz, low ESR). Schematic footprint set to the KiCad stock 1008/2520 land (Inductor_SMD:L_1008_2520Metric, pads 1.25x2.2mm), the generic land for the 2.5x2.0mm package. Re-run Update-PCB to place it, then route (the earlier upload still had L2 on a 0603 land). Swap to Murata's exact DFE252010F land later if preferred.</t>
+          <t>Murata DFE252010F-100M (10uH, 1.76A) per aem10300.pdf Table 11 / 9.8.2 (&gt;=1A, &gt;=10MHz, low ESR). Schematic footprint set to the KiCad stock 1008/2520 land (Inductor_SMD:L_1008_2520Metric, pads 1.25x2.2mm), the generic land for the 2.5x2.0mm package. Re-run Update-PCB to place it, then route (the earlier upload still had L2 on a 0603 land). Swap to Murata's exact DFE252010F land later if preferred. DK live-verified 2026-07-22: DK orderable MPN is DFE252010F-100M=P2 -&gt; 490-13039-1-ND, Active, $0.25 @1 (CT).</t>
         </is>
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>DFE252010F-100M (Murata; order by MPN, confirm DK P/N at cart)</t>
+          <t>490-13039-1-ND</t>
         </is>
       </c>
     </row>
@@ -2722,19 +2754,25 @@
           <t>BLM18PG221SN1D</t>
         </is>
       </c>
+      <c r="H39" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW - VERIFY</t>
+          <t>v4 NEW</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>No project part named; generic 0603 bead recommended (220 ohm @100 MHz). A low-DCR bead is preferable on a power feed - confirm at design review.</t>
+          <t>No project part named; generic 0603 bead recommended (220 ohm @100 MHz). A low-DCR bead is preferable on a power feed - confirm at design review. DK live-verified 2026-07-22: 490-5221-1-ND, Active, $0.10 @1 (verified; DKPN corrected).</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>BLM18PG221SN1D-ND (format-derived - confirm at cart)</t>
+          <t>490-5221-1-ND</t>
         </is>
       </c>
     </row>
@@ -2774,17 +2812,17 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>RE-SOURCE</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 1uF 0402 part.</t>
+          <t>Reuses the project 1uF 0402 part. DK live-verified 2026-07-22: MPN GRM155R61A105KE15D is OBSOLETE at DK, and the whole Murata GRM155 1uF 10V 0402 X5R family is EOL (no active sibling). C22 is the U9 LDO input cap on the STO island (node ~5.5V) so it needs an ACTIVE 1uF 0402 X5R rated &gt;=10V - re-source from another series/vendor (e.g. a 16V/25V 1uF 0402 X5R, or TDK/Samsung). Price/DKPN pending that pick.</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A105KE15D-ND (format-derived - confirm at cart)</t>
+          <t>(OBSOLETE at DK - re-source; see note)</t>
         </is>
       </c>
     </row>
@@ -2822,19 +2860,25 @@
           <t>GRM155R61A225KE11D</t>
         </is>
       </c>
+      <c r="H41" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>RE-SOURCE</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>Bumped 1uF -&gt; 2.2uF: TPS7A02 needs &gt;=0.5uF EFFECTIVE for stability; a 1uF 0402 worst-cases at that floor over bias/tol/temp/age. 2.2uF 0402 restores ~2x margin, no rework.</t>
+          <t>Bumped 1uF -&gt; 2.2uF: TPS7A02 needs &gt;=0.5uF EFFECTIVE for stability; a 1uF 0402 worst-cases at that floor over bias/tol/temp/age. 2.2uF 0402 restores ~2x margin, no rework. DK live-verified 2026-07-22: MPN GRM155R61A225KE11D returns NO results at DK. Same-spec ACTIVE drop-in = GRM155R61A225KE01J (2.2uF 10V X5R 0402), 490-GRM155R61A225KE01JCT-ND, $0.10 @1, 38k in stock. C23 = U9 LDO output on VS (3.3V), so 10V rating is fine. SUGGESTED SUB - bless the MPN swap before order.</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A225KE11D-ND (format-derived - confirm at cart)</t>
+          <t>490-GRM155R61A225KE01JCT-ND</t>
         </is>
       </c>
     </row>
@@ -2872,6 +2916,12 @@
           <t>GRM155R71C104KA88D</t>
         </is>
       </c>
+      <c r="H42" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
@@ -2879,7 +2929,7 @@
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part.</t>
+          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
@@ -2922,6 +2972,12 @@
           <t>GRM188R61A226ME15D</t>
         </is>
       </c>
+      <c r="H43" s="8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0.16</v>
+      </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
@@ -2929,12 +2985,12 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard.</t>
+          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard. DK live-verified 2026-07-22: 490-10476-1-ND, Active, $0.16 @1 (DKPN + price filled).</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A226ME15D-ND (format-derived - confirm at cart)</t>
+          <t>490-10476-1-ND</t>
         </is>
       </c>
     </row>
@@ -2972,19 +3028,25 @@
           <t>GRM155R60J106ME44D</t>
         </is>
       </c>
+      <c r="H44" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>RE-SOURCE</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>AEM CINT (datasheet Table 11: 10uF 6.3V 0402; ME44D is the current-production equivalent). VINT ~2.2V, so 6.3V rating is fine.</t>
+          <t>AEM CINT (datasheet Table 11: 10uF 6.3V 0402; ME44D is the current-production equivalent). VINT ~2.2V, so 6.3V rating is fine. DK live-verified 2026-07-22: MPN GRM155R60J106ME44D is DISCONTINUED at DK. Same-spec ACTIVE drop-in = GRM155R60J106ME05D (10uF 6.3V X5R 0402), 490-GRM155R60J106ME05DCT-ND, $0.10 @1, 1.2M in stock. C26 = VINT buffer (6.3V intent preserved). SUGGESTED SUB - bless the MPN swap before order.</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>GRM155R60J106ME44D-ND (format-derived - confirm at cart)</t>
+          <t>490-GRM155R60J106ME05DCT-ND</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3091,12 @@
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>Moved to 0603 to keep 10uF at 10V (per request; matches C25's approach). STO rides to 4.65V where a 6.3V 0402 was thin + heavily derated; 10V 0603 gives full margin and effective bulk. Shares the C4/C13 10uF 10V 0603 reel. Land grows from 0402 - PCB rework.</t>
+          <t>Moved to 0603 to keep 10uF at 10V (per request; matches C25's approach). STO rides to 4.65V where a 6.3V 0402 was thin + heavily derated; 10V 0603 gives full margin and effective bulk. Shares the C4/C13 10uF 10V 0603 reel. Land grows from 0402 - PCB rework. DK live-verified 2026-07-22: 490-10474-1-ND, Active, but DK API returned no qty-1 standard price (non-stock/order item); ~$0.15 class - confirm at cart.</t>
         </is>
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D-ND (format-derived - confirm at cart)</t>
+          <t>490-10474-1-ND</t>
         </is>
       </c>
     </row>
@@ -3072,6 +3134,12 @@
           <t>GRM155R71C104KA88D</t>
         </is>
       </c>
+      <c r="H46" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
@@ -3079,7 +3147,7 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part.</t>
+          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.</t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr">
@@ -3122,6 +3190,12 @@
           <t>RC0402FR-072ML</t>
         </is>
       </c>
+      <c r="H47" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
@@ -3129,12 +3203,12 @@
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart.</t>
+          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart. DK live-verified 2026-07-22: 13-RC0402FR-072MLCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-072ML-ND (format-derived - confirm at cart)</t>
+          <t>13-RC0402FR-072MLCT-ND</t>
         </is>
       </c>
     </row>
@@ -3172,6 +3246,12 @@
           <t>RC0402FR-071ML</t>
         </is>
       </c>
+      <c r="H48" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
@@ -3179,12 +3259,12 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 1 M part (shared with R5/R6/R14).</t>
+          <t>Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML-ND (format-derived - confirm at cart)</t>
+          <t>311-1.00MLRCT-ND</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3387,7 @@
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
+          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback. DK live-verified 2026-07-22: DK TC2030-MCPTC-ND, Active, $36.00 @1 (AUX bench cable, one-time; not a per-board cost).</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
@@ -3554,18 +3634,18 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>130</v>
+        <v>134.44</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>Sum of the 30 priced Ext$ cells only - several converted lines remain unpriced pending quotes (and U8/AEM10300 pending a Mouser quote); see footnote.</t>
+          <t>Sum of the 44 priced Ext$ cells only - several lines remain unpriced (C4/C13/C27 10uF 0603 no DK price; C22 obsolete; U8/AEM10300 Mouser-pending). C23/C26 use suggested-sub pricing. See footnote.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22.</t>
+          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>1 uF, 0402, X5R</t>
+          <t>1 uF, 25 V, 0402, X5R</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -2807,22 +2807,28 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A105KE15D</t>
-        </is>
+          <t>GRM155R61E105MA12D</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>RE-SOURCE</t>
+          <t>v4 NEW</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 1uF 0402 part. DK live-verified 2026-07-22: MPN GRM155R61A105KE15D is OBSOLETE at DK, and the whole Murata GRM155 1uF 10V 0402 X5R family is EOL (no active sibling). C22 is the U9 LDO input cap on the STO island (node ~5.5V) so it needs an ACTIVE 1uF 0402 X5R rated &gt;=10V - re-source from another series/vendor (e.g. a 16V/25V 1uF 0402 X5R, or TDK/Samsung). Price/DKPN pending that pick.</t>
+          <t>v4 LDO input cap on the STO island (~5.5 V). Original GRM155R61A105KE15D (1 uF 10 V) is obsolete and the whole Murata GRM155 1 uF 10 V 0402 X5R family is EOL. RE-SOURCED 2026-07-22 -&gt; GRM155R61E105MA12D (1 uF 25 V X5R 0402), DK 490-10018-1-ND, Active, $0.10 @1, 461k in stock. 25 V chosen for DC-bias headroom on the ~5.5 V node. Schematic MPN updated to match.</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>(OBSOLETE at DK - re-source; see note)</t>
+          <t>490-10018-1-ND</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2863,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A225KE11D</t>
+          <t>GRM155R61A225KE01J</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
@@ -2868,12 +2874,12 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>RE-SOURCE</t>
+          <t>v4 NEW</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>Bumped 1uF -&gt; 2.2uF: TPS7A02 needs &gt;=0.5uF EFFECTIVE for stability; a 1uF 0402 worst-cases at that floor over bias/tol/temp/age. 2.2uF 0402 restores ~2x margin, no rework. DK live-verified 2026-07-22: MPN GRM155R61A225KE11D returns NO results at DK. Same-spec ACTIVE drop-in = GRM155R61A225KE01J (2.2uF 10V X5R 0402), 490-GRM155R61A225KE01JCT-ND, $0.10 @1, 38k in stock. C23 = U9 LDO output on VS (3.3V), so 10V rating is fine. SUGGESTED SUB - bless the MPN swap before order.</t>
+          <t>v4 LDO output cap on VS (3.3 V). Original GRM155R61A225KE11D returned no DK results. RE-SOURCED 2026-07-22 -&gt; GRM155R61A225KE01J (2.2 uF 10 V X5R 0402, same spec), DK 490-GRM155R61A225KE01JCT-ND, Active, $0.10 @1, 38k in stock. Schematic MPN updated to match.</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
@@ -3025,7 +3031,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>GRM155R60J106ME44D</t>
+          <t>GRM155R60J106ME05D</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
@@ -3036,12 +3042,12 @@
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>RE-SOURCE</t>
+          <t>v4 NEW</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>AEM CINT (datasheet Table 11: 10uF 6.3V 0402; ME44D is the current-production equivalent). VINT ~2.2V, so 6.3V rating is fine. DK live-verified 2026-07-22: MPN GRM155R60J106ME44D is DISCONTINUED at DK. Same-spec ACTIVE drop-in = GRM155R60J106ME05D (10uF 6.3V X5R 0402), 490-GRM155R60J106ME05DCT-ND, $0.10 @1, 1.2M in stock. C26 = VINT buffer (6.3V intent preserved). SUGGESTED SUB - bless the MPN swap before order.</t>
+          <t>v4 AEM VINT buffer cap (6.3 V rail). Original GRM155R60J106ME44D discontinued at DK. RE-SOURCED 2026-07-22 -&gt; GRM155R60J106ME05D (10 uF 6.3 V X5R 0402, same spec), DK 490-GRM155R60J106ME05DCT-ND, Active, $0.10 @1, 1.2M in stock. Schematic MPN updated to match.</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
@@ -3634,11 +3640,11 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>134.44</v>
+        <v>134.54</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>Sum of the 44 priced Ext$ cells only - several lines remain unpriced (C4/C13/C27 10uF 0603 no DK price; C22 obsolete; U8/AEM10300 Mouser-pending). C23/C26 use suggested-sub pricing. See footnote.</t>
+          <t>Sum of the 45 priced Ext$ cells only - a few lines remain unpriced (C4/C13/C27 10uF 0603 no DK price; U8/AEM10300 Mouser-pending). See footnote.</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -1315,11 +1315,15 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="n"/>
-      <c r="I15" s="14" t="n"/>
+          <t>GRM188R61A106ME69D</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>0.12</v>
+      </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
           <t>LAND REWORK</t>
@@ -1327,7 +1331,7 @@
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603 for more effective VS bulk (stiffer rail under glow / NFC-inrush / accel transients). 0603 land - PCB rework. DK live-verified 2026-07-22: 490-10474-1-ND, Active, but DK API returned no qty-1 standard price (non-stock/order item); ~$0.15 class - confirm at cart.</t>
+          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
@@ -1337,7 +1341,7 @@
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>490-10474-1-ND</t>
+          <t>490-10475-1-ND</t>
         </is>
       </c>
     </row>
@@ -2287,11 +2291,15 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="n"/>
+          <t>GRM188R61A106ME69D</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>0.12</v>
+      </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
           <t>LAND REWORK</t>
@@ -2299,13 +2307,13 @@
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Bumped 4.7uF 0402 -&gt; 10uF 10V 0603; keeps the glow-PWM transient off the shared VS rail. 0603 land - PCB rework. DK live-verified 2026-07-22: 490-10474-1-ND, Active, but DK API returned no qty-1 standard price (non-stock/order item); ~$0.15 class - confirm at cart.</t>
+          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)</t>
         </is>
       </c>
       <c r="L31" s="11" t="n"/>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>490-10474-1-ND</t>
+          <t>490-10475-1-ND</t>
         </is>
       </c>
     </row>
@@ -2810,10 +2818,10 @@
           <t>GRM155R61E105MA12D</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="H40" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I40" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -3087,8 +3095,14 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A106KE69D</t>
-        </is>
+          <t>GRM188R61A106ME69D</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.12</v>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
@@ -3097,12 +3111,12 @@
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>Moved to 0603 to keep 10uF at 10V (per request; matches C25's approach). STO rides to 4.65V where a 6.3V 0402 was thin + heavily derated; 10V 0603 gives full margin and effective bulk. Shares the C4/C13 10uF 10V 0603 reel. Land grows from 0402 - PCB rework. DK live-verified 2026-07-22: 490-10474-1-ND, Active, but DK API returned no qty-1 standard price (non-stock/order item); ~$0.15 class - confirm at cart.</t>
+          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)</t>
         </is>
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>490-10474-1-ND</t>
+          <t>490-10475-1-ND</t>
         </is>
       </c>
     </row>
@@ -3640,11 +3654,11 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>134.54</v>
+        <v>134.9</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>Sum of the 45 priced Ext$ cells only - a few lines remain unpriced (C4/C13/C27 10uF 0603 no DK price; U8/AEM10300 Mouser-pending). See footnote.</t>
+          <t>Sum of the 48 priced Ext$ cells only - the only remaining unpriced ordered line is U8/AEM10300 (Mouser-pending). See footnote.</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2534,6 +2534,12 @@
           <t>10AEM10300C0000</t>
         </is>
       </c>
+      <c r="H35" s="8" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>3.77</v>
+      </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
@@ -2541,7 +2547,7 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>Datasheet-confirmed orderable P/N (aem10300.pdf p1). Specialty long-lead part - order early. SOURCING: MOUSER only - this is the one non-DigiKey line (e-peas is not a DigiKey vendor); Mouser carries the AEM10300 line (verified 2026-07). Order by MPN 10AEM10300C0000.</t>
+          <t>Datasheet-confirmed orderable P/N (aem10300.pdf p1). Specialty long-lead part - order early. SOURCING: MOUSER only - this is the one non-DigiKey line (e-peas is not a DigiKey vendor); Mouser carries the AEM10300 line (verified 2026-07). Order by MPN 10AEM10300C0000. Mouser live-verified 2026-07-22: 120-AEM10300-QFN (Mouser lists mfr P/N as AEM10300-QFN; the datasheet ordering code 10AEM10300C0000 resolves to this listing), 553 in stock, 16-day lead, $3.77 @1 (breaks 10@$2.81, 25@$2.57, 100@$2.31, 250@$2.19, 1000@$1.85). Schematic U8 symbol now carries Supplier=Mouser + Supplier P/N=120-AEM10300-QFN fields (MPN stays the e-peas ordering code 10AEM10300C0000).</t>
         </is>
       </c>
       <c r="L35" s="8" t="inlineStr">
@@ -2551,7 +2557,7 @@
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>MOUSER 10AEM10300C0000 (e-peas; not a DigiKey vendor)</t>
+          <t>MOUSER 120-AEM10300-QFN (e-peas; not a DigiKey vendor)</t>
         </is>
       </c>
     </row>
@@ -3098,10 +3104,10 @@
           <t>GRM188R61A106ME69D</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="8" t="n">
         <v>0.12</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="8" t="n">
         <v>0.12</v>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -3654,11 +3660,11 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>134.9</v>
+        <v>138.67</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>Sum of the 48 priced Ext$ cells only - the only remaining unpriced ordered line is U8/AEM10300 (Mouser-pending). See footnote.</t>
+          <t>Sum of the 49 priced Ext$ cells only. Every ordered on-board line is now priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -827,7 +827,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07150RL</t>
+          <t>AC0402FR-07150RL</t>
         </is>
       </c>
       <c r="H7" s="14" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>Package corrected to 0402 to match the placed land (BOM previously listed 1206; a 1206 part will not fit). 1/16 W is ample (~12 mW peak/LED). Value still SIZED for the clamped ~3.47 V rail (~9 mA/LED peak); re-tune after the energy-budget bench test. Any 0402 150 Ω 1% equivalent works (esp. for PCBA sourcing). DK live-verified 2026-07-22: 311-150LRCT-ND, Active, $0.10 @1 (DKPN corrected from format-derived guess).</t>
+          <t>Package corrected to 0402 to match the placed land (BOM previously listed 1206; a 1206 part will not fit). 1/16 W is ample (~12 mW peak/LED). Value still SIZED for the clamped ~3.47 V rail (~9 mA/LED peak); re-tune after the energy-budget bench test. Any 0402 150 Ω 1% equivalent works (esp. for PCBA sourcing). DK live-verified 2026-07-22: 311-150LRCT-ND, Active, $0.10 @1 (DKPN corrected from format-derived guess).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3443CT-ND, $0.1 @1, Active.</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
-          <t>311-150LRCT-ND</t>
+          <t>YAG3443CT-ND</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-07220RL</t>
+          <t>AC0402FR-07220RL</t>
         </is>
       </c>
       <c r="H8" s="14" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>Sets the SW2 TINY dim level; tunable. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-220LRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
+          <t>Sets the SW2 TINY dim level; tunable. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-220LRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3456CT-ND, $0.1 @1, Active.</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
-          <t>311-220LRCT-ND</t>
+          <t>YAG3456CT-ND</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>1 MΩ, ±1%</t>
+          <t>1 MΩ, ±0.1%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -949,14 +949,14 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML</t>
+          <t>RE0402BRE071ML</t>
         </is>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>R5=R6 → VSENSE = VIN/2 (tracks light, ~0 V dark). Feeds ADC + the AC0 wake-on-light comparator. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
+          <t>R5=R6 → VSENSE = VIN/2 (tracks light, ~0 V dark). Feeds ADC + the AC0 wake-on-light comparator. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (stability): precision Yageo RE, 0.1% / 50 ppm (VSENSE divider ratio + drift). DK 13-RE0402BRE071MLCT-ND, $0.30 @1, Active. (True thin-film not available at 1M in 0402; RE precision thick-film is the best in-footprint option.)</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>311-1.00MLRCT-ND</t>
+          <t>13-RE0402BRE071MLCT-ND</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>100 nF, X7R, 50 V</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H10" s="14" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC] [consolidation: 10nF -&gt; 100nF, joins the 100 nF group] DK live-verified 2026-07-22: DKPN corrected from GRM155R71C103KA01D-ND (a 10nF part, stale from the 10nF-&gt;100nF consolidation) to 490-3261-1-ND (100nF, matches the KA88D MPN). Active, $0.10 @1.</t>
+          <t>RC filter on the VSENSE node. [v3.0: 0402 to match board land; price TBC] [consolidation: 10nF -&gt; 100nF, joins the 100 nF group] DK live-verified 2026-07-22: DKPN corrected from GRM155R71C103KA01D-ND (a 10nF part, stale from the 10nF-&gt;100nF consolidation) to 490-3261-1-ND (100nF, matches the KA88D MPN). Active, $0.10 @1.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>RC0402FR-074K7L</t>
+          <t>AC0402FR-074K7L</t>
         </is>
       </c>
       <c r="H12" s="14" t="n">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>Required — open-drain TWI bus. Firmware must set TWIROUTEA = ALT2. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-4.7KLRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
+          <t>Required — open-drain TWI bus. Firmware must set TWIROUTEA = ALT2. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-4.7KLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3497CT-ND, $0.1 @1, Active.</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
-          <t>311-4.7KLRCT-ND</t>
+          <t>YAG3497CT-ND</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>100 nF, X7R, 50 V</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H13" s="14" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C3/C6/C7/C8 are the same line item.</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C3/C6/C7/C8 are the same line item.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>100 nF, X7R, 50 V</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H14" s="14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>10 µF, X5R, 10 V</t>
+          <t>10 µF, X5R, 16 V</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -1315,14 +1315,14 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>GRM188R61A106ME69D</t>
+          <t>GRT188R61C106KE13D</t>
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)</t>
+          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-12317-1-ND, $0.29 @1, Active. 10-&gt;16 V, 20-&gt;10% tol.</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>490-10475-1-ND</t>
+          <t>490-12317-1-ND</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>100 nF, X7R, 50 V</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H16" s="14" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C224KA12D</t>
+          <t>GRT155R71C224KE01D</t>
         </is>
       </c>
       <c r="H17" s="14" t="n">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>ADXL367 pin 9 VREG_OUT1 → GND. Datasheet-mandated 0.2 µF; 0.22 µF nearest std. DK live-verified 2026-07-22: 490-5418-1-ND, Active, $0.10 @1 (DKPN filled).</t>
+          <t>ADXL367 pin 9 VREG_OUT1 → GND. Datasheet-mandated 0.2 µF; 0.22 µF nearest std. DK live-verified 2026-07-22: 490-5418-1-ND, Active, $0.10 @1 (DKPN filled).  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71C224KE01DCT-ND, $0.1 @1, Active.</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>490-5418-1-ND</t>
+          <t>490-GRT155R71C224KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>100 nF, X7R, 50 V</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H18" s="14" t="n">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>ADXL367 pin 12 VDDIO → GND.</t>
+          <t>ADXL367 pin 12 VDDIO → GND.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>100 nF, X7R, 50 V</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -1559,14 +1559,14 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H19" s="14" t="n">
         <v>0.1</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>100 nF, X7R, 50 V</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H29" s="14" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>10 µF, X5R, 10 V</t>
+          <t>10 µF, X5R, 16 V</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -2291,14 +2291,14 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>GRM188R61A106ME69D</t>
+          <t>GRT188R61C106KE13D</t>
         </is>
       </c>
       <c r="H31" s="14" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
@@ -2307,13 +2307,13 @@
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)</t>
+          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-12317-1-ND, $0.29 @1, Active. 10-&gt;16 V, 20-&gt;10% tol.</t>
         </is>
       </c>
       <c r="L31" s="11" t="n"/>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>490-10475-1-ND</t>
+          <t>490-12317-1-ND</t>
         </is>
       </c>
     </row>
@@ -2409,14 +2409,14 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>TPS22918DBVR</t>
+          <t>TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/U6  TPS22918DBVR  $0.55.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off. DK live-verified 2026-07-22: 296-46278-1-ND, Active, $0.55 @1 (DKPN filled).</t>
+          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/U6  TPS22918DBVR  $0.55.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off. DK live-verified 2026-07-22: 296-46278-1-ND, Active, $0.55 @1 (DKPN filled).  UPGRADED 2026-07-23: AEC-Q100 automotive drop-in TPS22918TDBVRQ1 (pin-identical, same die as TPS22918DBVR) -- fixes the zero-stock DBVR AND upgrades reliability. DK 296-44632-1-ND, $0.75 @1, 882 stock.</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>296-46278-1-ND</t>
+          <t>296-44632-1-ND</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML</t>
+          <t>AC0402FR-071ML</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition, placed with the R14 board patch. Consolidated 100 kΩ -&gt; 1 MΩ (joins the R5/R6/R16/R17 reel, RC0402FR-071ML). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
+          <t>v3.0 addition, placed with the R14 board patch. Consolidated 100 kΩ -&gt; 1 MΩ (joins the R5/R6/R16/R17 reel, RC0402FR-071ML). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active.</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>311-1.00MLRCT-ND</t>
+          <t>YAG3450CT-ND</t>
         </is>
       </c>
     </row>
@@ -2821,14 +2821,14 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61E105MA12D</t>
+          <t>GRT155R61E105KE01J</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>v4 LDO input cap on the STO island (~5.5 V). Original GRM155R61A105KE15D (1 uF 10 V) is obsolete and the whole Murata GRM155 1 uF 10 V 0402 X5R family is EOL. RE-SOURCED 2026-07-22 -&gt; GRM155R61E105MA12D (1 uF 25 V X5R 0402), DK 490-10018-1-ND, Active, $0.10 @1, 461k in stock. 25 V chosen for DC-bias headroom on the ~5.5 V node. Schematic MPN updated to match.</t>
+          <t>v4 LDO input cap on the STO island (~5.5 V). Original GRM155R61A105KE15D (1 uF 10 V) is obsolete and the whole Murata GRM155 1 uF 10 V 0402 X5R family is EOL. RE-SOURCED 2026-07-22 -&gt; GRM155R61E105MA12D (1 uF 25 V X5R 0402), DK 490-10018-1-ND, Active, $0.10 @1, 461k in stock. 25 V chosen for DC-bias headroom on the ~5.5 V node. Schematic MPN updated to match.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R61E105KE01JCT-ND, $0.12 @1, Active. 20-&gt;10% tol.</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>490-10018-1-ND</t>
+          <t>490-GRT155R61E105KE01JCT-ND</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>2.2 µF, 10 V, 0402, X5R</t>
+          <t>2.2 µF, 25 V, 0402, X5R</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -2877,14 +2877,14 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>GRM155R61A225KE01J</t>
+          <t>GRT155R61E225KE13D</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
@@ -2893,12 +2893,12 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>v4 LDO output cap on VS (3.3 V). Original GRM155R61A225KE11D returned no DK results. RE-SOURCED 2026-07-22 -&gt; GRM155R61A225KE01J (2.2 uF 10 V X5R 0402, same spec), DK 490-GRM155R61A225KE01JCT-ND, Active, $0.10 @1, 38k in stock. Schematic MPN updated to match.</t>
+          <t>v4 LDO output cap on VS (3.3 V). Original GRM155R61A225KE11D returned no DK results. RE-SOURCED 2026-07-22 -&gt; GRM155R61A225KE01J (2.2 uF 10 V X5R 0402, same spec), DK 490-GRM155R61A225KE01JCT-ND, Active, $0.10 @1, 38k in stock. Schematic MPN updated to match.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-12267-1-ND, $0.25 @1, Active. 10-&gt;25 V (LDO-loop stability).</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>490-GRM155R61A225KE01JCT-ND</t>
+          <t>490-12267-1-ND</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.</t>
+          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -2989,14 +2989,14 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A226ME15D</t>
+          <t>GRT188R61A226ME13D</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard. DK live-verified 2026-07-22: 490-10476-1-ND, Active, $0.16 @1 (DKPN + price filled).</t>
+          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard. DK live-verified 2026-07-22: 490-10476-1-ND, Active, $0.16 @1 (DKPN + price filled).  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT188R61A226ME13DCT-ND, $0.31 @1, Active. Also fixes the zero-stock GRM188R61A226ME15D.</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>490-10476-1-ND</t>
+          <t>490-GRT188R61A226ME13DCT-ND</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>10 uF, 0402, X5R</t>
+          <t>10 uF, 10 V, 0402, X5R</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -3045,14 +3045,14 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>GRM155R60J106ME05D</t>
+          <t>GRT155R61A106ME13J</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
@@ -3061,12 +3061,12 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>v4 AEM VINT buffer cap (6.3 V rail). Original GRM155R60J106ME44D discontinued at DK. RE-SOURCED 2026-07-22 -&gt; GRM155R60J106ME05D (10 uF 6.3 V X5R 0402, same spec), DK 490-GRM155R60J106ME05DCT-ND, Active, $0.10 @1, 1.2M in stock. Schematic MPN updated to match.</t>
+          <t>v4 AEM VINT buffer cap (6.3 V rail). Original GRM155R60J106ME44D discontinued at DK. RE-SOURCED 2026-07-22 -&gt; GRM155R60J106ME05D (10 uF 6.3 V X5R 0402, same spec), DK 490-GRM155R60J106ME05DCT-ND, Active, $0.10 @1, 1.2M in stock. Schematic MPN updated to match.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R61A106ME13JCT-ND, $0.28 @1, Active. 6.3-&gt;10 V margin.</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>490-GRM155R60J106ME05DCT-ND</t>
+          <t>490-GRT155R61A106ME13JCT-ND</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>10 µF, 10 V, 0603, X5R</t>
+          <t>10 µF, 16 V, 0603, X5R</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -3101,14 +3101,14 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>GRM188R61A106ME69D</t>
+          <t>GRT188R61C106KE13D</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)</t>
+          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-12317-1-ND, $0.29 @1, Active. 10-&gt;16 V, 20-&gt;10% tol.</t>
         </is>
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>490-10475-1-ND</t>
+          <t>490-12317-1-ND</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.</t>
+          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t>490-3261-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-072ML</t>
+          <t>AC0402FR-072ML</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart. DK live-verified 2026-07-22: 13-RC0402FR-072MLCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
+          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart. DK live-verified 2026-07-22: 13-RC0402FR-072MLCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK 13-AC0402FR-072MLCT-ND, $0.1 @1, Active. No 0.1%/50ppm thin-film exists at 2M in 0402, so grade-only.</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>13-RC0402FR-072MLCT-ND</t>
+          <t>13-AC0402FR-072MLCT-ND</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>RC0402FR-071ML</t>
+          <t>AC0402FR-071ML</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).</t>
+          <t>Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active. (R16 STO-sense bottom; the R15 2M partner has no 0402 precision option, so this leg stays AEC-Q200 grade.)</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>311-1.00MLRCT-ND</t>
+          <t>YAG3450CT-ND</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>138.67</v>
+        <v>140.08</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).</t>
+          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).  Longevity/stability pass 2026-07-23: ceramics GRM-&gt;GRT (AEC-Q200) with V/tol bumps; resistors RC-&gt;AC (AEC-Q200), VSENSE divider R5/R6 to 0.1%/50ppm Yageo RE; U6 to AEC-Q100 TPS22918TDBVRQ1 (also clears the two zero-stock lines C25 + U6). Same footprints/values -- no layout change.</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="8" min="1" max="1"/>
@@ -3198,29 +3198,29 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>2 M, 0402, 1%</t>
+          <t>2 M, 0603, ±0.1%, 25 ppm</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603 (R_0603_1608Metric)</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>AC0402FR-072ML</t>
+          <t>MCT0603MD2004BP500</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
@@ -3229,37 +3229,37 @@
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>2 M in the project Yageo RC0402FR-07 1% convention; confirm at cart. DK live-verified 2026-07-22: 13-RC0402FR-072MLCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK 13-AC0402FR-072MLCT-ND, $0.1 @1, Active. No 0.1%/50ppm thin-film exists at 2M in 0402, so grade-only.</t>
+          <t>UPGRADED 2026-07-23 (stability): moved to an 0603 land to unlock precision that does not exist at 2M in 0402 -&gt; Vishay MCT0603 thin film, 0.1% / 25 ppm. Pairs with R16 (same land + precision class) so the STO_SNS divider ratio is ~0.1% with matched tempco. DK 541-MCT0603MD2004BP500CT-ND, $0.22 @1, 36k stock, Active. BOARD: new 0603 land to place + route (was solarglow:C1 0402-class); PCB rework pending.</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>13-AC0402FR-072MLCT-ND</t>
+          <t>541-MCT0603MD2004BP500CT-ND</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="9">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>R16, R17</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>STO sense divider bottom (R16) + EN_STO_CH pull-up to VINT (R17)</t>
+          <t>STO sense divider bottom (STO_SNS -&gt; GND)</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>1 M, 0402, 1%</t>
+          <t>1 M, 0603, ±0.1%, 25 ppm</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603 (R_0603_1608Metric)</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -3269,113 +3269,118 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>AC0402FR-071ML</t>
+          <t>RT0603BRD071ML</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>v4 - REWORK 0603</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active. (R16 STO-sense bottom; the R15 2M partner has no 0402 precision option, so this leg stays AEC-Q200 grade.)</t>
+          <t>UPGRADED 2026-07-23 (stability): 0603 thin film 0.1% / 25 ppm (Yageo RT), matched with R15 so the divider ratio carries the full precision. DK YAG4498CT-ND, $0.10 @1, 169k stock, Active. Split from the former R16,R17 shared line. BOARD: new 0603 land to place + route; PCB rework pending.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
+          <t>YAG4498CT-ND</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="9">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EN_STO_CH pull-up to VINT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1 M, 0402, ±1%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>AC0402FR-071ML</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Split 2026-07-23 from the former R16,R17 shared line: R17 is a non-critical pull-up and stays on the 0402 AEC-Q200 part (AC0402FR-071ML, DK YAG3450CT-ND). Prior shared-line note: Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active. (R16 STO-sense bottom; the R15 2M partner has no 0402 precision option, so this leg stays AEC-Q200 grade.)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
           <t>YAG3450CT-ND</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="9">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
-        </is>
-      </c>
-      <c r="J49" s="8" t="inlineStr">
-        <is>
-          <t>AUX</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>PRG1</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="n">
-        <v>1</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Adafruit UPDI Friend</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>26.4×17.8 mm board + JST-SH lead</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>6.95</v>
+          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
+        </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="inlineStr">
-        <is>
-          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
-        <is>
-          <t>(guide linked in firmware/README)</t>
-        </is>
-      </c>
-      <c r="M50" s="8" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="360.4" customHeight="1" s="9">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>CBL1</t>
+          <t>PRG1</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
@@ -3383,28 +3388,34 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
+          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>TC2030-MCP (legged, RJ12 end)</t>
+          <t>Adafruit UPDI Friend</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>6-ft cable, 6P6C modular plug</t>
+          <t>26.4×17.8 mm board + JST-SH lead</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>TC2030-MCP</t>
-        </is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>6.95</v>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
@@ -3413,52 +3424,52 @@
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback. DK live-verified 2026-07-22: DK TC2030-MCPTC-ND, Active, $36.00 @1 (AUX bench cable, one-time; not a per-board cost).</t>
+          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
+          <t>(guide linked in firmware/README)</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>HW1</t>
+          <t>CBL1</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
+          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
+          <t>TC2030-MCP (legged, RJ12 end)</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>head ⌀3.8 × 1.4 mm</t>
+          <t>6-ft cable, 6P6C modular plug</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>DIN 84 M2×3 brass</t>
+          <t>TC2030-MCP</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -3468,52 +3479,52 @@
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
+          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback. DK live-verified 2026-07-22: DK TC2030-MCPTC-ND, Active, $36.00 @1 (AUX bench cable, one-time; not a per-board cost).</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>docs/screw-m2x3-cheese.png</t>
+          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>ENC1</t>
+          <t>HW1</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V, 3.55 mm stack</t>
+          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>CNC from enclosure/ STEP</t>
+          <t>head ⌀3.8 × 1.4 mm</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>(PCBWay CNC or equiv.)</t>
+          <t>(generic)</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>(order from enclosure/*.step)</t>
+          <t>DIN 84 M2×3 brass</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -3523,12 +3534,12 @@
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>enclosure/README.md</t>
+          <t>docs/screw-m2x3-cheese.png</t>
         </is>
       </c>
       <c r="M53" s="8" t="inlineStr">
@@ -3540,7 +3551,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>INS1</t>
+          <t>ENC1</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
@@ -3548,42 +3559,42 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>~0.05 mm polyimide, die-cut to board outline</t>
+          <t>Ti-6Al-4V, 3.55 mm stack</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>sheet / die-cut</t>
+          <t>CNC from enclosure/ STEP</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>(PCBWay CNC or equiv.)</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>(polyimide film, 0.05 mm)</t>
+          <t>(order from enclosure/*.step)</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>AUX-OPTIONAL</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>enclosure/README.md</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr">
@@ -3595,81 +3606,137 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
+          <t>INS1</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>~0.05 mm polyimide, die-cut to board outline</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>sheet / die-cut</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>(generic)</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>(polyimide film, 0.05 mm)</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>AUX-OPTIONAL</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+        </is>
+      </c>
+      <c r="L55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
           <t>FER1</t>
         </is>
       </c>
-      <c r="B55" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="B56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>Würth Elektronik</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>364006</t>
         </is>
       </c>
-      <c r="H55" s="8" t="n">
+      <c r="H56" s="8" t="n">
         <v>17.43</v>
       </c>
-      <c r="I55" s="8" t="n">
+      <c r="I56" s="8" t="n">
         <v>17.43</v>
       </c>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="J56" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
         </is>
       </c>
-      <c r="K55" s="8" t="inlineStr">
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>FINAL, verified 2026-07-03: DK 732-5049-ND, Active, tray, $17.43 @ 1 (51 in stock at verification; 24-wk mfr lead — buy with the order). 60×60 mm sheet, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA); one sheet = 4 patches. Cut 12.2 × 25.8 mm on the 2 mm score grid; brace channel depth = measured stack − 0.05 (sits ~0.05 proud, seats flush; PET face to the board, PSA into the brace). Stock-dry fallback: 3× stacked 3641014 (732-13935-ND, $4.19 ea, µ′150/µ″3 @ 13.56 MHz, 0.14 mm ea) ≈ same ferrite thickness; last resort Laird MHLL6060-300 (240-2791-ND, 0.09 mm, weakest). All three datasheets in repo.</t>
         </is>
       </c>
-      <c r="L55" s="8" t="inlineStr">
+      <c r="L56" s="8" t="inlineStr">
         <is>
           <t>FER1  Wurth WE-FSFS 364006  $17.43.pdf + FER1-alt  Wurth WE-FSFS 3641014  $4.19.pdf + FER1-alt  Laird MHLL6060-300  $6.40.pdf (repo)</t>
         </is>
       </c>
-      <c r="M55" s="8" t="inlineStr">
+      <c r="M56" s="8" t="inlineStr">
         <is>
           <t>732-5049-ND</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="G56" s="8" t="inlineStr">
+    <row r="57">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
         </is>
       </c>
-      <c r="I56" s="8" t="n">
-        <v>140.08</v>
-      </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>Sum of the 49 priced Ext$ cells only. Every ordered on-board line is now priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="I57" s="8" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>Sum of the 50 priced Ext$ cells only. Every ordered on-board line is now priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).  Longevity/stability pass 2026-07-23: ceramics GRM-&gt;GRT (AEC-Q200) with V/tol bumps; resistors RC-&gt;AC (AEC-Q200), VSENSE divider R5/R6 to 0.1%/50ppm Yageo RE; U6 to AEC-Q100 TPS22918TDBVRQ1 (also clears the two zero-stock lines C25 + U6). Same footprints/values -- no layout change.</t>
         </is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="8" min="1" max="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>1 MΩ, ±0.1%</t>
+          <t>1 MΩ, ±0.1%, 25 ppm, 0603</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603 (R_0603_1608Metric)</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -949,14 +949,14 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>RE0402BRE071ML</t>
+          <t>RT0603BRD071ML</t>
         </is>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>R5=R6 → VSENSE = VIN/2 (tracks light, ~0 V dark). Feeds ADC + the AC0 wake-on-light comparator. [v3.0: 0402 to match board land; price TBC] DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (stability): precision Yageo RE, 0.1% / 50 ppm (VSENSE divider ratio + drift). DK 13-RE0402BRE071MLCT-ND, $0.30 @1, Active. (True thin-film not available at 1M in 0402; RE precision thick-film is the best in-footprint option.)</t>
+          <t>UPSIZED 2026-07-23 (stability): 0402 RE 0.1%/50ppm -&gt; 0603 thin film 0.1%/25ppm (Yageo RT). VSENSE divider matched pair; same MPN as R16 - three refs now share RT0603BRD071ML. DK YAG4498CT-ND (CT MOQ 1), $0.10 @1, 169k stock. BOARD: two 0603 lands pending.</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>13-RE0402BRE071MLCT-ND</t>
+          <t>YAG4498CT-ND</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>1 uF, 25 V, 0402, X5R</t>
+          <t>1 uF, 25 V, 0603, X7R</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603 (C_0603_1608Metric)</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -2821,14 +2821,14 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>GRT155R61E105KE01J</t>
+          <t>GRT188R71E105KE13D</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>v4 LDO input cap on the STO island (~5.5 V). Original GRM155R61A105KE15D (1 uF 10 V) is obsolete and the whole Murata GRM155 1 uF 10 V 0402 X5R family is EOL. RE-SOURCED 2026-07-22 -&gt; GRM155R61E105MA12D (1 uF 25 V X5R 0402), DK 490-10018-1-ND, Active, $0.10 @1, 461k in stock. 25 V chosen for DC-bias headroom on the ~5.5 V node. Schematic MPN updated to match.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R61E105KE01JCT-ND, $0.12 @1, Active. 20-&gt;10% tol.</t>
+          <t>UPSIZED 2026-07-23 (stability): 0402 X5R -&gt; 0603 X7R, stays Murata GRT (AEC-Q200). LDO input cap on the STO_LDO island (~5.5 V max) - X7R + bigger body = near-full capacitance under bias/temp. DK 490-GRT188R71E105KE13DCT-ND (CT MOQ 1), $0.14 @1, 91k stock. BOARD: 0603 land pending (Update PCB from Schematic).</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>490-GRT155R61E105KE01JCT-ND</t>
+          <t>490-GRT188R71E105KE13DCT-ND</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>2.2 µF, 25 V, 0402, X5R</t>
+          <t>2.2 µF, 25 V, 0603, X7R</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603 (C_0603_1608Metric)</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -2877,14 +2877,14 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>GRT155R61E225KE13D</t>
+          <t>GRM188Z71E225ME43D</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
@@ -2893,12 +2893,12 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>v4 LDO output cap on VS (3.3 V). Original GRM155R61A225KE11D returned no DK results. RE-SOURCED 2026-07-22 -&gt; GRM155R61A225KE01J (2.2 uF 10 V X5R 0402, same spec), DK 490-GRM155R61A225KE01JCT-ND, Active, $0.10 @1, 38k in stock. Schematic MPN updated to match.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-12267-1-ND, $0.25 @1, Active. 10-&gt;25 V (LDO-loop stability).</t>
+          <t>UPSIZED 2026-07-23 (stability): 0402 X5R -&gt; 0603 X7R 25 V. U9 LDO output cap - TPS7A02 loop stability rides on effective C staying in band; X7R holds it over temp/bias. X7R chosen over staying GRT/AEC (the GRT 0603 2.2uF is X5R; dielectric wins here - GRT188R61E225KE13D is the AEC alternate). DK 490-GRM188Z71E225ME43DCT-ND (CT MOQ 1), $0.17 @1, 341k stock. BOARD: 0603 land pending.</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>490-12267-1-ND</t>
+          <t>490-GRM188Z71E225ME43DCT-ND</t>
         </is>
       </c>
     </row>
@@ -3017,63 +3017,63 @@
     <row r="44" ht="15" customHeight="1" s="9">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C26, C27</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>AEM VINT buffer cap</t>
+          <t>AEM VINT buffer (C26) + STO local bulk/decoupling (C27)</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>10 uF, 10 V, 0402, X5R</t>
+          <t>10 µF, 10 V, 0805, X7R</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805 (C_0805_2012Metric)</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Murata (rec.)</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>GRT155R61A106ME13J</t>
+          <t>GRM21BR71A106KA73L</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>v4 - REWORK 0805</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>v4 AEM VINT buffer cap (6.3 V rail). Original GRM155R60J106ME44D discontinued at DK. RE-SOURCED 2026-07-22 -&gt; GRM155R60J106ME05D (10 uF 6.3 V X5R 0402, same spec), DK 490-GRM155R60J106ME05DCT-ND, Active, $0.10 @1, 1.2M in stock. Schematic MPN updated to match.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R61A106ME13JCT-ND, $0.28 @1, Active. 6.3-&gt;10 V margin.</t>
+          <t>UPSIZED 2026-07-23 (stability): C26 (0402 X5R 10 V) and C27 (0603 X5R 16 V) merge onto one 0805 X7R 10 V line. 10 uF at 0402 is the density ceiling (worst DC-bias/temp rolloff on the board); 0805 X7R holds capacitance. C26 = VINT (~2.2 V, trivial bias); C27 = STO (&lt;=5.5 V on 10 V X7R = comfortable). NOTE: the AEC-Q200 0805 option (Cal-Chip GMT21X7R106K16NT3) is reel-only MOQ 3000 - rejected for a one-of-one build; Murata GRM CT MOQ 1 chosen instead. DK 490-10516-1-ND, $0.12 @1, 143k stock. BOARD: two 0805 lands pending.</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>490-GRT155R61A106ME13JCT-ND</t>
+          <t>490-10516-1-ND</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="9">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>STO local HF decoupling</t>
+          <t>FRAM VNFC decoupling</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>10 µF, 16 V, 0603, X5R</t>
+          <t>100 nF, 0402, X7R</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -3101,35 +3101,35 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>GRT188R61C106KE13D</t>
+          <t>GRT155R71H104KE01D</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.29</v>
+        <v>0.1</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.29</v>
+        <v>0.1</v>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>LAND REWORK</t>
+          <t>v4 NEW</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>10 uF 10 V X5R 0603. Original GRM188R61A106KE69D is Active but DigiKey stocks/prices no variation (order-only). RE-SOURCED 2026-07-22 -&gt; GRM188R61A106ME69D (same 10 uF/10 V/X5R/0603, tol K-&gt;M i.e. +-10%-&gt;+-20%, immaterial for bulk/decoupling), DK 490-10475-1-ND, Active, $0.12 @1, 578k in stock. Schematic MPN updated to match. (For more DC-bias margin on the STO/LED nodes, GRM188R61E106MA73D 25 V, DK 490-7202-1-ND, $0.26 is a drop-in.)  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-12317-1-ND, $0.29 @1, Active. 10-&gt;16 V, 20-&gt;10% tol.</t>
+          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
         </is>
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>490-12317-1-ND</t>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="9">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
@@ -3137,34 +3137,34 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>FRAM VNFC decoupling</t>
+          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>100 nF, 0402, X7R</t>
+          <t>2 M, 0603, ±0.1%, 25 ppm</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603 (R_0603_1608Metric)</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>GRT155R71H104KE01D</t>
+          <t>MCT0603MD2004BP500</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
@@ -3173,19 +3173,19 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
+          <t>UPGRADED 2026-07-23 (stability): moved to an 0603 land to unlock precision that does not exist at 2M in 0402 -&gt; Vishay MCT0603 thin film, 0.1% / 25 ppm. Pairs with R16 (same land + precision class) so the STO_SNS divider ratio is ~0.1% with matched tempco. DK 541-MCT0603MD2004BP500CT-ND, $0.22 @1, 36k stock, Active. BOARD: new 0603 land to place + route (was solarglow:C1 0402-class); PCB rework pending.</t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t>490-GRT155R71H104KE01DCT-ND</t>
+          <t>541-MCT0603MD2004BP500CT-ND</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="9">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
+          <t>STO sense divider bottom (STO_SNS -&gt; GND)</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>2 M, 0603, ±0.1%, 25 ppm</t>
+          <t>1 M, 0603, ±0.1%, 25 ppm</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -3208,40 +3208,45 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>MCT0603MD2004BP500</t>
+          <t>RT0603BRD071ML</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>v4 - REWORK 0603</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>UPGRADED 2026-07-23 (stability): moved to an 0603 land to unlock precision that does not exist at 2M in 0402 -&gt; Vishay MCT0603 thin film, 0.1% / 25 ppm. Pairs with R16 (same land + precision class) so the STO_SNS divider ratio is ~0.1% with matched tempco. DK 541-MCT0603MD2004BP500CT-ND, $0.22 @1, 36k stock, Active. BOARD: new 0603 land to place + route (was solarglow:C1 0402-class); PCB rework pending.</t>
+          <t>UPGRADED 2026-07-23 (stability): 0603 thin film 0.1% / 25 ppm (Yageo RT), matched with R15 so the divider ratio carries the full precision. DK YAG4498CT-ND, $0.10 @1, 169k stock, Active. Split from the former R16,R17 shared line. BOARD: new 0603 land to place + route; PCB rework pending.</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>541-MCT0603MD2004BP500CT-ND</t>
+          <t>YAG4498CT-ND</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="9">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
@@ -3249,17 +3254,17 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>STO sense divider bottom (STO_SNS -&gt; GND)</t>
+          <t>EN_STO_CH pull-up to VINT</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>1 M, 0603, ±0.1%, 25 ppm</t>
+          <t>1 M, 0402, ±1%</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>0603 (R_0603_1608Metric)</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -3269,7 +3274,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>RT0603BRD071ML</t>
+          <t>AC0402FR-071ML</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
@@ -3280,107 +3285,107 @@
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>v4 - REWORK 0603</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>UPGRADED 2026-07-23 (stability): 0603 thin film 0.1% / 25 ppm (Yageo RT), matched with R15 so the divider ratio carries the full precision. DK YAG4498CT-ND, $0.10 @1, 169k stock, Active. Split from the former R16,R17 shared line. BOARD: new 0603 land to place + route; PCB rework pending.</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
+          <t>Split 2026-07-23 from the former R16,R17 shared line: R17 is a non-critical pull-up and stays on the 0402 AEC-Q200 part (AC0402FR-071ML, DK YAG3450CT-ND). Prior shared-line note: Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active. (R16 STO-sense bottom; the R15 2M partner has no 0402 precision option, so this leg stays AEC-Q200 grade.)</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>YAG4498CT-ND</t>
+          <t>YAG3450CT-ND</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="9">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>R17</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>EN_STO_CH pull-up to VINT</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1 M, 0402, ±1%</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Yageo</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>AC0402FR-071ML</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Split 2026-07-23 from the former R16,R17 shared line: R17 is a non-critical pull-up and stays on the 0402 AEC-Q200 part (AC0402FR-071ML, DK YAG3450CT-ND). Prior shared-line note: Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active. (R16 STO-sense bottom; the R15 2M partner has no 0402 precision option, so this leg stays AEC-Q200 grade.)</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>YAG3450CT-ND</t>
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>AUX</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>PRG1</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
-        </is>
+          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Adafruit UPDI Friend</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>26.4×17.8 mm board + JST-SH lead</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Adafruit</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>6.95</v>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>(guide linked in firmware/README)</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="inlineStr">
+        <is>
+          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="360.4" customHeight="1" s="9">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>PRG1</t>
+          <t>CBL1</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
@@ -3388,34 +3393,28 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
+          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Adafruit UPDI Friend</t>
+          <t>TC2030-MCP (legged, RJ12 end)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>26.4×17.8 mm board + JST-SH lead</t>
+          <t>6-ft cable, 6P6C modular plug</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Adafruit</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="I51" s="8" t="n">
-        <v>6.95</v>
+          <t>TC2030-MCP</t>
+        </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
@@ -3424,52 +3423,52 @@
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
+          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback. DK live-verified 2026-07-22: DK TC2030-MCPTC-ND, Active, $36.00 @1 (AUX bench cable, one-time; not a per-board cost).</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>(guide linked in firmware/README)</t>
+          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>CBL1</t>
+          <t>HW1</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
+          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>TC2030-MCP (legged, RJ12 end)</t>
+          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>6-ft cable, 6P6C modular plug</t>
+          <t>head ⌀3.8 × 1.4 mm</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>(generic)</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>TC2030-MCP</t>
+          <t>DIN 84 M2×3 brass</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -3479,52 +3478,52 @@
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback. DK live-verified 2026-07-22: DK TC2030-MCPTC-ND, Active, $36.00 @1 (AUX bench cable, one-time; not a per-board cost).</t>
+          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
+          <t>docs/screw-m2x3-cheese.png</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>HW1</t>
+          <t>ENC1</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
+          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
+          <t>Ti-6Al-4V, 3.55 mm stack</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>head ⌀3.8 × 1.4 mm</t>
+          <t>CNC from enclosure/ STEP</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>(PCBWay CNC or equiv.)</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>DIN 84 M2×3 brass</t>
+          <t>(order from enclosure/*.step)</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -3534,12 +3533,12 @@
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
+          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>docs/screw-m2x3-cheese.png</t>
+          <t>enclosure/README.md</t>
         </is>
       </c>
       <c r="M53" s="8" t="inlineStr">
@@ -3551,7 +3550,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>ENC1</t>
+          <t>INS1</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
@@ -3559,42 +3558,42 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V, 3.55 mm stack</t>
+          <t>~0.05 mm polyimide, die-cut to board outline</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>CNC from enclosure/ STEP</t>
+          <t>sheet / die-cut</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>(PCBWay CNC or equiv.)</t>
+          <t>(generic)</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>(order from enclosure/*.step)</t>
+          <t>(polyimide film, 0.05 mm)</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>AUX-OPTIONAL</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>enclosure/README.md</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr">
@@ -3606,7 +3605,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>INS1</t>
+          <t>FER1</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
@@ -3614,129 +3613,74 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+          <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>~0.05 mm polyimide, die-cut to board outline</t>
+          <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>sheet / die-cut</t>
+          <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>Würth Elektronik</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>(polyimide film, 0.05 mm)</t>
-        </is>
+          <t>364006</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>17.43</v>
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>AUX-OPTIONAL</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+          <t>FINAL, verified 2026-07-03: DK 732-5049-ND, Active, tray, $17.43 @ 1 (51 in stock at verification; 24-wk mfr lead — buy with the order). 60×60 mm sheet, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA); one sheet = 4 patches. Cut 12.2 × 25.8 mm on the 2 mm score grid; brace channel depth = measured stack − 0.05 (sits ~0.05 proud, seats flush; PET face to the board, PSA into the brace). Stock-dry fallback: 3× stacked 3641014 (732-13935-ND, $4.19 ea, µ′150/µ″3 @ 13.56 MHz, 0.14 mm ea) ≈ same ferrite thickness; last resort Laird MHLL6060-300 (240-2791-ND, 0.09 mm, weakest). All three datasheets in repo.</t>
         </is>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FER1  Wurth WE-FSFS 364006  $17.43.pdf + FER1-alt  Wurth WE-FSFS 3641014  $4.19.pdf + FER1-alt  Laird MHLL6060-300  $6.40.pdf (repo)</t>
         </is>
       </c>
       <c r="M55" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>732-5049-ND</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>FER1</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>Würth Elektronik</t>
-        </is>
-      </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>364006</t>
-        </is>
-      </c>
-      <c r="H56" s="8" t="n">
-        <v>17.43</v>
+          <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
+        </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="J56" s="8" t="inlineStr">
-        <is>
-          <t>AUX</t>
-        </is>
+        <v>139.41</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>FINAL, verified 2026-07-03: DK 732-5049-ND, Active, tray, $17.43 @ 1 (51 in stock at verification; 24-wk mfr lead — buy with the order). 60×60 mm sheet, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA); one sheet = 4 patches. Cut 12.2 × 25.8 mm on the 2 mm score grid; brace channel depth = measured stack − 0.05 (sits ~0.05 proud, seats flush; PET face to the board, PSA into the brace). Stock-dry fallback: 3× stacked 3641014 (732-13935-ND, $4.19 ea, µ′150/µ″3 @ 13.56 MHz, 0.14 mm ea) ≈ same ferrite thickness; last resort Laird MHLL6060-300 (240-2791-ND, 0.09 mm, weakest). All three datasheets in repo.</t>
-        </is>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
-        <is>
-          <t>FER1  Wurth WE-FSFS 364006  $17.43.pdf + FER1-alt  Wurth WE-FSFS 3641014  $4.19.pdf + FER1-alt  Laird MHLL6060-300  $6.40.pdf (repo)</t>
-        </is>
-      </c>
-      <c r="M56" s="8" t="inlineStr">
-        <is>
-          <t>732-5049-ND</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
-        </is>
-      </c>
-      <c r="I57" s="8" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="K57" s="8" t="inlineStr">
-        <is>
-          <t>Sum of the 50 priced Ext$ cells only. Every ordered on-board line is now priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+          <t>Sum of the 49 priced Ext$ cells only. Every ordered on-board line is now priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).  Longevity/stability pass 2026-07-23: ceramics GRM-&gt;GRT (AEC-Q200) with V/tol bumps; resistors RC-&gt;AC (AEC-Q200), VSENSE divider R5/R6 to 0.1%/50ppm Yageo RE; U6 to AEC-Q100 TPS22918TDBVRQ1 (also clears the two zero-stock lines C25 + U6). Same footprints/values -- no layout change.</t>
         </is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>SOIC-8 (150 mil)</t>
+          <t>DFN-8 LCC-8P-M05 (5.0×6.0×0.90 mm MAX, 1.27 mm pitch)</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>MB85RC512TYPNF-GS-BCERE1</t>
+          <t>MB85RC512TYPN-GS-AWEWE1</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>v4 - REWORK DFN</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>Price from repo datasheet filename. AEC-Q100. DK live-verified 2026-07-22: 865-MB85RC512TYPNF-GS-BCERE1CT-ND, Active, $10.19 @1 (CT variation of the TR P/N).</t>
+          <t>REPACKAGED 2026-07-23 (height): same MB85RC512TY die, SOP-8 (1.75 mm) -&gt; DFN LCC-8P-M05 (0.90 mm MAX) - U7 was the tallest rear part and drove the backshell's 0.95 floor pocket. Identical electricals (512 kbit I2C 0x50, 16-bit addressing, 1.8-3.6 V, 125 C, TY/GS AEC grade) - zero firmware change; same $10.19 @1, DK live-verified 2026-07-23 (1500 stock, CT MOQ 1). Mouser alt: 249-MB85RC512TYPNGA1. Repo datasheet covers both packages (drawing p.~end: 5.00x6.00, 0.90 MAX, 0.40 lead, 1.27 BSC). BOARD: draw solarglow:U7_DFN8 land from the drawing (no stock KiCad footprint; no recommended pattern in the datasheet), Update-PCB, route. Hand-solder note: side-wettable LCC flanks at 1.27 mm pitch - drag/side-fillet, a step down from SOIC. Enclosure follow-up: the U7 pocket may be deletable.</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>865-MB85RC512TYPNF-GS-BCERE1CT-ND</t>
+          <t>865-MB85RC512TYPN-GS-AWEWE1CT-ND</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>High-side load switch</t>
+          <t>Ultra-low-leakage load switch</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -2409,14 +2409,14 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>TPS22918TDBVRQ1</t>
+          <t>TPS22917DBVT</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.75</v>
+        <v>1.14</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.75</v>
+        <v>1.14</v>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/U6  TPS22918DBVR  $0.55.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off. DK live-verified 2026-07-22: 296-46278-1-ND, Active, $0.55 @1 (DKPN filled).  UPGRADED 2026-07-23: AEC-Q100 automotive drop-in TPS22918TDBVRQ1 (pin-identical, same die as TPS22918DBVR) -- fixes the zero-stock DBVR AND upgrades reliability. DK 296-44632-1-ND, $0.75 @1, 882 stock.</t>
+          <t>SWAPPED 2026-07-23 (dark current): TPS22918TDBVRQ1 -&gt; TPS22917DBVT, TI's ultra-low-leakage pin-identical sibling (SLVSDW8B, saved in datasheets/): OFF-state ISD 10 nA typ vs the 918's 0.5 uA typ / 3.5 uA MAX @3.3V (repo 918 datasheet 6.5) - U6 sits energized on VS and off ~always, so this was the board's largest standing silicon drain; ~50x lower now. ON-state IQ 0.5 uA vs 8.3 uA. Same SOT-23-6 land, pinout identical (Table 6-1: VIN GND ON CT QOD VOUT); board config sanctioned (CT float = fastest rise, QOD tied to VOUT). Ron 80 vs 52 mOhm - immaterial at mA loads. Bonus: 125 C + always-on reverse-current blocking (NFC EH pin downstream). Trade: no AEC-Q100 variant exists - dark current prioritized over grade by design call. DO NOT substitute TPS22917L (active-LOW ON - inverts NFC_EN). DK live-verified: 296-48370-1-ND, Active, $1.14 @1 CT MOQ 1, 7.2k stock (Mouser alt 595-TPS22917DBVT, 13k).</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>296-44632-1-ND</t>
+          <t>296-48370-1-ND</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>139.41</v>
+        <v>139.8</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -522,14 +522,14 @@
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>AVR64DD28-I/STX</t>
+          <t>AVR64DD28-E/STX</t>
         </is>
       </c>
       <c r="H2" s="14" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="I2" s="14" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>VQFN land has an exposed pad → EP to GND. /STX confirmed = VQFN-28 (4×4). DK verified 2026-07-02: Active, tube, $1.17 @ 1, VQFN28 (4x4) confirmed on the DK listing.</t>
+          <t>VQFN land has an exposed pad → EP to GND. /STX confirmed = VQFN-28 (4×4). DK verified 2026-07-02: Active, tube, $1.17 @ 1, VQFN28 (4x4) confirmed on the DK listing. GRADE BUMP EXECUTED 2026-07-23: -I/STX (-40..85C) -&gt; -E/STX (-40..125C) - closing a doc&lt;-&gt;BOM drift: design-notes 'Bumped to automotive/higher temp' already committed to this exact swap but the BOM/sch never carried it. Same die, same VQFN28 4x4 land, same firmware; $1.24 @1 (+$0.07). DK live-verified: 150-AVR64DD28-E/STX-ND, Active, 319 stock (tube); deep-stock alt: AVR64DD28T-E/STX tape, DK 3.3k / Mouser 3.1k, same price. Datasheet DS40002315C (repo copy filed under the -I name) covers all grades.</t>
         </is>
       </c>
       <c r="L2" s="11" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>150-AVR64DD28-I/STX-ND</t>
+          <t>150-AVR64DD28-E/STX-ND</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>139.8</v>
+        <v>139.87</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>AVR64DD28, 64 KB, 24 MHz</t>
+          <t>AVR64EA28, 64 KB, 20 MHz</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>AVR64DD28-E/STX</t>
+          <t>AVR64EA28-E/STX</t>
         </is>
       </c>
       <c r="H2" s="14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I2" s="14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>VQFN land has an exposed pad → EP to GND. /STX confirmed = VQFN-28 (4×4). DK verified 2026-07-02: Active, tube, $1.17 @ 1, VQFN28 (4x4) confirmed on the DK listing. GRADE BUMP EXECUTED 2026-07-23: -I/STX (-40..85C) -&gt; -E/STX (-40..125C) - closing a doc&lt;-&gt;BOM drift: design-notes 'Bumped to automotive/higher temp' already committed to this exact swap but the BOM/sch never carried it. Same die, same VQFN28 4x4 land, same firmware; $1.24 @1 (+$0.07). DK live-verified: 150-AVR64DD28-E/STX-ND, Active, 319 stock (tube); deep-stock alt: AVR64DD28T-E/STX tape, DK 3.3k / Mouser 3.1k, same price. Datasheet DS40002315C (repo copy filed under the -I name) covers all grades.</t>
+          <t>FAMILY SWAP 2026-07-23: AVR64DD28 -&gt; AVR64EA28-E/STX (extended -40..125C), datasheet-verified (DS40002443A, saved in datasheets/; note PRELIMINARY rev). Verified wins: 12-bit DIFFERENTIAL ADC + PGA + 1024-sample accumulation (pairs with the 0.1%/25ppm dividers), VREF 1.024/2.048V +-2% vs DD's +-4%, base power-down 0.08uA vs 0.65uA, EEPROM 512B vs 256B (black box), cheaper + deeper stocked. Board-compatible with the frozen copper per Microchip atdf pin diff: 27/28 pads identical; pin 10 VDDIO2-&gt;PD0 handled by SJ1=DNP. TWI ALT2 (PC2/PC3), TCA0 PORTA (WO0-3=PA0-3), PD1/PD2 AINP/AINN all confirmed present. FIRMWARE PORT REQUIRED (sense.c ADC rewrite, fuses: BOD 2.45V level does not exist on EA -&gt; 2.60V BODLEVEL2, MVSYSCFG dropped) - see TODO. DK live-verified: 150-AVR64EA28-E/STX-ND, Active, $1.23 @1, 1365 stock (tape alt AVR64EA28T-E/STX, DK 3.3k / Mouser 3.3k, $1.04-1.25).</t>
         </is>
       </c>
       <c r="L2" s="11" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="M2" s="11" t="inlineStr">
         <is>
-          <t>150-AVR64DD28-E/STX-ND</t>
+          <t>150-AVR64EA28-E/STX-ND</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>0 Ω jumper</t>
+          <t>DNP (was 0 Ω jumper)</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -1620,23 +1620,23 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>RC0805JR-070RL</t>
+          <t>(DNP - not ordered)</t>
         </is>
       </c>
       <c r="H20" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>DK live-verified 2026-07-22: 311-0.0ARCT-ND, Active, $0.10 @1 (was $0.05; DKPN corrected).</t>
+          <t>DNP 2026-07-23 with the AVR-EA U1 swap: pin 10 on the EA28 is PD0 (GPIO), not VDDIO2, so the 0R VS tie must NOT be bridged - PD0 floats and firmware inits it input-disabled. The RC0805JR-070RL 0R stays a valid spare if the DD28 is ever reinstated (land unchanged).</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
-          <t>311-0.0ARCT-ND</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>139.87</v>
+        <v>139.76</v>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -538,12 +538,12 @@
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>FAMILY SWAP 2026-07-23: AVR64DD28 -&gt; AVR64EA28-E/STX (extended -40..125C), datasheet-verified (DS40002443A, saved in datasheets/; note PRELIMINARY rev). Verified wins: 12-bit DIFFERENTIAL ADC + PGA + 1024-sample accumulation (pairs with the 0.1%/25ppm dividers), VREF 1.024/2.048V +-2% vs DD's +-4%, base power-down 0.08uA vs 0.65uA, EEPROM 512B vs 256B (black box), cheaper + deeper stocked. Board-compatible with the frozen copper per Microchip atdf pin diff: 27/28 pads identical; pin 10 VDDIO2-&gt;PD0 handled by SJ1=DNP. TWI ALT2 (PC2/PC3), TCA0 PORTA (WO0-3=PA0-3), PD1/PD2 AINP/AINN all confirmed present. FIRMWARE PORT REQUIRED (sense.c ADC rewrite, fuses: BOD 2.45V level does not exist on EA -&gt; 2.60V BODLEVEL2, MVSYSCFG dropped) - see TODO. DK live-verified: 150-AVR64EA28-E/STX-ND, Active, $1.23 @1, 1365 stock (tape alt AVR64EA28T-E/STX, DK 3.3k / Mouser 3.3k, $1.04-1.25).</t>
+          <t>FAMILY SWAP 2026-07-23: AVR64DD28 -&gt; AVR64EA28-E/STX (extended -40..125C), datasheet-verified (DS40002443A, saved in datasheets/; note PRELIMINARY rev). Verified wins: 12-bit DIFFERENTIAL ADC + PGA + 1024-sample accumulation (pairs with the 0.1%/25ppm dividers), VREF 1.024/2.048V +-2% vs DD's +-4%, base power-down 0.08uA vs 0.65uA, EEPROM 512B vs 256B (black box), cheaper + deeper stocked. Board-compatible with the frozen copper per Microchip atdf pin diff: 27/28 pads identical; pin 10 VDDIO2-&gt;PD0 handled by SJ1=DNP. TWI ALT2 (PC2/PC3), TCA0 PORTA (WO0-3=PA0-3), PD1/PD2 AINP/AINN all confirmed present. FIRMWARE PORT DONE 2026-07-23 (PR #66): EA ADC model in sense.c, temp sensor on the 1.024V ref, fuses bodcfg 0x4A (2.60V BODLEVEL2 - no 2.45V level on EA) / osccfg 0x08 (16MHz base -&gt; exactly 1 MHz) / syscfg0 0xD1, no MVSYSCFG; floors re-derived 2750/2850 mV; compile-verified warning-free (3,960 B). DK live-verified: 150-AVR64EA28-E/STX-ND, Active, $1.23 @1, 1365 stock (tape alt AVR64EA28T-E/STX, DK 3.3k / Mouser 3.3k, $1.04-1.25).</t>
         </is>
       </c>
       <c r="L2" s="11" t="inlineStr">
         <is>
-          <t>U1  AVR64DD28-I-STX  $1.17.pdf</t>
+          <t>U1  AVR64EA28-E-STX  $1.23.pdf</t>
         </is>
       </c>
       <c r="M2" s="11" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>VDDIO2 tie — bonds VDDIO2 to VS (MVIO unused)</t>
+          <t>DD-era VDDIO2 tie (pin 10 = PD0 on the EA) — DNP, must NOT be bridged</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>U6  TPS22918DBVR  $0.55.pdf</t>
+          <t>U6  TPS22917DBVT  $1.14.pdf</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>v4 - REWORK DFN</t>
+          <t>v4 - DFN routed</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>REPACKAGED 2026-07-23 (height): same MB85RC512TY die, SOP-8 (1.75 mm) -&gt; DFN LCC-8P-M05 (0.90 mm MAX) - U7 was the tallest rear part and drove the backshell's 0.95 floor pocket. Identical electricals (512 kbit I2C 0x50, 16-bit addressing, 1.8-3.6 V, 125 C, TY/GS AEC grade) - zero firmware change; same $10.19 @1, DK live-verified 2026-07-23 (1500 stock, CT MOQ 1). Mouser alt: 249-MB85RC512TYPNGA1. Repo datasheet covers both packages (drawing p.~end: 5.00x6.00, 0.90 MAX, 0.40 lead, 1.27 BSC). BOARD: draw solarglow:U7_DFN8 land from the drawing (no stock KiCad footprint; no recommended pattern in the datasheet), Update-PCB, route. Hand-solder note: side-wettable LCC flanks at 1.27 mm pitch - drag/side-fillet, a step down from SOIC. Enclosure follow-up: the U7 pocket may be deletable.</t>
+          <t>REPACKAGED 2026-07-23 (height): same MB85RC512TY die, SOP-8 (1.75 mm) -&gt; DFN LCC-8P-M05 (0.90 mm MAX) - U7 was the tallest rear part and drove the backshell's 0.95 floor pocket. Identical electricals (512 kbit I2C 0x50, 16-bit addressing, 1.8-3.6 V, 125 C, TY/GS AEC grade) - zero firmware change; same $10.19 @1, DK live-verified 2026-07-23 (1500 stock, CT MOQ 1). Mouser alt: 249-MB85RC512TYPNGA1. Repo datasheet covers both packages (drawing p.~end: 5.00x6.00, 0.90 MAX, 0.40 lead, 1.27 BSC). BOARD DONE 2026-07-23: DFN land placed + routed, pads/nets/stubs electrically verified (0 unconnected). Remaining: Change Footprint to solarglow:U7_DFN8 (PCB/fp-lib-table registers the lib), re-DRC. Hand-solder note (corrected 2026-07-23 from the p.21 drawing): terminals are recessed bottom contacts, NOT side-wettable - reflow/hot-air is the primary process; the land's extended outer toe is the deliberate iron fallback. Enclosure follow-up: the U7 pocket may be deletable.</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2628,7 +2628,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>FRAM - 512 kbit I2C archival log (0x50), power-gated on VNFC with the NFC tag</t>
+          <t>FRAM - 512 kbit I2C archival log (0x50), on always-on VS, parked in I2C Sleep (back-power fix)</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>REPACKAGED 2026-07-23 (height): same MB85RC512TY die, SOP-8 (1.75 mm) -&gt; DFN LCC-8P-M05 (0.90 mm MAX) - U7 was the tallest rear part and drove the backshell's 0.95 floor pocket. Identical electricals (512 kbit I2C 0x50, 16-bit addressing, 1.8-3.6 V, 125 C, TY/GS AEC grade) - zero firmware change; same $10.19 @1, DK live-verified 2026-07-23 (1500 stock, CT MOQ 1). Mouser alt: 249-MB85RC512TYPNGA1. Repo datasheet covers both packages (drawing p.~end: 5.00x6.00, 0.90 MAX, 0.40 lead, 1.27 BSC). BOARD DONE 2026-07-23: DFN land placed + routed, pads/nets/stubs electrically verified (0 unconnected). Remaining: Change Footprint to solarglow:U7_DFN8 (PCB/fp-lib-table registers the lib), re-DRC. Hand-solder note (corrected 2026-07-23 from the p.21 drawing): terminals are recessed bottom contacts, NOT side-wettable - reflow/hot-air is the primary process; the land's extended outer toe is the deliberate iron fallback. Enclosure follow-up: the U7 pocket may be deletable.</t>
+          <t>REPACKAGED 2026-07-23 (height): same MB85RC512TY die, SOP-8 (1.75 mm) -&gt; DFN LCC-8P-M05 (0.90 mm MAX) - U7 was the tallest rear part and drove the backshell's 0.95 floor pocket. Identical electricals (512 kbit I2C 0x50, 16-bit addressing, 1.8-3.6 V, 125 C, TY/GS AEC grade) - zero firmware change; same $10.19 @1, DK live-verified 2026-07-23 (1500 stock, CT MOQ 1). Mouser alt: 249-MB85RC512TYPNGA1. Repo datasheet covers both packages (drawing p.~end: 5.00x6.00, 0.90 MAX, 0.40 lead, 1.27 BSC). BOARD DONE 2026-07-23: DFN land placed + routed, pads/nets/stubs electrically verified (0 unconnected). Remaining: Change Footprint to solarglow:U7_DFN8 (PCB/fp-lib-table registers the lib), re-DRC. Hand-solder note (corrected 2026-07-23 from the p.21 drawing): terminals are recessed bottom contacts, NOT side-wettable - reflow/hot-air is the primary process; the land's extended outer toe is the deliberate iron fallback. Enclosure follow-up: the U7 pocket may be deletable. RE-RAILED 2026-07-23 (back-power fix, option A): VDD moved VNFC -&gt; VS + parked in the part's I2C Sleep mode (IZZ 0.20uA typ / 10uA max; enter S+F8h,addr,Sr+86h; ~450us wake) - kills the abs-max VIN&lt;=VDD+0.5 exposure from the VS bus pull-ups on a gated part (design-notes deep-dive addendum). SCH labels + firmware DONE; board copper re-net of U7.8 + C28.1 pending.</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
@@ -3678,7 +3678,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2611,6 +2611,11 @@
           <t>Verified active on DigiKey (product 12165099): TPS7A0233PDBVR, SOT-23-5, 200 mA nanopower LDO (TI TPS7A02 family, ~25 nA Iq). No repo datasheet. DK live-verified 2026-07-22: 296-TPS7A0233PDBVRCT-ND (DK 12165099), Active, $0.84 @1.</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>U9  TPS7A0233PDBVR  $0.84.pdf</t>
+        </is>
+      </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
           <t>296-TPS7A0233PDBVRCT-ND</t>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="8" min="1" max="1"/>
@@ -2611,7 +2611,7 @@
           <t>Verified active on DigiKey (product 12165099): TPS7A0233PDBVR, SOT-23-5, 200 mA nanopower LDO (TI TPS7A02 family, ~25 nA Iq). No repo datasheet. DK live-verified 2026-07-22: 296-TPS7A0233PDBVRCT-ND (DK 12165099), Active, $0.84 @1.</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t>U9  TPS7A0233PDBVR  $0.84.pdf</t>
         </is>
@@ -3251,15 +3251,15 @@
     <row r="48" ht="15" customHeight="1" s="9">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R17, R18</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>EN_STO_CH pull-up to VINT</t>
+          <t>EN_STO_CH pull-up to VINT (R17); Q2 gate pulldown (R18)</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3286,7 +3286,7 @@
         <v>0.1</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>Split 2026-07-23 from the former R16,R17 shared line: R17 is a non-critical pull-up and stays on the 0402 AEC-Q200 part (AC0402FR-071ML, DK YAG3450CT-ND). Prior shared-line note: Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active. (R16 STO-sense bottom; the R15 2M partner has no 0402 precision option, so this leg stays AEC-Q200 grade.)</t>
+          <t>Split 2026-07-23 from the former R16,R17 shared line: R17 is a non-critical pull-up and stays on the 0402 AEC-Q200 part (AC0402FR-071ML, DK YAG3450CT-ND). Prior shared-line note: Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active. (R16 STO-sense bottom; the R15 2M partner has no 0402 precision option, so this leg stays AEC-Q200 grade.) R18 ADDED 2026-07-23 (cold-start-deadlock fix): 1 M gate pulldown for Q2 -- holds the charge-disable FET off (charging ENABLED) while the MCU is dead/resetting. Same MPN, qty 1-&gt;2.</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
@@ -3669,22 +3669,83 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>EN_STO_CH low-side charge-disable buffer — cold-start-deadlock fix (dead MCU = charging enabled)</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>N-ch MOSFET, 60 V, logic-level</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>onsemi</t>
+        </is>
+      </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
+          <t>BSS138LT1G</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>v4 - NEW (audit fix)</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>ADDED 2026-07-23 (second-sift audit, FATAL fix): gate&lt;-PA4 push-pull via new net (R18 1M pulldown at the gate), drain=EN_STO_CH (place at the old PA4/net junction near U8/R17 -- keeps the 1M-class high-Z drain net short; gate line may run long), source=GND. Dead/resetting MCU -&gt; R18 holds gate low -&gt; FET off -&gt; EN_STO_CH floats to internal pull-up + R17 = charging ENABLED: a fully discharged card always recharges. Vgs(th) 0.5-1.5 V (fully on at 3.3 V drive); IDSS/Igss nA-class at 2.2 V (does not load the 1M node). Pick note: classic 2N7002LT1G/WT1G were Active but ZERO DK stock at audit time; BSS138LT1G live-verified 2026-07-23: BSS138LT1GOSCT-ND, Active, $0.34 @1, 204,900 stock, CT MOQ 1.</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="8" t="inlineStr">
+        <is>
+          <t>BSS138LT1GOSCT-ND</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="G57" s="8" t="inlineStr">
+        <is>
           <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
         </is>
       </c>
-      <c r="I56" s="8" t="n">
-        <v>139.76</v>
-      </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>Sum of the 49 priced Ext$ cells only. Every ordered on-board line is now priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="I57" s="8" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>Sum of the 50 priced Ext$ cells only (Q2 + R18 added 2026-07-23, +$0.44). Every ordered on-board line is priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).  Longevity/stability pass 2026-07-23: ceramics GRM-&gt;GRT (AEC-Q200) with V/tol bumps; resistors RC-&gt;AC (AEC-Q200), VSENSE divider R5/R6 to 0.1%/50ppm Yageo RE; U6 to AEC-Q100 TPS22918TDBVRQ1 (also clears the two zero-stock lines C25 + U6). Same footprints/values -- no layout change.</t>
         </is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -965,7 +965,7 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>UPSIZED 2026-07-23 (stability): 0402 RE 0.1%/50ppm -&gt; 0603 thin film 0.1%/25ppm (Yageo RT). VSENSE divider matched pair; same MPN as R16 - three refs now share RT0603BRD071ML. DK YAG4498CT-ND (CT MOQ 1), $0.10 @1, 169k stock. BOARD: two 0603 lands pending.</t>
+          <t>UPSIZED 2026-07-23 (stability): 0402 RE 0.1%/50ppm -&gt; 0603 thin film 0.1%/25ppm (Yageo RT). VSENSE divider matched pair; same MPN as R16 - three refs now share RT0603BRD071ML. DK YAG4498CT-ND (CT MOQ 1), $0.10 @1, 169k stock. BOARD: DONE 2026-07-25 — routed on R_0603_1608Metric, verified (0 unconnected).</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>UPSIZED 2026-07-23 (stability): 0402 X5R -&gt; 0603 X7R, stays Murata GRT (AEC-Q200). LDO input cap on the STO_LDO island (~5.5 V max) - X7R + bigger body = near-full capacitance under bias/temp. DK 490-GRT188R71E105KE13DCT-ND (CT MOQ 1), $0.14 @1, 91k stock. BOARD: 0603 land pending (Update PCB from Schematic).</t>
+          <t>UPSIZED 2026-07-23 (stability): 0402 X5R -&gt; 0603 X7R, stays Murata GRT (AEC-Q200). LDO input cap on the STO_LDO island (~5.5 V max) - X7R + bigger body = near-full capacitance under bias/temp. DK 490-GRT188R71E105KE13DCT-ND (CT MOQ 1), $0.14 @1, 91k stock. BOARD: DONE 2026-07-25 — routed on C_0603_1608Metric, verified.</t>
         </is>
       </c>
       <c r="M40" s="8" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>UPSIZED 2026-07-23 (stability): 0402 X5R -&gt; 0603 X7R 25 V. U9 LDO output cap - TPS7A02 loop stability rides on effective C staying in band; X7R holds it over temp/bias. X7R chosen over staying GRT/AEC (the GRT 0603 2.2uF is X5R; dielectric wins here - GRT188R61E225KE13D is the AEC alternate). DK 490-GRM188Z71E225ME43DCT-ND (CT MOQ 1), $0.17 @1, 341k stock. BOARD: 0603 land pending.</t>
+          <t>UPSIZED 2026-07-23 (stability): 0402 X5R -&gt; 0603 X7R 25 V. U9 LDO output cap - TPS7A02 loop stability rides on effective C staying in band; X7R holds it over temp/bias. X7R chosen over staying GRT/AEC (the GRT 0603 2.2uF is X5R; dielectric wins here - GRT188R61E225KE13D is the AEC alternate). DK 490-GRM188Z71E225ME43DCT-ND (CT MOQ 1), $0.17 @1, 341k stock. BOARD: DONE 2026-07-25 — routed on C_0603_1608Metric, verified.</t>
         </is>
       </c>
       <c r="M41" s="8" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>UPSIZED 2026-07-23 (stability): C26 (0402 X5R 10 V) and C27 (0603 X5R 16 V) merge onto one 0805 X7R 10 V line. 10 uF at 0402 is the density ceiling (worst DC-bias/temp rolloff on the board); 0805 X7R holds capacitance. C26 = VINT (~2.2 V, trivial bias); C27 = STO (&lt;=5.5 V on 10 V X7R = comfortable). NOTE: the AEC-Q200 0805 option (Cal-Chip GMT21X7R106K16NT3) is reel-only MOQ 3000 - rejected for a one-of-one build; Murata GRM CT MOQ 1 chosen instead. DK 490-10516-1-ND, $0.12 @1, 143k stock. BOARD: two 0805 lands pending.</t>
+          <t>UPSIZED 2026-07-23 (stability): C26 (0402 X5R 10 V) and C27 (0603 X5R 16 V) merge onto one 0805 X7R 10 V line. 10 uF at 0402 is the density ceiling (worst DC-bias/temp rolloff on the board); 0805 X7R holds capacitance. C26 = VINT (~2.2 V, trivial bias); C27 = STO (&lt;=5.5 V on 10 V X7R = comfortable). NOTE: the AEC-Q200 0805 option (Cal-Chip GMT21X7R106K16NT3) is reel-only MOQ 3000 - rejected for a one-of-one build; Murata GRM CT MOQ 1 chosen instead. DK 490-10516-1-ND, $0.12 @1, 143k stock. BOARD: DONE 2026-07-25 — both routed on C_0805_2012Metric, verified.</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>UPGRADED 2026-07-23 (stability): moved to an 0603 land to unlock precision that does not exist at 2M in 0402 -&gt; Vishay MCT0603 thin film, 0.1% / 25 ppm. Pairs with R16 (same land + precision class) so the STO_SNS divider ratio is ~0.1% with matched tempco. DK 541-MCT0603MD2004BP500CT-ND, $0.22 @1, 36k stock, Active. BOARD: new 0603 land to place + route (was solarglow:C1 0402-class); PCB rework pending.</t>
+          <t>UPGRADED 2026-07-23 (stability): moved to an 0603 land to unlock precision that does not exist at 2M in 0402 -&gt; Vishay MCT0603 thin film, 0.1% / 25 ppm. Pairs with R16 (same land + precision class) so the STO_SNS divider ratio is ~0.1% with matched tempco. DK 541-MCT0603MD2004BP500CT-ND, $0.22 @1, 36k stock, Active. BOARD: DONE 2026-07-25 — routed on R_0603_1608Metric, verified (0 unconnected).</t>
         </is>
       </c>
       <c r="M46" s="8" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>UPGRADED 2026-07-23 (stability): 0603 thin film 0.1% / 25 ppm (Yageo RT), matched with R15 so the divider ratio carries the full precision. DK YAG4498CT-ND, $0.10 @1, 169k stock, Active. Split from the former R16,R17 shared line. BOARD: new 0603 land to place + route; PCB rework pending.</t>
+          <t>UPGRADED 2026-07-23 (stability): 0603 thin film 0.1% / 25 ppm (Yageo RT), matched with R15 so the divider ratio carries the full precision. DK YAG4498CT-ND, $0.10 @1, 169k stock, Active. Split from the former R16,R17 shared line. BOARD: DONE 2026-07-25 — routed on R_0603_1608Metric, verified.</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Reverse-mount; light path runs through the all-layer keepout window. Fully verified 2026-07-02: DK lists the full code; ams-OSRAM packing doc maps it to Q65110A9267 = the REVERSE-mount bin per the LA P47F datasheet; DK CT number confirmed verbatim; 11.3k in stock; $0.43 @ 1 / $0.294 @ 10.</t>
+          <t>Reverse-mount; light path runs through the all-layer keepout window. Fully verified 2026-07-02: DK lists the full code; ams-OSRAM packing doc maps it to Q65110A9267 = the REVERSE-mount bin per the LA P47F datasheet; DK CT number confirmed verbatim; 11.3k in stock; $0.43 @ 1 / $0.294 @ 10. LED AUDIT 2026-07-25: part CONFIRMED OPTIMAL for this land - newest + only in-stock/Active amber in the reverse-mount PointLED land (older LA P47B/P476 are ~5-8x dimmer, zero stock; the brighter-floor -AABA- variant is obsolete). 120deg near-Lambertian emission is the right optimization for diffuse FR4 backlighting (high-mcd alternatives are 11-20deg pencil beams on other footprints). CAVEAT: the order code is UNBINNED - V2BB/24/3B5A are min-to-max SPANS, so brightness varies ~3x part-to-part (V2 900mcd/3030mlm ~49lm/W .. BB 2800mcd/7560mlm ~123lm/W @30mA); DK's '1850 mcd' is a mid-span nominal, NOT a guarantee. Size the energy budget / glow duty to the V2 FLOOR. Package field '3.4x1.9 mm' verified against the p.12 drawing (Ø2.5 round body in a 3.4x1.9 outline). SEPARATE BOARD ISSUE (see TODO): the D2-D5 land pads sit 0.25mm too far inward vs the recommended land.</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -3744,10 +3744,11 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).  Longevity/stability pass 2026-07-23: ceramics GRM-&gt;GRT (AEC-Q200) with V/tol bumps; resistors RC-&gt;AC (AEC-Q200), VSENSE divider R5/R6 to 0.1%/50ppm Yageo RE; U6 to AEC-Q100 TPS22918TDBVRQ1 (also clears the two zero-stock lines C25 + U6). Same footprints/values -- no layout change.</t>
+          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 added U6 (load switch, now TPS22917DBVT) + R14 (1 M NFC_EN pulldown) and converted most passives to 0402 to match the board lands. UPDATE 2026-07-25: every ordered line is now live-priced (no blanks); the longevity/precision passes moved C4/C13/C25/C22/C23/R5/R6/R15/R16 to 0603 and C26/C27 to 0805; SJ1 is DNP; Q2+R18 added by the cold-start-deadlock fix.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).  Longevity/stability pass 2026-07-23: ceramics GRM-&gt;GRT (AEC-Q200) with V/tol bumps; resistors RC-&gt;AC (AEC-Q200), VSENSE divider R5/R6 to 0.1%/50ppm Yageo RE; U6 to AEC-Q100 TPS22918TDBVRQ1 (also cleared the two zero-stock lines C25 + U6); U6 was then re-swapped 2026-07-23 to TPS22917DBVT for dark current. Same footprints/values -- no layout change.</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -407,7 +407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="8" min="1" max="1"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>MCU decoupling (VDD)</t>
+          <t>MCU decoupling (VS) — U1 pin-24/25 pair</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C3/C6/C7/C8 are the same line item.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C3/C6/C7/C8 are the same line item.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.  2026-07-26: C29 added for U1's OTHER VDD/GND pair (18/19); C1 now serves 24/25 alone (pad 1 is 1.97 mm from pin 24 vs 3.07 mm from pin 18).</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>FRAM VNFC decoupling</t>
+          <t>FRAM (U7) decoupling — on VS</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.</t>
+          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.  CORRECTED 2026-07-26: the Function read "FRAM VNFC decoupling", which predates the 2026-07-23 back-power fix. U7 was re-railed to always-on VS and C28 followed it — board pad 1 is on VS, not VNFC. VNFC decoupling is C8's job (U5, the tag), and C8 is correctly on VNFC.</t>
         </is>
       </c>
       <c r="M45" s="8" t="inlineStr">
@@ -3132,65 +3132,65 @@
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="9">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>R15</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>2 M, 0603, ±0.1%, 25 ppm</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>0603 (R_0603_1608Metric)</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>Vishay</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>MCT0603MD2004BP500</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I46" s="8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MCU decoupling (VS) — U1 pin-18/19 pair</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>100 nF, 0402, X7R</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Murata</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>GRT155R71H104KE01D</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>v4 NEW</t>
         </is>
       </c>
-      <c r="K46" s="8" t="inlineStr">
-        <is>
-          <t>UPGRADED 2026-07-23 (stability): moved to an 0603 land to unlock precision that does not exist at 2M in 0402 -&gt; Vishay MCT0603 thin film, 0.1% / 25 ppm. Pairs with R16 (same land + precision class) so the STO_SNS divider ratio is ~0.1% with matched tempco. DK 541-MCT0603MD2004BP500CT-ND, $0.22 @1, 36k stock, Active. BOARD: DONE 2026-07-25 — routed on R_0603_1608Metric, verified (0 unconnected).</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t>541-MCT0603MD2004BP500CT-ND</t>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.  ADDED 2026-07-26: U1 had ONE decoupling cap (C1) for TWO VDD/GND pairs. C29 was placed and routed on the board first and was missing from both the schematic and this master; the schematic symbol landed in f5581d0. Board pad 1 is 1.00 mm from U1 pin 18 (VS) and 1.27 mm from pin 19 (GND). Same part as C1/C3/C5/C6/C7/C8/C12/C24/C28.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="9">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>STO sense divider bottom (STO_SNS -&gt; GND)</t>
+          <t>STO sense divider top (STO -&gt; STO_SNS)</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>1 M, 0603, ±0.1%, 25 ppm</t>
+          <t>2 M, 0603, ±0.1%, 25 ppm</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -3213,63 +3213,58 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>RT0603BRD071ML</t>
+          <t>MCT0603MD2004BP500</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>v4 - REWORK 0603</t>
+          <t>v4 NEW</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>UPGRADED 2026-07-23 (stability): 0603 thin film 0.1% / 25 ppm (Yageo RT), matched with R15 so the divider ratio carries the full precision. DK YAG4498CT-ND, $0.10 @1, 169k stock, Active. Split from the former R16,R17 shared line. BOARD: DONE 2026-07-25 — routed on R_0603_1608Metric, verified.</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>UPGRADED 2026-07-23 (stability): moved to an 0603 land to unlock precision that does not exist at 2M in 0402 -&gt; Vishay MCT0603 thin film, 0.1% / 25 ppm. Pairs with R16 (same land + precision class) so the STO_SNS divider ratio is ~0.1% with matched tempco. DK 541-MCT0603MD2004BP500CT-ND, $0.22 @1, 36k stock, Active. BOARD: DONE 2026-07-25 — routed on R_0603_1608Metric, verified (0 unconnected).</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>YAG4498CT-ND</t>
+          <t>541-MCT0603MD2004BP500CT-ND</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="9">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>R17, R18</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>EN_STO_CH pull-up to VINT (R17); Q2 gate pulldown (R18)</t>
+          <t>STO sense divider bottom (STO_SNS -&gt; GND)</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>1 M, 0402, ±1%</t>
+          <t>1 M, 0603, ±0.1%, 25 ppm</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0603 (R_0603_1608Metric)</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -3279,23 +3274,23 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>AC0402FR-071ML</t>
+          <t>RT0603BRD071ML</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>v4 - REWORK 0603</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>Split 2026-07-23 from the former R16,R17 shared line: R17 is a non-critical pull-up and stays on the 0402 AEC-Q200 part (AC0402FR-071ML, DK YAG3450CT-ND). Prior shared-line note: Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active. (R16 STO-sense bottom; the R15 2M partner has no 0402 precision option, so this leg stays AEC-Q200 grade.) R18 ADDED 2026-07-23 (cold-start-deadlock fix): 1 M gate pulldown for Q2 -- holds the charge-disable FET off (charging ENABLED) while the MCU is dead/resetting. Same MPN, qty 1-&gt;2.</t>
+          <t>UPGRADED 2026-07-23 (stability): 0603 thin film 0.1% / 25 ppm (Yageo RT), matched with R15 so the divider ratio carries the full precision. DK YAG4498CT-ND, $0.10 @1, 169k stock, Active. Split from the former R16,R17 shared line. BOARD: DONE 2026-07-25 — routed on R_0603_1608Metric, verified.</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
@@ -3305,92 +3300,92 @@
       </c>
       <c r="M48" s="8" t="inlineStr">
         <is>
-          <t>YAG3450CT-ND</t>
+          <t>YAG4498CT-ND</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="9">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
+          <t>R17, R18</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
-        </is>
+          <t>EN_STO_CH pull-up to VINT (R17); Q2 gate pulldown (R18)</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>1 M, 0402, ±1%</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>AC0402FR-071ML</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>0.2</v>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Split 2026-07-23 from the former R16,R17 shared line: R17 is a non-critical pull-up and stays on the 0402 AEC-Q200 part (AC0402FR-071ML, DK YAG3450CT-ND). Prior shared-line note: Reuses the project 1 M part (shared with R5/R6/R14). DK live-verified 2026-07-22: 311-1.00MLRCT-ND, Active, $0.10 @1 (DKPN corrected).  UPGRADED 2026-07-23 (longevity): Yageo RC-&gt;AC (AEC-Q200 automotive grade), same value/tol. DK YAG3450CT-ND, $0.1 @1, Active. (R16 STO-sense bottom; the R15 2M partner has no 0402 precision option, so this leg stays AEC-Q200 grade.) R18 ADDED 2026-07-23 (cold-start-deadlock fix): 1 M gate pulldown for Q2 -- holds the charge-disable FET off (charging ENABLED) while the MCU is dead/resetting. Same MPN, qty 1-&gt;2.</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>YAG3450CT-ND</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>PRG1</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="n">
-        <v>1</v>
+          <t>—</t>
+        </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>Adafruit UPDI Friend</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>26.4×17.8 mm board + JST-SH lead</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Adafruit</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="I50" s="8" t="n">
-        <v>6.95</v>
+          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
+        </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
           <t>AUX</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="inlineStr">
-        <is>
-          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
-        <is>
-          <t>(guide linked in firmware/README)</t>
-        </is>
-      </c>
-      <c r="M50" s="8" t="inlineStr">
-        <is>
-          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="360.4" customHeight="1" s="9">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>CBL1</t>
+          <t>PRG1</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
@@ -3398,28 +3393,34 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
+          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>TC2030-MCP (legged, RJ12 end)</t>
+          <t>Adafruit UPDI Friend</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>6-ft cable, 6P6C modular plug</t>
+          <t>26.4×17.8 mm board + JST-SH lead</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>Adafruit</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>TC2030-MCP</t>
-        </is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>6.95</v>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
@@ -3428,52 +3429,52 @@
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback. DK live-verified 2026-07-22: DK TC2030-MCPTC-ND, Active, $36.00 @1 (AUX bench cable, one-time; not a per-board cost).</t>
+          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
+          <t>(guide linked in firmware/README)</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
         <is>
-          <t>(DK page verified — order by MPN)</t>
+          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>HW1</t>
+          <t>CBL1</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
+          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
+          <t>TC2030-MCP (legged, RJ12 end)</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>head ⌀3.8 × 1.4 mm</t>
+          <t>6-ft cable, 6P6C modular plug</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>DIN 84 M2×3 brass</t>
+          <t>TC2030-MCP</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -3483,52 +3484,52 @@
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
+          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback. DK live-verified 2026-07-22: DK TC2030-MCPTC-ND, Active, $36.00 @1 (AUX bench cable, one-time; not a per-board cost).</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>docs/screw-m2x3-cheese.png</t>
+          <t>TC1  Tag-Connect TC2030-MCP  $0.pdf</t>
         </is>
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>ENC1</t>
+          <t>HW1</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V, 3.55 mm stack</t>
+          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>CNC from enclosure/ STEP</t>
+          <t>head ⌀3.8 × 1.4 mm</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>(PCBWay CNC or equiv.)</t>
+          <t>(generic)</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>(order from enclosure/*.step)</t>
+          <t>DIN 84 M2×3 brass</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -3538,12 +3539,12 @@
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>enclosure/README.md</t>
+          <t>docs/screw-m2x3-cheese.png</t>
         </is>
       </c>
       <c r="M53" s="8" t="inlineStr">
@@ -3555,7 +3556,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>INS1</t>
+          <t>ENC1</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
@@ -3563,42 +3564,42 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>~0.05 mm polyimide, die-cut to board outline</t>
+          <t>Ti-6Al-4V, 3.55 mm stack</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>sheet / die-cut</t>
+          <t>CNC from enclosure/ STEP</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>(generic)</t>
+          <t>(PCBWay CNC or equiv.)</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>(polyimide film, 0.05 mm)</t>
+          <t>(order from enclosure/*.step)</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>AUX-OPTIONAL</t>
+          <t>AUX</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
+          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>enclosure/README.md</t>
         </is>
       </c>
       <c r="M54" s="8" t="inlineStr">
@@ -3610,7 +3611,7 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>FER1</t>
+          <t>INS1</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
@@ -3618,135 +3619,190 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
+          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
+          <t>~0.05 mm polyimide, die-cut to board outline</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
+          <t>sheet / die-cut</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Würth Elektronik</t>
+          <t>(generic)</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>364006</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>17.43</v>
+          <t>(polyimide film, 0.05 mm)</t>
+        </is>
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>AUX</t>
+          <t>AUX-OPTIONAL</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>FINAL, verified 2026-07-03: DK 732-5049-ND, Active, tray, $17.43 @ 1 (51 in stock at verification; 24-wk mfr lead — buy with the order). 60×60 mm sheet, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA); one sheet = 4 patches. Cut 12.2 × 25.8 mm on the 2 mm score grid; brace channel depth = measured stack − 0.05 (sits ~0.05 proud, seats flush; PET face to the board, PSA into the brace). Stock-dry fallback: 3× stacked 3641014 (732-13935-ND, $4.19 ea, µ′150/µ″3 @ 13.56 MHz, 0.14 mm ea) ≈ same ferrite thickness; last resort Laird MHLL6060-300 (240-2791-ND, 0.09 mm, weakest). All three datasheets in repo.</t>
+          <t>BENCH CONTINGENCY ONLY (was a standing spec; corrected 2026-07-03): the committed shell runs kapton_th = 0.00 — lip and locator contacts land on bare laminate by design, and the brace + ferrite cover the middle third. Buy only if a bench via/short audit on the contact bands ever demands a die-cut strip. The shell generator notes 0.05 reinstates it if needed.</t>
         </is>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>FER1  Wurth WE-FSFS 364006  $17.43.pdf + FER1-alt  Wurth WE-FSFS 3641014  $4.19.pdf + FER1-alt  Laird MHLL6060-300  $6.40.pdf (repo)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M55" s="8" t="inlineStr">
         <is>
-          <t>732-5049-ND</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
+          <t>FER1</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Würth Elektronik</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>364006</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>FINAL, verified 2026-07-03: DK 732-5049-ND, Active, tray, $17.43 @ 1 (51 in stock at verification; 24-wk mfr lead — buy with the order). 60×60 mm sheet, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA); one sheet = 4 patches. Cut 12.2 × 25.8 mm on the 2 mm score grid; brace channel depth = measured stack − 0.05 (sits ~0.05 proud, seats flush; PET face to the board, PSA into the brace). Stock-dry fallback: 3× stacked 3641014 (732-13935-ND, $4.19 ea, µ′150/µ″3 @ 13.56 MHz, 0.14 mm ea) ≈ same ferrite thickness; last resort Laird MHLL6060-300 (240-2791-ND, 0.09 mm, weakest). All three datasheets in repo.</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>FER1  Wurth WE-FSFS 364006  $17.43.pdf + FER1-alt  Wurth WE-FSFS 3641014  $4.19.pdf + FER1-alt  Laird MHLL6060-300  $6.40.pdf (repo)</t>
+        </is>
+      </c>
+      <c r="M56" s="8" t="inlineStr">
+        <is>
+          <t>732-5049-ND</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B56" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="B57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>EN_STO_CH low-side charge-disable buffer — cold-start-deadlock fix (dead MCU = charging enabled)</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>N-ch MOSFET, 60 V, logic-level</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>SOT-23</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>onsemi</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>BSS138LT1G</t>
         </is>
       </c>
-      <c r="H56" s="8" t="n">
+      <c r="H57" s="8" t="n">
         <v>0.34</v>
       </c>
-      <c r="I56" s="8" t="n">
+      <c r="I57" s="8" t="n">
         <v>0.34</v>
       </c>
-      <c r="J56" s="8" t="inlineStr">
+      <c r="J57" s="8" t="inlineStr">
         <is>
           <t>v4 - NEW (audit fix)</t>
         </is>
       </c>
-      <c r="K56" s="8" t="inlineStr">
+      <c r="K57" s="8" t="inlineStr">
         <is>
           <t>ADDED 2026-07-23 (second-sift audit, FATAL fix): gate&lt;-PA4 push-pull via new net (R18 1M pulldown at the gate), drain=EN_STO_CH (place at the old PA4/net junction near U8/R17 -- keeps the 1M-class high-Z drain net short; gate line may run long), source=GND. Dead/resetting MCU -&gt; R18 holds gate low -&gt; FET off -&gt; EN_STO_CH floats to internal pull-up + R17 = charging ENABLED: a fully discharged card always recharges. Vgs(th) 0.5-1.5 V (fully on at 3.3 V drive); IDSS/Igss nA-class at 2.2 V (does not load the 1M node). Pick note: classic 2N7002LT1G/WT1G were Active but ZERO DK stock at audit time; BSS138LT1G live-verified 2026-07-23: BSS138LT1GOSCT-ND, Active, $0.34 @1, 204,900 stock, CT MOQ 1.</t>
         </is>
       </c>
-      <c r="L56" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M56" s="8" t="inlineStr">
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M57" s="8" t="inlineStr">
         <is>
           <t>BSS138LT1GOSCT-ND</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="G57" s="8" t="inlineStr">
+    <row r="58">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
         </is>
       </c>
-      <c r="I57" s="8" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="K57" s="8" t="inlineStr">
+      <c r="I58" s="8" t="n">
+        <v>140.3</v>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
         <is>
           <t>Sum of the 50 priced Ext$ cells only (Q2 + R18 added 2026-07-23, +$0.44). Every ordered on-board line is priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 added U6 (load switch, now TPS22917DBVT) + R14 (1 M NFC_EN pulldown) and converted most passives to 0402 to match the board lands. UPDATE 2026-07-25: every ordered line is now live-priced (no blanks); the longevity/precision passes moved C4/C13/C25/C22/C23/R5/R6/R15/R16 to 0603 and C26/C27 to 0805; SJ1 is DNP; Q2+R18 added by the cold-start-deadlock fix.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).  Longevity/stability pass 2026-07-23: ceramics GRM-&gt;GRT (AEC-Q200) with V/tol bumps; resistors RC-&gt;AC (AEC-Q200), VSENSE divider R5/R6 to 0.1%/50ppm Yageo RE; U6 to AEC-Q100 TPS22918TDBVRQ1 (also cleared the two zero-stock lines C25 + U6); U6 was then re-swapped 2026-07-23 to TPS22917DBVT for dark current. Same footprints/values -- no layout change.</t>
         </is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>DD-era VDDIO2 tie (pin 10 = PD0 on the EA) — DNP, must NOT be bridged</t>
+          <t>REMOVED from schematic AND board 2026-07-30 — row kept as lineage only. Was: DD-era VDDIO2 tie (pin 10 = PD0 on the EA), DNP, must NOT be bridged.</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>DNP 2026-07-23 with the AVR-EA U1 swap: pin 10 on the EA28 is PD0 (GPIO), not VDDIO2, so the 0R VS tie must NOT be bridged - PD0 floats and firmware inits it input-disabled. The RC0805JR-070RL 0R stays a valid spare if the DD28 is ever reinstated (land unchanged).</t>
+          <t>Culled 2026-07-30: the symbol, its land and the strap are gone from the sources (PR #114 sch cull + the 2026-07-30 board sync); bridging it would have tied a GPIO to VS. DNP'd 2026-07-23 with the AVR-EA U1 swap; deleted outright once DRC could gate on it. The RC0805JR-070RL 0R note no longer applies — there is no land.</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
@@ -2210,43 +2210,43 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>NFC antenna trim — DNP (U5's internal 50 pF tunes the coil)</t>
+          <t>NFC tank trim — sets the ENCLOSED resonance to 14.45 MHz against AN11276 §4.2.1's 14.5 MHz single-tag target. PLACED at assembly since 2026-07-30 (was DNP/bench-trim).</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>DNP (NP0/C0G land)</t>
+          <t>47 pF, C0G/NP0, ±2%, 250 V, High-Q</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>0402 (NP0/C0G land)</t>
+          <t>0805 (C_0805_2012Metric)</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Johanson</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>(DNP — not ordered)</t>
+          <t>QSCT251Q470G1GV001E</t>
         </is>
       </c>
       <c r="H30" s="14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>DNP</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): the 364006 sheet (0.38 mm stack, µ′~100-150 class ferrite) against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
+          <t>Derived, not trimmed (2026-07-30): coil L = 0.958 uH by Greenhouse on the board's 7 rails (cross-checked vs Mohan and vs NXP's Class 5 reference antenna, which the same code reproduces to 14.2-14.7 MHz); ferrite loads it +10-36% (1.05-1.30 uH); tag Ci = 50 pF (NT3H2211 Table 42); Cc = 6 pF (AN11276 Table 2). 47 pF -&gt; 14.31-15.91 MHz across the whole ferrite range, never under the 13.56 carrier. The old 82 pF/bench-trim plan solved the same tank for 13.56 exactly and sat ~1 MHz UNDER the carrier once enclosed. MEASURE ENCLOSED: bare reads ~16.7 MHz and that is expected, the ferrite brings it down. If the first enclosed card lands outside ~13.6-15.3 MHz the same-series ladder neighbours are 39 pF (QSCT251Q390G1GV001E) and 56 pF (QSCT251Q560G1GV001E), both Active/stocked at DigiKey 2026-07-30. DK P/N 712-QSCT251Q470G1GV001ECT-ND (CT, MOQ 1) / ...ETR-ND (reel 4k).</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>2.76 µH design value</t>
+          <t>0.96 µH computed (bare copper)</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>Sch-only symbol, no footprint. Inductance set by copper geometry; C9 land reserved for bench trim against it. Nothing to order or place.</t>
+          <t>Sch-only symbol, no footprint. L = 0.958 uH bare by Greenhouse partial-inductance on the committed copper (7 turns, 0.30 mm trace, 0.60 mm pitch; 60% of it is turn-to-turn mutual), matching this BOM's own 2026-07-02 partial-inductance figure of 0.98 uH and validated by reproducing NXP's Class 5 reference antenna to a quarter-megahertz. Ferrite-loaded (FER1) it rises to ~1.05-1.30 uH. The schematic symbol says 1.0uH, which is right. The old '2.76 uH design value' here was the stale pre-rebuild estimate this row itself flagged for fixing. C9 (47 pF, placed) tunes against this L — see its row.</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
@@ -3132,56 +3132,56 @@
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="9">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>MCU decoupling (VS) — U1 pin-18/19 pair</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>100 nF, 0402, X7R</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>Murata</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>GRT155R71H104KE01D</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>v4 NEW</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="8" t="inlineStr">
         <is>
           <t>Reuses the project 100 nF 0402 part. DK live-verified 2026-07-22: 490-3261-1-ND, Active, $0.10 @1.  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT155R71H104KE01DCT-ND, $0.1 @1, Active. 16-&gt;50 V margin.  ADDED 2026-07-26: U1 had ONE decoupling cap (C1) for TWO VDD/GND pairs. C29 was placed and routed on the board first and was missing from both the schematic and this master; the schematic symbol landed in f5581d0. Board pad 1 is 1.00 mm from U1 pin 18 (VS) and 1.27 mm from pin 19 (GND). Same part as C1/C3/C5/C6/C7/C8/C12/C24/C28.</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t>490-GRT155R71H104KE01DCT-ND</t>
         </is>
@@ -3792,19 +3792,18 @@
         </is>
       </c>
       <c r="I58" s="8" t="n">
-        <v>140.3</v>
+        <v>141.5</v>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>Sum of the 50 priced Ext$ cells only (Q2 + R18 added 2026-07-23, +$0.44). Every ordered on-board line is priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
+          <t>Sum of the 51 priced Ext$ cells only (C9 joined the order 2026-07-30, +$1.15; Q2 + R18 added 2026-07-23, +$0.44). Every ordered on-board line is priced (U8/AEM10300 filled from Mouser 2026-07-22). See footnote.</t>
+        </is>
+      </c>
+    </row>
     <row r="60">
       <c r="A60" s="15" t="inlineStr">
         <is>
-          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 added U6 (load switch, now TPS22917DBVT) + R14 (1 M NFC_EN pulldown) and converted most passives to 0402 to match the board lands. UPDATE 2026-07-25: every ordered line is now live-priced (no blanks); the longevity/precision passes moved C4/C13/C25/C22/C23/R5/R6/R15/R16 to 0603 and C26/C27 to 0805; SJ1 is DNP; Q2+R18 added by the cold-start-deadlock fix.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).  Longevity/stability pass 2026-07-23: ceramics GRM-&gt;GRT (AEC-Q200) with V/tol bumps; resistors RC-&gt;AC (AEC-Q200), VSENSE divider R5/R6 to 0.1%/50ppm Yageo RE; U6 to AEC-Q100 TPS22918TDBVRQ1 (also cleared the two zero-stock lines C25 + U6); U6 was then re-swapped 2026-07-23 to TPS22917DBVT for dark current. Same footprints/values -- no layout change.</t>
+          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 added U6 (load switch, now TPS22917DBVT) + R14 (1 M NFC_EN pulldown) and converted most passives to 0402 to match the board lands. UPDATE 2026-07-25: every ordered line is now live-priced (no blanks); the longevity/precision passes moved C4/C13/C25/C22/C23/R5/R6/R15/R16 to 0603 and C26/C27 to 0805; SJ1 removed outright 2026-07-30 (was DNP since the EA swap); Q2+R18 added by the cold-start-deadlock fix.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).  Supercaps (SS17 3-153-440 / WS17 3-153-438) live-verified via DigiKey 2026-07-22. Full BOM re-verified live against DigiKey 2026-07-22: format-derived DK P/Ns replaced with real ones, prices refreshed, and C22/C23/C26 flagged (see rows).  Longevity/stability pass 2026-07-23: ceramics GRM-&gt;GRT (AEC-Q200) with V/tol bumps; resistors RC-&gt;AC (AEC-Q200), VSENSE divider R5/R6 to 0.1%/50ppm Yageo RE; U6 to AEC-Q100 TPS22918TDBVRQ1 (also cleared the two zero-stock lines C25 + U6); U6 was then re-swapped 2026-07-23 to TPS22917DBVT for dark current. Same footprints/values -- no layout change.  Passive audit #2 2026-07-30: C9 placed at 47 pF (derived, Johanson 0805); C25 flagged under the AEM CSRC minimum at bias and C26/C27 stock-zero at DK+Mouser — re-pick candidates in TODO.md; every other MPN re-verified Active/stocked.</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -2974,43 +2974,43 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>AEM BUFSRC input buffer cap</t>
+          <t>AEM CSRC buffer at BUFSRC (re-picked audit #2 2026-07-30: 0603/10V derated under the AEM's 13 µF effective minimum)</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>22 uF, 10 V, 0603, X5R</t>
+          <t>22 µF, 16 V, 0805, X5R</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805 (C_0805_2012Metric)</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>GRT188R61A226ME13D</t>
+          <t>C2012X5R1C226M125AC</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>v4 NEW</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>AEM10300 datasheet Table 11 CSRC = GRM188R61A226ME15D (22 uF, 10 V, X5R, 0603). 10 V rating (was 6.3 V) keeps usable capacitance at the SRC node, which rides toward panel Voc ~4.15 V where a 6.3 V X5R 0603 derates hard. DK live-verified 2026-07-22: 490-10476-1-ND, Active, $0.16 @1 (DKPN + price filled).  UPGRADED 2026-07-23 (longevity): GRM-&gt;GRT (Murata AEC-Q200 automotive grade). DK 490-GRT188R61A226ME13DCT-ND, $0.31 @1, Active. Also fixes the zero-stock GRM188R61A226ME15D.</t>
+          <t>Re-pick 2026-07-30 (audit #2). Old GRT188R61A226ME13D (0603/10V X5R) held ~9-12 uF at the 3.1-4.15 V BUFSRC bias vs the AEM10300's min 13 uF (Table 6 footnote 1 names DC-bias derating verbatim). 16V/0805 holds ~15-17 uF. DK 445-7647-1-ND (CT), 11,799 in stock, $0.56 q1, verified live 2026-07-30. Fits in place (measured gaps SC3 0.529 / L2 0.575 / SB2 0.776 mm); a 1206 does NOT fit. LAND: 0603-&gt;0805 sync pending in KiCad (footprint_symbol_mismatch tripwire armed); part_heights 0.90-&gt;1.25 rides with the sync.</t>
         </is>
       </c>
       <c r="M43" s="8" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>AEM VINT buffer (C26) + STO local bulk/decoupling (C27)</t>
+          <t>AEM VINT buffer (C26) + STO local bulk/decoupling (C27) — re-picked audit #2 2026-07-30 (old MPN stock-zero at DK AND Mouser)</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>10 µF, 10 V, 0805, X7R</t>
+          <t>10 µF, 16 V, 0805, X7R</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -3045,28 +3045,28 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>GRM21BR71A106KA73L</t>
+          <t>CL21B106KOQNNNG</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>v4 - REWORK 0805</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>UPSIZED 2026-07-23 (stability): C26 (0402 X5R 10 V) and C27 (0603 X5R 16 V) merge onto one 0805 X7R 10 V line. 10 uF at 0402 is the density ceiling (worst DC-bias/temp rolloff on the board); 0805 X7R holds capacitance. C26 = VINT (~2.2 V, trivial bias); C27 = STO (&lt;=5.5 V on 10 V X7R = comfortable). NOTE: the AEC-Q200 0805 option (Cal-Chip GMT21X7R106K16NT3) is reel-only MOQ 3000 - rejected for a one-of-one build; Murata GRM CT MOQ 1 chosen instead. DK 490-10516-1-ND, $0.12 @1, 143k stock. BOARD: DONE 2026-07-25 — both routed on C_0805_2012Metric, verified.</t>
+          <t>Re-pick 2026-07-30 (audit #2). GRM21BR71A106KA73L: 0 stock at DigiKey (all package types) AND no availability at Mouser; auto sibling GRT21BR71A106KE13L is NRND. Samsung CL21B106KOQNNNG 16V X7R: Mouser 187-CL21B106KOQNNNG, 4,292 in stock, $0.22 q1, verified live 2026-07-30. 16V halves the DC-bias loss on C27's 5.5 V STO node (was 55% of a 10V rating). BODY 1.40 mm max -&gt; part_heights C26/C27 = 1.45 (landed with this re-pick). Same 0805 land, zero layout change.</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="I58" s="8" t="n">
-        <v>141.5</v>
+        <v>141.9</v>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>

--- a/PCB/solar-glow-drh-v4_0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v4_0-BOM.xlsx
@@ -1958,25 +1958,25 @@
     <row r="26" ht="15" customHeight="1" s="9">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>TP1</t>
+          <t>TP1–TP7</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>VIN test pad (solar node SRC) — charge test / panel emulation</t>
+          <t>Test pads — TP1: VIN (solar node SRC); TP2–TP7: harvest-chain probe points (VS, MID, LX_LOUT, VINT, BUFSRC, STO_LDO)</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>1× bare SMD pad</t>
+          <t>7× bare SMD pads</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>1.7 mm sq, B side</t>
+          <t>TP1 1.7 mm sq; TP2–TP7 Ø1.0 mm, B side</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>(bare pad — no component)</t>
+          <t>(bare pads — no component)</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>v3.0 addition at (48.4, 12.0). Mark DNP in the CPL.</t>
+          <t>TP1 v3.0 at (48.4, 12.0). TP2–TP7 added 2026-07-30: the whole harvester was unprobeable (audit find); pads sit on own-net B.Cu, stub-fed where needed, and pair with panel tooling holes TH1/TH2 for in-frame pogo test. Mark all DNP in the CPL.</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
